--- a/tools/importer/reports/import-ingredient-product-detail.report.xlsx
+++ b/tools/importer/reports/import-ingredient-product-detail.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1158">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,6 +61,603 @@
     <t>https://www.nzmp.com/global/en.html</t>
   </si>
   <si>
+    <t>global/en/about-nzmp/global-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-category","cards-value","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients</t>
+  </si>
+  <si>
+    <t>category-landing</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:45:38.779Z</t>
+  </si>
+  <si>
+    <t>NZMP's Global Ingredients Network | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/news.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/news</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:31.458Z</t>
+  </si>
+  <si>
+    <t>NZMP Newsfeed: News, Updates &amp; Events | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/news.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/our-way-of-farming.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/our-way-of-farming</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:41.127Z</t>
+  </si>
+  <si>
+    <t>Our Way of Farming | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/our-way-of-farming.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/safety-and-quality.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/safety-and-quality</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:51.860Z</t>
+  </si>
+  <si>
+    <t>NZMP Ingredient Safety &amp; Quality Processes | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/safety-and-quality.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/active-lifestyle.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-feature","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/active-lifestyle</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:01.179Z</t>
+  </si>
+  <si>
+    <t>Active Lifestyle | NZMP Dairy Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/active-lifestyle.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/beverages.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-feature","columns-feature","columns-feature","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/beverages</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:11.096Z</t>
+  </si>
+  <si>
+    <t>Beverages | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/beverages.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/consumer-milk-powders.report.json</t>
+  </si>
+  <si>
+    <t>global/en/applications/consumer-milk-powders</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:19.849Z</t>
+  </si>
+  <si>
+    <t>Consumer Milk Powders | NZMP Dairy Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/consumer-milk-powders.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/food-manufacture.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/food-manufacture</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:30.462Z</t>
+  </si>
+  <si>
+    <t>Food Manufacture | NZMP Dairy Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/food-manufacture.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/medical-nutrition.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-feature","cards-value","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/medical-nutrition</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:39.833Z</t>
+  </si>
+  <si>
+    <t>Medical Nutrition | NZMP Dairy Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/medical-nutrition.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/paediatric-nutrition.report.json</t>
+  </si>
+  <si>
+    <t>global/en/applications/paediatric-nutrition</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:03.662Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/paediatric-nutrition.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/yoghurts-and-cultured-products.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-feature","columns-feature","cards-value","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/yoghurts-and-cultured-products</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:17.092Z</t>
+  </si>
+  <si>
+    <t>Yoghurts and Cultured Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/yoghurts-and-cultured-products.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity.report.json</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:04.268Z</t>
+  </si>
+  <si>
+    <t>Innovation and Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/price-risk-management.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/price-risk-management</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:55:19.165Z</t>
+  </si>
+  <si>
+    <t>Price Risk Management | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/price-risk-management.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/third-party-manufacturing.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/third-party-manufacturing</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:55:26.273Z</t>
+  </si>
+  <si>
+    <t>Third Party Manufacturing | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/third-party-manufacturing.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-australian-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-australian-ingredients</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:45:46.523Z</t>
+  </si>
+  <si>
+    <t>Our Australian Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients/our-australian-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-european-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-european-ingredients</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:45:56.282Z</t>
+  </si>
+  <si>
+    <t>Our European Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients/our-european-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-global-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","cards-category","cards-category","cards-value","cards-value","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-global-ingredients</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:09.109Z</t>
+  </si>
+  <si>
+    <t>Our Global Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients/our-global-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-new-zealand-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-new-zealand-ingredients</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:18.260Z</t>
+  </si>
+  <si>
+    <t>Our New Zealand Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients/our-new-zealand-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-north-american-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-north-american-ingredients</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:24.482Z</t>
+  </si>
+  <si>
+    <t>Our North American Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients/our-north-american-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/organic-dairy/organic-product-claims.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/organic-dairy/organic-product-claims</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:47.471Z</t>
+  </si>
+  <si>
+    <t>Organic Product Claims | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/organic-dairy/organic-product-claims.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/organic-dairy/organic-supply.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/organic-dairy/organic-supply</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:54.925Z</t>
+  </si>
+  <si>
+    <t>Organic Supply | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/organic-dairy/organic-supply.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:24.667Z</t>
+  </si>
+  <si>
+    <t>Cheddar Cheese - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cream-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cream-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:35.558Z</t>
+  </si>
+  <si>
+    <t>Cream Cheese - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cream-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:44.089Z</t>
+  </si>
+  <si>
+    <t>Mozzarella Cheese - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/new-zealand-cheeses.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/new-zealand-cheeses</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:57.621Z</t>
+  </si>
+  <si>
+    <t>Uniquely from New Zealand Cheese - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/new-zealand-cheeses.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:04.959Z</t>
+  </si>
+  <si>
+    <t>Parmesan and Popular cheeses | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/parmesan-and-popular-cheeses.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/repack-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/repack-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:11.863Z</t>
+  </si>
+  <si>
+    <t>Repack Cheese - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/repack-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:20.764Z</t>
+  </si>
+  <si>
+    <t>Anhydrous Milk Fat | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/butter.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/butter</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:27.460Z</t>
+  </si>
+  <si>
+    <t>Butter - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/dairy-fats-cream/butter.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/cream-powder.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/cream-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:34.663Z</t>
+  </si>
+  <si>
+    <t>Cream Powder - Dairy Fats Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/dairy-fats-cream/cream-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/repack-butter.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/repack-butter</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:41.822Z</t>
+  </si>
+  <si>
+    <t>Repack Butter - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/dairy-fats-cream/repack-butter.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/uht-cream.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-category"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/uht-cream</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:47.598Z</t>
+  </si>
+  <si>
+    <t>UHT Cream | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/dairy-fats-cream/uht-cream.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/buttermilk-powder.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/buttermilk-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:54.464Z</t>
+  </si>
+  <si>
+    <t>Buttermilk Powder - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/buttermilk-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/instant-milk-powder.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/instant-milk-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:02.024Z</t>
+  </si>
+  <si>
+    <t>Instant Milk Powder - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/instant-milk-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/lactose.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/lactose</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:08.323Z</t>
+  </si>
+  <si>
+    <t>Lactose - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/lactose.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/powders-concentrates/nzmp-frozen-wholemilk-concentrate.report.json</t>
   </si>
   <si>
@@ -82,288 +679,621 @@
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/nzmp-frozen-wholemilk-concentrate.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:13.822Z</t>
+  </si>
+  <si>
+    <t>Paediatric Grade Powders | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/paediatric-grade-powders.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/skim-milk-powder.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/skim-milk-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:21.160Z</t>
+  </si>
+  <si>
+    <t>Skim Milk Powder - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/skim-milk-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/whey-powder.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/whey-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:28.059Z</t>
+  </si>
+  <si>
+    <t>Whey Powder - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/whey-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/whole-milk-powder.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/whole-milk-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:36.482Z</t>
+  </si>
+  <si>
+    <t>Whole Milk Powder | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/whole-milk-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/caseins-and-caseinates.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/caseins-and-caseinates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:43.522Z</t>
+  </si>
+  <si>
+    <t>Caseins and Caseinates | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/caseins-and-caseinates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/functional-proteins.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/functional-proteins</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:58.239Z</t>
+  </si>
+  <si>
+    <t>Functional Proteins - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/functional-proteins.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/hydrolysates.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/hydrolysates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:04.924Z</t>
+  </si>
+  <si>
+    <t>Hydrolysates - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/hydrolysates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:13.056Z</t>
+  </si>
+  <si>
+    <t>Milk Protein Concentrates - Proteins | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/nzmp-dpc.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/nzmp-dpc</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:10.880Z</t>
+  </si>
+  <si>
+    <t>NZMP CrispBar Dairy Protein Crisp | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/nzmp-dpc.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:18.624Z</t>
+  </si>
+  <si>
+    <t>Whey Protein Concentrates | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-isolates.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-isolates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:48.058Z</t>
+  </si>
+  <si>
+    <t>Whey Protein Isolates | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-isolates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/complex-lipids.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/complex-lipids</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:01.158Z</t>
+  </si>
+  <si>
+    <t>MFGM Complex Lipids | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/complex-lipids.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/hydrolysates.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/hydrolysates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:08.624Z</t>
+  </si>
+  <si>
+    <t>Hydrolysates - Specialty Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/lactoferrin.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/lactoferrin</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:29.630Z</t>
+  </si>
+  <si>
+    <t>Lactoferrin - Speciality Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/lactoferrin.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/lactose.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/lactose</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:37.970Z</t>
+  </si>
+  <si>
+    <t>Lactose - Speciality Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/lactose.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/prebiotics.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/prebiotics</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:45.151Z</t>
+  </si>
+  <si>
+    <t>Prebiotics - Speciality Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/prebiotics.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:12.757Z</t>
+  </si>
+  <si>
+    <t>World-Leading Global Dairy Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-global-expertise.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-protein-expertise.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-value","cards-value","cards-value","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-protein-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:55:04.443Z</t>
+  </si>
+  <si>
+    <t>Our Protein Expertise - Innovation &amp; Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-protein-expertise.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/the-fonterra-research-and-development-centre.report.json</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/the-fonterra-research-and-development-centre</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:55:12.107Z</t>
+  </si>
+  <si>
+    <t>The Fonterra Research and Development Centre | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/the-fonterra-research-and-development-centre.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/third-party-manufacturing/private-label-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/third-party-manufacturing/private-label-solutions</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:55:35.658Z</t>
+  </si>
+  <si>
+    <t>Our Private Label Solutions | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/third-party-manufacturing/private-label-solutions.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-au.report.json</t>
   </si>
   <si>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-au</t>
+  </si>
+  <si>
+    <t>2026-08-14T01:34:19.627Z</t>
+  </si>
+  <si>
+    <t>Cheddar Cheese (Australia Specification) | NZMP Dairy Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-au.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:15:23.694Z</t>
+  </si>
+  <si>
+    <t>Cheddar Cheese Frozen | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-manufacturing.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-manufacturing</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:15:33.759Z</t>
+  </si>
+  <si>
+    <t>Cheddar Cheese for Manufacturing | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-manufacturing.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:15:40.959Z</t>
+  </si>
+  <si>
+    <t>Cheddar Cheese | NZMP Dairy Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:15:49.141Z</t>
+  </si>
+  <si>
+    <t>Coloured Cheddar Cheese | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:15:56.362Z</t>
+  </si>
+  <si>
+    <t>Frozen Functional Cheddar Cheese | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:16:04.559Z</t>
+  </si>
+  <si>
+    <t>Mature Cheddar | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/organic-cheddar-cheese-frozen.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/organic-cheddar-cheese-frozen</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:16:13.023Z</t>
+  </si>
+  <si>
+    <t>Organic Frozen Cheddar Cheese, Reduced Salt  | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/organic-cheddar-cheese-frozen.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:16:20.559Z</t>
+  </si>
+  <si>
+    <t>Organic Mature Cheddar Cheese | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/organic-mild-cheddar-cheese.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/organic-mild-cheddar-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:16:30.171Z</t>
+  </si>
+  <si>
+    <t>Organic Mild Cheddar Cheese | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/organic-mild-cheddar-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","carousel-news"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:16:39.195Z</t>
+  </si>
+  <si>
+    <t>Strong Cheddar Cheese for Manufacturing | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/young-cheddar-cheese-manufacturing-gdt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese/young-cheddar-cheese-manufacturing-gdt</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:16:46.723Z</t>
+  </si>
+  <si>
+    <t>Young Cheddar Cheese for Manufacturing GDT Specification | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/young-cheddar-cheese-manufacturing-gdt.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/easy-shred-mozzarella-nz.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/easy-shred-mozzarella-nz</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:16:55.022Z</t>
+  </si>
+  <si>
+    <t>Easy Shred Mozzarella | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/easy-shred-mozzarella-nz.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/european-mozzarella.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/european-mozzarella</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:51.698Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/european-mozzarella.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/frozen-mozzarella.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/frozen-mozzarella</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:17:04.860Z</t>
+  </si>
+  <si>
+    <t>Frozen Mozzarella | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/frozen-mozzarella.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/iqf-mozzarella.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/iqf-mozzarella</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:17:13.085Z</t>
+  </si>
+  <si>
+    <t>Individually Quick Frozen Mozzarella | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/iqf-mozzarella.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/lower-salt-mozzarella.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/lower-salt-mozzarella</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:17:22.024Z</t>
+  </si>
+  <si>
+    <t>Lower Salt Mozzarella | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/lower-salt-mozzarella.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/medium-fat-mozzarella.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/medium-fat-mozzarella</t>
+  </si>
+  <si>
+    <t>2026-08-13T21:17:32.323Z</t>
+  </si>
+  <si>
+    <t>Medium Fat Mozzarella | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/medium-fat-mozzarella.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-curd.report.json</t>
+  </si>
+  <si>
     <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-au</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:15:15.215Z</t>
-  </si>
-  <si>
-    <t>Cheddar Cheese (Australia Specification) | NZMP Dairy Ingredients | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-au.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen.report.json</t>
-  </si>
-  <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:15:23.694Z</t>
-  </si>
-  <si>
-    <t>Cheddar Cheese Frozen | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-manufacturing.report.json</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-manufacturing</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:15:33.759Z</t>
-  </si>
-  <si>
-    <t>Cheddar Cheese for Manufacturing | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-manufacturing.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese.report.json</t>
-  </si>
-  <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:15:40.959Z</t>
-  </si>
-  <si>
-    <t>Cheddar Cheese | NZMP Dairy Ingredients | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese.report.json</t>
-  </si>
-  <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:15:49.141Z</t>
-  </si>
-  <si>
-    <t>Coloured Cheddar Cheese | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese.report.json</t>
-  </si>
-  <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:15:56.362Z</t>
-  </si>
-  <si>
-    <t>Frozen Functional Cheddar Cheese | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese.report.json</t>
-  </si>
-  <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:16:04.559Z</t>
-  </si>
-  <si>
-    <t>Mature Cheddar | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/organic-cheddar-cheese-frozen.report.json</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/organic-cheddar-cheese-frozen</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:16:13.023Z</t>
-  </si>
-  <si>
-    <t>Organic Frozen Cheddar Cheese, Reduced Salt  | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/organic-cheddar-cheese-frozen.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese.report.json</t>
-  </si>
-  <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:16:20.559Z</t>
-  </si>
-  <si>
-    <t>Organic Mature Cheddar Cheese | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/organic-mild-cheddar-cheese.report.json</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/organic-mild-cheddar-cheese</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:16:30.171Z</t>
-  </si>
-  <si>
-    <t>Organic Mild Cheddar Cheese | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/organic-mild-cheddar-cheese.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing.report.json</t>
-  </si>
-  <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","carousel-news"]</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:16:39.195Z</t>
-  </si>
-  <si>
-    <t>Strong Cheddar Cheese for Manufacturing | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/young-cheddar-cheese-manufacturing-gdt.report.json</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/cheddar-cheese/young-cheddar-cheese-manufacturing-gdt</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:16:46.723Z</t>
-  </si>
-  <si>
-    <t>Young Cheddar Cheese for Manufacturing GDT Specification | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese/young-cheddar-cheese-manufacturing-gdt.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/easy-shred-mozzarella-nz.report.json</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/easy-shred-mozzarella-nz</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:16:55.022Z</t>
-  </si>
-  <si>
-    <t>Easy Shred Mozzarella | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/easy-shred-mozzarella-nz.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/frozen-mozzarella.report.json</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/frozen-mozzarella</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:17:04.860Z</t>
-  </si>
-  <si>
-    <t>Frozen Mozzarella | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/frozen-mozzarella.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/iqf-mozzarella.report.json</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/iqf-mozzarella</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:17:13.085Z</t>
-  </si>
-  <si>
-    <t>Individually Quick Frozen Mozzarella | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/iqf-mozzarella.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/lower-salt-mozzarella.report.json</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/lower-salt-mozzarella</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:17:22.024Z</t>
-  </si>
-  <si>
-    <t>Lower Salt Mozzarella | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/lower-salt-mozzarella.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/medium-fat-mozzarella.report.json</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/medium-fat-mozzarella</t>
-  </si>
-  <si>
-    <t>2026-08-13T21:17:32.323Z</t>
-  </si>
-  <si>
-    <t>Medium Fat Mozzarella | NZMP.com</t>
-  </si>
-  <si>
-    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/medium-fat-mozzarella.html</t>
-  </si>
-  <si>
-    <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-curd.report.json</t>
-  </si>
-  <si>
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-curd</t>
   </si>
   <si>
@@ -1555,6 +2485,30 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-485.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4424-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4424-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:20.860Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4424-yoghurt.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-470-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-470-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:29.757Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-470-yoghurt.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4851.report.json</t>
   </si>
   <si>
@@ -1570,6 +2524,18 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4851.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:35.757Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861-yoghurt.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861.report.json</t>
   </si>
   <si>
@@ -1585,6 +2551,42 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4862-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4862-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:43.260Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4862-yoghurt.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4867.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4867</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:49.341Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4867.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:56.622Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882-yoghurt.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882.report.json</t>
   </si>
   <si>
@@ -1618,6 +2620,18 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4887.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-shortbar-milk-protein-concentrate-4857.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-shortbar-milk-protein-concentrate-4857</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:04.924Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-shortbar-milk-protein-concentrate-4857.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-sureprotein-mpc-4881.report.json</t>
   </si>
   <si>
@@ -1738,6 +2752,18 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flex-wpc-515.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flexbar.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flexbar</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:26.525Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flexbar.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flow-wpc-510.report.json</t>
   </si>
   <si>
@@ -1783,6 +2809,18 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-pro-optima-wpc-567.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-surestart-whey-protein-concentrate-392.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-surestart-whey-protein-concentrate-392</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:34.460Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-surestart-whey-protein-concentrate-392.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-132.report.json</t>
   </si>
   <si>
@@ -1972,6 +3010,18 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-550.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-gelling-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-gelling-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:41.460Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-gelling-yoghurt.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/organic-whey-protein-concentrate-392.report.json</t>
   </si>
   <si>
@@ -2062,6 +3112,18 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-isolates/nzmp-optibar.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-shortbar-825.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-shortbar-825</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:55.259Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-isolates/nzmp-shortbar-825.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-wpi-895.report.json</t>
   </si>
   <si>
@@ -2107,6 +3169,30 @@
     <t>https://www.nzmp.com/global/en/ingredients/specialty/complex-lipids/surestart-mfgm-lipids.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-817.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-817</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:15.653Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-817.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-shortbar-911.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-shortbar-911</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:22.328Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-shortbar-911.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-softbar-917.report.json</t>
   </si>
   <si>
@@ -2164,6 +3250,81 @@
     <t>https://www.nzmp.com/global/en/ingredients/specialty/prebiotics/galacto-oligosaccharide-gos-prebiotic-fibre.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/specialty/prebiotics/surestart-galacto-oligosaccharide-gos.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/prebiotics/surestart-galacto-oligosaccharide-gos</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:52.286Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/prebiotics/surestart-galacto-oligosaccharide-gos.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/china-dairy-expertise.report.json</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/china-dairy-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:22.422Z</t>
+  </si>
+  <si>
+    <t>Our China Dairy Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-global-expertise/china-dairy-expertise.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/europe-dairy-expertise.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/europe-dairy-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:30.887Z</t>
+  </si>
+  <si>
+    <t>Our Europe Dairy Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-global-expertise/europe-dairy-expertise.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/middle-east-africa-dairy-expertise.report.json</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/middle-east-africa-dairy-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:42.257Z</t>
+  </si>
+  <si>
+    <t>Our Middle East &amp; Africa Dairy Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-global-expertise/middle-east-africa-dairy-expertise.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/south-southeast-asia-dairy-expertise.report.json</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/south-southeast-asia-dairy-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:50.940Z</t>
+  </si>
+  <si>
+    <t>Our South &amp; Southeast Asia Dairy Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-global-expertise/south-southeast-asia-dairy-expertise.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/acid-casein-741.report.json</t>
   </si>
   <si>
@@ -2192,6 +3353,18 @@
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-720.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-730.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-730</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:51.273Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-730.html</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/calcium-caseinate-380.report.json</t>
@@ -2700,7 +3873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -2844,10 +4017,10 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -2856,24 +4029,24 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -2882,24 +4055,24 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -2908,21 +4081,21 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
         <v>54</v>
@@ -2974,10 +4147,10 @@
         <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -2986,21 +4159,21 @@
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
         <v>71</v>
@@ -3015,18 +4188,18 @@
         <v>72</v>
       </c>
       <c r="G12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" t="s">
         <v>73</v>
-      </c>
-      <c r="H12" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
         <v>75</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
       </c>
       <c r="C13" t="s">
         <v>76</v>
@@ -3052,10 +4225,10 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
         <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -3064,21 +4237,21 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" t="s">
         <v>83</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>84</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
         <v>86</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
       </c>
       <c r="C15" t="s">
         <v>87</v>
@@ -3104,10 +4277,10 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -3116,24 +4289,24 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -3142,24 +4315,24 @@
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -3168,24 +4341,24 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -3194,24 +4367,24 @@
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G19" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H19" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -3220,24 +4393,24 @@
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -3246,24 +4419,24 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -3272,24 +4445,24 @@
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H22" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -3298,24 +4471,24 @@
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G23" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -3324,24 +4497,24 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G24" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H24" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -3350,24 +4523,24 @@
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G25" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H25" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -3376,24 +4549,24 @@
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G26" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H26" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C27" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -3402,24 +4575,24 @@
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G27" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H27" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -3428,24 +4601,24 @@
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -3454,24 +4627,24 @@
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G29" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H29" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -3480,24 +4653,24 @@
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G30" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H30" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>166</v>
       </c>
       <c r="C31" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -3506,24 +4679,24 @@
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="G31" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H31" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -3532,24 +4705,24 @@
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G32" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H32" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -3558,24 +4731,24 @@
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G33" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="H33" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -3584,24 +4757,24 @@
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G34" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="H34" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="C35" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -3610,24 +4783,24 @@
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="G35" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="H35" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C36" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -3636,24 +4809,24 @@
         <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="G36" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="H36" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -3662,50 +4835,50 @@
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="G37" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H37" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C38" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F38" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="G38" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="H38" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="C39" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -3714,24 +4887,24 @@
         <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="G39" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="H39" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C40" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -3740,24 +4913,24 @@
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="G40" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="H40" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -3766,24 +4939,24 @@
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="G41" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="H41" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>238</v>
+      </c>
+      <c r="B42" t="s">
         <v>223</v>
       </c>
-      <c r="B42" t="s">
-        <v>53</v>
-      </c>
       <c r="C42" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -3792,24 +4965,24 @@
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G42" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="H42" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -3818,24 +4991,24 @@
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="G43" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="H43" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
@@ -3844,24 +5017,24 @@
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="G44" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="H44" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>254</v>
       </c>
       <c r="C45" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -3870,24 +5043,24 @@
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="G45" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="H45" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -3896,24 +5069,24 @@
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="G46" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="H46" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="C47" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -3922,24 +5095,24 @@
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="G47" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="H47" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -3948,24 +5121,24 @@
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="G48" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="H48" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="C49" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -3974,24 +5147,24 @@
         <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="G49" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="H49" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -4000,24 +5173,24 @@
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="G50" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="H50" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>254</v>
       </c>
       <c r="C51" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -4026,24 +5199,24 @@
         <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="G51" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="H51" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>290</v>
       </c>
       <c r="C52" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -4052,24 +5225,24 @@
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="G52" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="H52" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B53" t="s">
-        <v>280</v>
+        <v>166</v>
       </c>
       <c r="C53" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -4078,24 +5251,24 @@
         <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="G53" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="H53" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B54" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="C54" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -4104,24 +5277,24 @@
         <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="G54" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="H54" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>306</v>
       </c>
       <c r="C55" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -4130,24 +5303,24 @@
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="G55" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="H55" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="C56" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -4156,24 +5329,24 @@
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="G56" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="H56" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="C57" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -4182,24 +5355,24 @@
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="G57" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="H57" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B58" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="C58" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -4208,362 +5381,362 @@
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="G58" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="H58" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B59" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="C59" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F59" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="G59" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="H59" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B60" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C60" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F60" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="G60" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="H60" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="B61" t="s">
-        <v>323</v>
+        <v>216</v>
       </c>
       <c r="C61" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F61" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="G61" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="H61" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B62" t="s">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="C62" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F62" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="G62" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="H62" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>352</v>
       </c>
       <c r="C63" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F63" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="G63" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="H63" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C64" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F64" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="G64" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="H64" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>364</v>
       </c>
       <c r="C65" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F65" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="G65" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="H65" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="B66" t="s">
-        <v>53</v>
+        <v>358</v>
       </c>
       <c r="C66" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F66" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="G66" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="H66" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="B67" t="s">
-        <v>41</v>
+        <v>375</v>
       </c>
       <c r="C67" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F67" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="G67" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="H67" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>375</v>
       </c>
       <c r="C68" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F68" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="G68" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="H68" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>386</v>
       </c>
       <c r="C69" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F69" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="G69" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="H69" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>216</v>
       </c>
       <c r="C70" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F70" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="G70" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="H70" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>335</v>
       </c>
       <c r="C71" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F71" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="G71" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="H71" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="B72" t="s">
-        <v>380</v>
+        <v>149</v>
       </c>
       <c r="C72" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
@@ -4572,1963 +5745,3913 @@
         <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="G72" t="s">
-        <v>383</v>
+        <v>152</v>
       </c>
       <c r="H72" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>216</v>
       </c>
       <c r="C73" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F73" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="G73" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="H73" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B74" t="s">
-        <v>380</v>
+        <v>335</v>
       </c>
       <c r="C74" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F74" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="G74" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="H74" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>335</v>
       </c>
       <c r="C75" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F75" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="G75" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="H75" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>375</v>
       </c>
       <c r="C76" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
       </c>
       <c r="E76" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F76" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="G76" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="H76" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>426</v>
       </c>
       <c r="C77" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F77" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="G77" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="H77" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="B78" t="s">
-        <v>311</v>
+        <v>432</v>
       </c>
       <c r="C78" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F78" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="G78" t="s">
-        <v>331</v>
+        <v>435</v>
       </c>
       <c r="H78" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="B79" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C79" t="s">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F79" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="G79" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="H79" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>375</v>
       </c>
       <c r="C80" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
       </c>
       <c r="E80" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F80" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="G80" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="H80" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="B81" t="s">
-        <v>41</v>
+        <v>364</v>
       </c>
       <c r="C81" t="s">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F81" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="G81" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="H81" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="B82" t="s">
-        <v>30</v>
+        <v>335</v>
       </c>
       <c r="C82" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F82" t="s">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="G82" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="H82" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>458</v>
       </c>
       <c r="C83" t="s">
-        <v>434</v>
+        <v>459</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
       </c>
       <c r="E83" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F83" t="s">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="G83" t="s">
-        <v>436</v>
+        <v>461</v>
       </c>
       <c r="H83" t="s">
-        <v>437</v>
+        <v>462</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="B84" t="s">
-        <v>17</v>
+        <v>346</v>
       </c>
       <c r="C84" t="s">
-        <v>439</v>
+        <v>464</v>
       </c>
       <c r="D84" t="s">
         <v>11</v>
       </c>
       <c r="E84" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F84" t="s">
-        <v>440</v>
+        <v>465</v>
       </c>
       <c r="G84" t="s">
-        <v>441</v>
+        <v>466</v>
       </c>
       <c r="H84" t="s">
-        <v>442</v>
+        <v>467</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>443</v>
+        <v>468</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>346</v>
       </c>
       <c r="C85" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F85" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="G85" t="s">
-        <v>446</v>
+        <v>471</v>
       </c>
       <c r="H85" t="s">
-        <v>447</v>
+        <v>472</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>448</v>
+        <v>473</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>426</v>
       </c>
       <c r="C86" t="s">
-        <v>449</v>
+        <v>474</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F86" t="s">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="G86" t="s">
-        <v>451</v>
+        <v>476</v>
       </c>
       <c r="H86" t="s">
-        <v>452</v>
+        <v>477</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="B87" t="s">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="C87" t="s">
-        <v>454</v>
+        <v>479</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F87" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="G87" t="s">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="H87" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C88" t="s">
-        <v>459</v>
+        <v>484</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F88" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="G88" t="s">
-        <v>461</v>
+        <v>486</v>
       </c>
       <c r="H88" t="s">
-        <v>462</v>
+        <v>487</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="B89" t="s">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="C89" t="s">
-        <v>464</v>
+        <v>489</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F89" t="s">
-        <v>465</v>
+        <v>490</v>
       </c>
       <c r="G89" t="s">
-        <v>466</v>
+        <v>491</v>
       </c>
       <c r="H89" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="B90" t="s">
-        <v>469</v>
+        <v>335</v>
       </c>
       <c r="C90" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="D90" t="s">
         <v>11</v>
       </c>
       <c r="E90" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F90" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="G90" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="H90" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>474</v>
+        <v>498</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C91" t="s">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F91" t="s">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="G91" t="s">
-        <v>477</v>
+        <v>501</v>
       </c>
       <c r="H91" t="s">
-        <v>478</v>
+        <v>502</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>479</v>
+        <v>503</v>
       </c>
       <c r="B92" t="s">
-        <v>41</v>
+        <v>216</v>
       </c>
       <c r="C92" t="s">
-        <v>480</v>
+        <v>504</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F92" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="G92" t="s">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="H92" t="s">
-        <v>483</v>
+        <v>507</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>484</v>
+        <v>508</v>
       </c>
       <c r="B93" t="s">
-        <v>485</v>
+        <v>364</v>
       </c>
       <c r="C93" t="s">
-        <v>486</v>
+        <v>509</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F93" t="s">
-        <v>487</v>
+        <v>510</v>
       </c>
       <c r="G93" t="s">
-        <v>488</v>
+        <v>511</v>
       </c>
       <c r="H93" t="s">
-        <v>489</v>
+        <v>512</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>490</v>
+        <v>513</v>
       </c>
       <c r="B94" t="s">
-        <v>491</v>
+        <v>426</v>
       </c>
       <c r="C94" t="s">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="D94" t="s">
         <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F94" t="s">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="G94" t="s">
-        <v>494</v>
+        <v>516</v>
       </c>
       <c r="H94" t="s">
-        <v>495</v>
+        <v>517</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
       <c r="B95" t="s">
-        <v>497</v>
+        <v>386</v>
       </c>
       <c r="C95" t="s">
-        <v>498</v>
+        <v>519</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
       </c>
       <c r="E95" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F95" t="s">
-        <v>499</v>
+        <v>520</v>
       </c>
       <c r="G95" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="H95" t="s">
-        <v>501</v>
+        <v>522</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="B96" t="s">
-        <v>503</v>
+        <v>358</v>
       </c>
       <c r="C96" t="s">
-        <v>504</v>
+        <v>524</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
       </c>
       <c r="E96" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F96" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="G96" t="s">
-        <v>506</v>
+        <v>526</v>
       </c>
       <c r="H96" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>508</v>
+        <v>528</v>
       </c>
       <c r="B97" t="s">
-        <v>509</v>
+        <v>358</v>
       </c>
       <c r="C97" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
       </c>
       <c r="E97" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F97" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="G97" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="H97" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="B98" t="s">
-        <v>503</v>
+        <v>358</v>
       </c>
       <c r="C98" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="D98" t="s">
         <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F98" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="G98" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="H98" t="s">
-        <v>518</v>
+        <v>537</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="B99" t="s">
-        <v>497</v>
+        <v>335</v>
       </c>
       <c r="C99" t="s">
-        <v>520</v>
+        <v>539</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
       </c>
       <c r="E99" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F99" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="G99" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="H99" t="s">
-        <v>523</v>
+        <v>542</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>524</v>
+        <v>543</v>
       </c>
       <c r="B100" t="s">
-        <v>525</v>
+        <v>544</v>
       </c>
       <c r="C100" t="s">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="D100" t="s">
         <v>11</v>
       </c>
       <c r="E100" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F100" t="s">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="G100" t="s">
-        <v>528</v>
+        <v>547</v>
       </c>
       <c r="H100" t="s">
-        <v>529</v>
+        <v>548</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>530</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s">
-        <v>503</v>
+        <v>216</v>
       </c>
       <c r="C101" t="s">
-        <v>531</v>
+        <v>550</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
       </c>
       <c r="E101" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F101" t="s">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="G101" t="s">
-        <v>533</v>
+        <v>552</v>
       </c>
       <c r="H101" t="s">
-        <v>534</v>
+        <v>553</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="B102" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C102" t="s">
-        <v>536</v>
+        <v>555</v>
       </c>
       <c r="D102" t="s">
         <v>11</v>
       </c>
       <c r="E102" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F102" t="s">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c r="G102" t="s">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="H102" t="s">
-        <v>539</v>
+        <v>558</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>540</v>
+        <v>559</v>
       </c>
       <c r="B103" t="s">
-        <v>70</v>
+        <v>216</v>
       </c>
       <c r="C103" t="s">
-        <v>541</v>
+        <v>560</v>
       </c>
       <c r="D103" t="s">
         <v>11</v>
       </c>
       <c r="E103" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F103" t="s">
-        <v>542</v>
+        <v>561</v>
       </c>
       <c r="G103" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="H103" t="s">
-        <v>544</v>
+        <v>563</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="B104" t="s">
-        <v>41</v>
+        <v>346</v>
       </c>
       <c r="C104" t="s">
-        <v>546</v>
+        <v>565</v>
       </c>
       <c r="D104" t="s">
         <v>11</v>
       </c>
       <c r="E104" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F104" t="s">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="G104" t="s">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="H104" t="s">
-        <v>549</v>
+        <v>568</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>550</v>
+        <v>569</v>
       </c>
       <c r="B105" t="s">
-        <v>41</v>
+        <v>346</v>
       </c>
       <c r="C105" t="s">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
       </c>
       <c r="E105" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F105" t="s">
-        <v>552</v>
+        <v>571</v>
       </c>
       <c r="G105" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
       <c r="H105" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="B106" t="s">
-        <v>47</v>
+        <v>335</v>
       </c>
       <c r="C106" t="s">
-        <v>556</v>
+        <v>575</v>
       </c>
       <c r="D106" t="s">
         <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F106" t="s">
-        <v>557</v>
+        <v>576</v>
       </c>
       <c r="G106" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="H106" t="s">
-        <v>559</v>
+        <v>578</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
       <c r="B107" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C107" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
       </c>
       <c r="E107" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F107" t="s">
-        <v>562</v>
+        <v>581</v>
       </c>
       <c r="G107" t="s">
-        <v>563</v>
+        <v>582</v>
       </c>
       <c r="H107" t="s">
-        <v>564</v>
+        <v>583</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>565</v>
+        <v>584</v>
       </c>
       <c r="B108" t="s">
-        <v>503</v>
+        <v>335</v>
       </c>
       <c r="C108" t="s">
-        <v>566</v>
+        <v>585</v>
       </c>
       <c r="D108" t="s">
         <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F108" t="s">
-        <v>567</v>
+        <v>586</v>
       </c>
       <c r="G108" t="s">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="H108" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="B109" t="s">
-        <v>491</v>
+        <v>590</v>
       </c>
       <c r="C109" t="s">
-        <v>571</v>
+        <v>591</v>
       </c>
       <c r="D109" t="s">
         <v>11</v>
       </c>
       <c r="E109" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F109" t="s">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="G109" t="s">
-        <v>573</v>
+        <v>593</v>
       </c>
       <c r="H109" t="s">
-        <v>574</v>
+        <v>594</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>575</v>
+        <v>595</v>
       </c>
       <c r="B110" t="s">
-        <v>485</v>
+        <v>596</v>
       </c>
       <c r="C110" t="s">
-        <v>576</v>
+        <v>597</v>
       </c>
       <c r="D110" t="s">
         <v>11</v>
       </c>
       <c r="E110" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F110" t="s">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="G110" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="H110" t="s">
-        <v>579</v>
+        <v>600</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>580</v>
+        <v>601</v>
       </c>
       <c r="B111" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="C111" t="s">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="D111" t="s">
         <v>11</v>
       </c>
       <c r="E111" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F111" t="s">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="G111" t="s">
-        <v>583</v>
+        <v>604</v>
       </c>
       <c r="H111" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>585</v>
+        <v>606</v>
       </c>
       <c r="B112" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="C112" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="D112" t="s">
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F112" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="G112" t="s">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="H112" t="s">
-        <v>589</v>
+        <v>610</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="B113" t="s">
-        <v>591</v>
+        <v>335</v>
       </c>
       <c r="C113" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="D113" t="s">
         <v>11</v>
       </c>
       <c r="E113" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F113" t="s">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="G113" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="H113" t="s">
-        <v>595</v>
+        <v>615</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>616</v>
+      </c>
+      <c r="B114" t="s">
         <v>596</v>
       </c>
-      <c r="B114" t="s">
-        <v>485</v>
-      </c>
       <c r="C114" t="s">
-        <v>597</v>
+        <v>617</v>
       </c>
       <c r="D114" t="s">
         <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F114" t="s">
-        <v>598</v>
+        <v>618</v>
       </c>
       <c r="G114" t="s">
         <v>599</v>
       </c>
       <c r="H114" t="s">
-        <v>600</v>
+        <v>619</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="B115" t="s">
-        <v>591</v>
+        <v>621</v>
       </c>
       <c r="C115" t="s">
-        <v>602</v>
+        <v>622</v>
       </c>
       <c r="D115" t="s">
         <v>11</v>
       </c>
       <c r="E115" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F115" t="s">
-        <v>603</v>
+        <v>623</v>
       </c>
       <c r="G115" t="s">
-        <v>604</v>
+        <v>624</v>
       </c>
       <c r="H115" t="s">
-        <v>605</v>
+        <v>625</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>606</v>
+        <v>626</v>
       </c>
       <c r="B116" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="C116" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="D116" t="s">
         <v>11</v>
       </c>
       <c r="E116" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F116" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="G116" t="s">
-        <v>610</v>
+        <v>630</v>
       </c>
       <c r="H116" t="s">
-        <v>611</v>
+        <v>631</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="B117" t="s">
-        <v>485</v>
+        <v>633</v>
       </c>
       <c r="C117" t="s">
-        <v>613</v>
+        <v>634</v>
       </c>
       <c r="D117" t="s">
         <v>11</v>
       </c>
       <c r="E117" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F117" t="s">
-        <v>614</v>
+        <v>635</v>
       </c>
       <c r="G117" t="s">
-        <v>615</v>
+        <v>636</v>
       </c>
       <c r="H117" t="s">
-        <v>616</v>
+        <v>637</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>617</v>
+        <v>638</v>
       </c>
       <c r="B118" t="s">
-        <v>497</v>
+        <v>621</v>
       </c>
       <c r="C118" t="s">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="D118" t="s">
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F118" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="G118" t="s">
-        <v>620</v>
+        <v>641</v>
       </c>
       <c r="H118" t="s">
-        <v>621</v>
+        <v>642</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>622</v>
+        <v>643</v>
       </c>
       <c r="B119" t="s">
-        <v>485</v>
+        <v>216</v>
       </c>
       <c r="C119" t="s">
-        <v>623</v>
+        <v>644</v>
       </c>
       <c r="D119" t="s">
         <v>11</v>
       </c>
       <c r="E119" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F119" t="s">
-        <v>624</v>
+        <v>645</v>
       </c>
       <c r="G119" t="s">
-        <v>625</v>
+        <v>646</v>
       </c>
       <c r="H119" t="s">
-        <v>626</v>
+        <v>647</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>627</v>
+        <v>648</v>
       </c>
       <c r="B120" t="s">
-        <v>491</v>
+        <v>649</v>
       </c>
       <c r="C120" t="s">
-        <v>628</v>
+        <v>650</v>
       </c>
       <c r="D120" t="s">
         <v>11</v>
       </c>
       <c r="E120" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F120" t="s">
-        <v>629</v>
+        <v>651</v>
       </c>
       <c r="G120" t="s">
-        <v>630</v>
+        <v>652</v>
       </c>
       <c r="H120" t="s">
-        <v>631</v>
+        <v>653</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>632</v>
+        <v>654</v>
       </c>
       <c r="B121" t="s">
-        <v>591</v>
+        <v>335</v>
       </c>
       <c r="C121" t="s">
-        <v>633</v>
+        <v>655</v>
       </c>
       <c r="D121" t="s">
         <v>11</v>
       </c>
       <c r="E121" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F121" t="s">
-        <v>634</v>
+        <v>656</v>
       </c>
       <c r="G121" t="s">
-        <v>635</v>
+        <v>657</v>
       </c>
       <c r="H121" t="s">
-        <v>636</v>
+        <v>658</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>637</v>
+        <v>659</v>
       </c>
       <c r="B122" t="s">
-        <v>485</v>
+        <v>358</v>
       </c>
       <c r="C122" t="s">
-        <v>638</v>
+        <v>660</v>
       </c>
       <c r="D122" t="s">
         <v>11</v>
       </c>
       <c r="E122" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F122" t="s">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="G122" t="s">
-        <v>640</v>
+        <v>662</v>
       </c>
       <c r="H122" t="s">
-        <v>641</v>
+        <v>663</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>642</v>
+        <v>664</v>
       </c>
       <c r="B123" t="s">
-        <v>591</v>
+        <v>346</v>
       </c>
       <c r="C123" t="s">
-        <v>643</v>
+        <v>665</v>
       </c>
       <c r="D123" t="s">
         <v>11</v>
       </c>
       <c r="E123" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F123" t="s">
-        <v>644</v>
+        <v>666</v>
       </c>
       <c r="G123" t="s">
-        <v>645</v>
+        <v>667</v>
       </c>
       <c r="H123" t="s">
-        <v>646</v>
+        <v>668</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>647</v>
+        <v>669</v>
       </c>
       <c r="B124" t="s">
-        <v>648</v>
+        <v>426</v>
       </c>
       <c r="C124" t="s">
-        <v>649</v>
+        <v>670</v>
       </c>
       <c r="D124" t="s">
         <v>11</v>
       </c>
       <c r="E124" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F124" t="s">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="G124" t="s">
-        <v>651</v>
+        <v>672</v>
       </c>
       <c r="H124" t="s">
-        <v>652</v>
+        <v>673</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>653</v>
+        <v>674</v>
       </c>
       <c r="B125" t="s">
-        <v>17</v>
+        <v>335</v>
       </c>
       <c r="C125" t="s">
-        <v>654</v>
+        <v>675</v>
       </c>
       <c r="D125" t="s">
         <v>11</v>
       </c>
       <c r="E125" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F125" t="s">
-        <v>655</v>
+        <v>676</v>
       </c>
       <c r="G125" t="s">
-        <v>656</v>
+        <v>677</v>
       </c>
       <c r="H125" t="s">
-        <v>657</v>
+        <v>678</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>658</v>
+        <v>679</v>
       </c>
       <c r="B126" t="s">
-        <v>469</v>
+        <v>335</v>
       </c>
       <c r="C126" t="s">
-        <v>659</v>
+        <v>680</v>
       </c>
       <c r="D126" t="s">
         <v>11</v>
       </c>
       <c r="E126" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F126" t="s">
-        <v>660</v>
+        <v>681</v>
       </c>
       <c r="G126" t="s">
-        <v>661</v>
+        <v>682</v>
       </c>
       <c r="H126" t="s">
-        <v>662</v>
+        <v>683</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>663</v>
+        <v>684</v>
       </c>
       <c r="B127" t="s">
-        <v>503</v>
+        <v>335</v>
       </c>
       <c r="C127" t="s">
-        <v>664</v>
+        <v>685</v>
       </c>
       <c r="D127" t="s">
         <v>11</v>
       </c>
       <c r="E127" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F127" t="s">
-        <v>665</v>
+        <v>686</v>
       </c>
       <c r="G127" t="s">
-        <v>666</v>
+        <v>687</v>
       </c>
       <c r="H127" t="s">
-        <v>667</v>
+        <v>688</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>668</v>
+        <v>689</v>
       </c>
       <c r="B128" t="s">
-        <v>485</v>
+        <v>690</v>
       </c>
       <c r="C128" t="s">
-        <v>669</v>
+        <v>691</v>
       </c>
       <c r="D128" t="s">
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F128" t="s">
-        <v>670</v>
+        <v>692</v>
       </c>
       <c r="G128" t="s">
-        <v>671</v>
+        <v>693</v>
       </c>
       <c r="H128" t="s">
-        <v>672</v>
+        <v>694</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>673</v>
+        <v>695</v>
       </c>
       <c r="B129" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="C129" t="s">
-        <v>674</v>
+        <v>696</v>
       </c>
       <c r="D129" t="s">
         <v>11</v>
       </c>
       <c r="E129" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F129" t="s">
-        <v>675</v>
+        <v>697</v>
       </c>
       <c r="G129" t="s">
-        <v>676</v>
+        <v>698</v>
       </c>
       <c r="H129" t="s">
-        <v>677</v>
+        <v>699</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>678</v>
+        <v>700</v>
       </c>
       <c r="B130" t="s">
-        <v>485</v>
+        <v>690</v>
       </c>
       <c r="C130" t="s">
-        <v>679</v>
+        <v>701</v>
       </c>
       <c r="D130" t="s">
         <v>11</v>
       </c>
       <c r="E130" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F130" t="s">
-        <v>680</v>
+        <v>702</v>
       </c>
       <c r="G130" t="s">
-        <v>681</v>
+        <v>703</v>
       </c>
       <c r="H130" t="s">
-        <v>682</v>
+        <v>704</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>683</v>
+        <v>705</v>
       </c>
       <c r="B131" t="s">
-        <v>491</v>
+        <v>375</v>
       </c>
       <c r="C131" t="s">
-        <v>684</v>
+        <v>706</v>
       </c>
       <c r="D131" t="s">
         <v>11</v>
       </c>
       <c r="E131" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F131" t="s">
-        <v>685</v>
+        <v>707</v>
       </c>
       <c r="G131" t="s">
-        <v>686</v>
+        <v>708</v>
       </c>
       <c r="H131" t="s">
-        <v>687</v>
+        <v>709</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="B132" t="s">
-        <v>311</v>
+        <v>426</v>
       </c>
       <c r="C132" t="s">
-        <v>689</v>
+        <v>711</v>
       </c>
       <c r="D132" t="s">
         <v>11</v>
       </c>
       <c r="E132" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F132" t="s">
-        <v>690</v>
+        <v>712</v>
       </c>
       <c r="G132" t="s">
-        <v>691</v>
+        <v>713</v>
       </c>
       <c r="H132" t="s">
-        <v>692</v>
+        <v>714</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>693</v>
+        <v>715</v>
       </c>
       <c r="B133" t="s">
-        <v>380</v>
+        <v>426</v>
       </c>
       <c r="C133" t="s">
-        <v>694</v>
+        <v>716</v>
       </c>
       <c r="D133" t="s">
         <v>11</v>
       </c>
       <c r="E133" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F133" t="s">
-        <v>695</v>
+        <v>717</v>
       </c>
       <c r="G133" t="s">
-        <v>696</v>
+        <v>713</v>
       </c>
       <c r="H133" t="s">
-        <v>697</v>
+        <v>718</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>698</v>
+        <v>719</v>
       </c>
       <c r="B134" t="s">
-        <v>497</v>
+        <v>621</v>
       </c>
       <c r="C134" t="s">
-        <v>699</v>
+        <v>720</v>
       </c>
       <c r="D134" t="s">
         <v>11</v>
       </c>
       <c r="E134" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F134" t="s">
-        <v>700</v>
+        <v>721</v>
       </c>
       <c r="G134" t="s">
-        <v>500</v>
+        <v>641</v>
       </c>
       <c r="H134" t="s">
-        <v>701</v>
+        <v>722</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>702</v>
+        <v>723</v>
       </c>
       <c r="B135" t="s">
-        <v>469</v>
+        <v>649</v>
       </c>
       <c r="C135" t="s">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
       </c>
       <c r="E135" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F135" t="s">
-        <v>704</v>
+        <v>725</v>
       </c>
       <c r="G135" t="s">
-        <v>661</v>
+        <v>726</v>
       </c>
       <c r="H135" t="s">
-        <v>705</v>
+        <v>727</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>706</v>
+        <v>728</v>
       </c>
       <c r="B136" t="s">
-        <v>17</v>
+        <v>426</v>
       </c>
       <c r="C136" t="s">
-        <v>707</v>
+        <v>729</v>
       </c>
       <c r="D136" t="s">
         <v>11</v>
       </c>
       <c r="E136" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F136" t="s">
-        <v>708</v>
+        <v>730</v>
       </c>
       <c r="G136" t="s">
-        <v>709</v>
+        <v>731</v>
       </c>
       <c r="H136" t="s">
-        <v>710</v>
+        <v>732</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>711</v>
+        <v>733</v>
       </c>
       <c r="B137" t="s">
-        <v>712</v>
+        <v>346</v>
       </c>
       <c r="C137" t="s">
-        <v>713</v>
+        <v>734</v>
       </c>
       <c r="D137" t="s">
         <v>11</v>
       </c>
       <c r="E137" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F137" t="s">
-        <v>714</v>
+        <v>735</v>
       </c>
       <c r="G137" t="s">
-        <v>715</v>
+        <v>736</v>
       </c>
       <c r="H137" t="s">
-        <v>716</v>
+        <v>737</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>717</v>
+        <v>738</v>
       </c>
       <c r="B138" t="s">
-        <v>503</v>
+        <v>335</v>
       </c>
       <c r="C138" t="s">
-        <v>718</v>
+        <v>739</v>
       </c>
       <c r="D138" t="s">
         <v>11</v>
       </c>
       <c r="E138" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F138" t="s">
-        <v>719</v>
+        <v>740</v>
       </c>
       <c r="G138" t="s">
-        <v>720</v>
+        <v>741</v>
       </c>
       <c r="H138" t="s">
-        <v>721</v>
+        <v>742</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>722</v>
+        <v>743</v>
       </c>
       <c r="B139" t="s">
-        <v>503</v>
+        <v>335</v>
       </c>
       <c r="C139" t="s">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="D139" t="s">
         <v>11</v>
       </c>
       <c r="E139" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F139" t="s">
-        <v>724</v>
+        <v>745</v>
       </c>
       <c r="G139" t="s">
-        <v>725</v>
+        <v>746</v>
       </c>
       <c r="H139" t="s">
-        <v>726</v>
+        <v>747</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>727</v>
+        <v>748</v>
       </c>
       <c r="B140" t="s">
-        <v>525</v>
+        <v>216</v>
       </c>
       <c r="C140" t="s">
-        <v>728</v>
+        <v>749</v>
       </c>
       <c r="D140" t="s">
         <v>11</v>
       </c>
       <c r="E140" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F140" t="s">
-        <v>729</v>
+        <v>750</v>
       </c>
       <c r="G140" t="s">
-        <v>730</v>
+        <v>751</v>
       </c>
       <c r="H140" t="s">
-        <v>731</v>
+        <v>752</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>732</v>
+        <v>753</v>
       </c>
       <c r="B141" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="C141" t="s">
-        <v>733</v>
+        <v>754</v>
       </c>
       <c r="D141" t="s">
         <v>11</v>
       </c>
       <c r="E141" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F141" t="s">
-        <v>734</v>
+        <v>755</v>
       </c>
       <c r="G141" t="s">
-        <v>735</v>
+        <v>756</v>
       </c>
       <c r="H141" t="s">
-        <v>736</v>
+        <v>757</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>737</v>
+        <v>758</v>
       </c>
       <c r="B142" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="C142" t="s">
-        <v>738</v>
+        <v>759</v>
       </c>
       <c r="D142" t="s">
         <v>11</v>
       </c>
       <c r="E142" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F142" t="s">
-        <v>739</v>
+        <v>760</v>
       </c>
       <c r="G142" t="s">
-        <v>740</v>
+        <v>761</v>
       </c>
       <c r="H142" t="s">
-        <v>741</v>
+        <v>762</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>742</v>
+        <v>763</v>
       </c>
       <c r="B143" t="s">
-        <v>591</v>
+        <v>627</v>
       </c>
       <c r="C143" t="s">
-        <v>743</v>
+        <v>764</v>
       </c>
       <c r="D143" t="s">
         <v>11</v>
       </c>
       <c r="E143" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F143" t="s">
-        <v>744</v>
+        <v>765</v>
       </c>
       <c r="G143" t="s">
-        <v>745</v>
+        <v>766</v>
       </c>
       <c r="H143" t="s">
-        <v>746</v>
+        <v>767</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>747</v>
+        <v>768</v>
       </c>
       <c r="B144" t="s">
-        <v>591</v>
+        <v>426</v>
       </c>
       <c r="C144" t="s">
-        <v>748</v>
+        <v>769</v>
       </c>
       <c r="D144" t="s">
         <v>11</v>
       </c>
       <c r="E144" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F144" t="s">
-        <v>749</v>
+        <v>770</v>
       </c>
       <c r="G144" t="s">
-        <v>750</v>
+        <v>771</v>
       </c>
       <c r="H144" t="s">
-        <v>751</v>
+        <v>772</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>752</v>
+        <v>773</v>
       </c>
       <c r="B145" t="s">
-        <v>485</v>
+        <v>216</v>
       </c>
       <c r="C145" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="D145" t="s">
         <v>11</v>
       </c>
       <c r="E145" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F145" t="s">
-        <v>754</v>
+        <v>775</v>
       </c>
       <c r="G145" t="s">
-        <v>755</v>
+        <v>776</v>
       </c>
       <c r="H145" t="s">
-        <v>756</v>
+        <v>777</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>757</v>
+        <v>778</v>
       </c>
       <c r="B146" t="s">
-        <v>148</v>
+        <v>779</v>
       </c>
       <c r="C146" t="s">
-        <v>758</v>
+        <v>780</v>
       </c>
       <c r="D146" t="s">
         <v>11</v>
       </c>
       <c r="E146" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F146" t="s">
-        <v>759</v>
+        <v>781</v>
       </c>
       <c r="G146" t="s">
-        <v>760</v>
+        <v>782</v>
       </c>
       <c r="H146" t="s">
-        <v>761</v>
+        <v>783</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>762</v>
+        <v>784</v>
       </c>
       <c r="B147" t="s">
-        <v>148</v>
+        <v>426</v>
       </c>
       <c r="C147" t="s">
-        <v>763</v>
+        <v>785</v>
       </c>
       <c r="D147" t="s">
         <v>11</v>
       </c>
       <c r="E147" t="s">
+        <v>218</v>
+      </c>
+      <c r="F147" t="s">
+        <v>786</v>
+      </c>
+      <c r="G147" t="s">
+        <v>787</v>
+      </c>
+      <c r="H147" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>789</v>
+      </c>
+      <c r="B148" t="s">
+        <v>346</v>
+      </c>
+      <c r="C148" t="s">
+        <v>790</v>
+      </c>
+      <c r="D148" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" t="s">
+        <v>218</v>
+      </c>
+      <c r="F148" t="s">
+        <v>791</v>
+      </c>
+      <c r="G148" t="s">
+        <v>792</v>
+      </c>
+      <c r="H148" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>794</v>
+      </c>
+      <c r="B149" t="s">
+        <v>795</v>
+      </c>
+      <c r="C149" t="s">
+        <v>796</v>
+      </c>
+      <c r="D149" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" t="s">
+        <v>218</v>
+      </c>
+      <c r="F149" t="s">
+        <v>797</v>
+      </c>
+      <c r="G149" t="s">
+        <v>798</v>
+      </c>
+      <c r="H149" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>800</v>
+      </c>
+      <c r="B150" t="s">
+        <v>801</v>
+      </c>
+      <c r="C150" t="s">
+        <v>802</v>
+      </c>
+      <c r="D150" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" t="s">
+        <v>218</v>
+      </c>
+      <c r="F150" t="s">
+        <v>803</v>
+      </c>
+      <c r="G150" t="s">
+        <v>804</v>
+      </c>
+      <c r="H150" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>806</v>
+      </c>
+      <c r="B151" t="s">
+        <v>807</v>
+      </c>
+      <c r="C151" t="s">
+        <v>808</v>
+      </c>
+      <c r="D151" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" t="s">
+        <v>218</v>
+      </c>
+      <c r="F151" t="s">
+        <v>809</v>
+      </c>
+      <c r="G151" t="s">
+        <v>810</v>
+      </c>
+      <c r="H151" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>812</v>
+      </c>
+      <c r="B152" t="s">
+        <v>813</v>
+      </c>
+      <c r="C152" t="s">
+        <v>814</v>
+      </c>
+      <c r="D152" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" t="s">
+        <v>218</v>
+      </c>
+      <c r="F152" t="s">
+        <v>815</v>
+      </c>
+      <c r="G152" t="s">
+        <v>816</v>
+      </c>
+      <c r="H152" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>818</v>
+      </c>
+      <c r="B153" t="s">
+        <v>819</v>
+      </c>
+      <c r="C153" t="s">
+        <v>820</v>
+      </c>
+      <c r="D153" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" t="s">
+        <v>218</v>
+      </c>
+      <c r="F153" t="s">
+        <v>821</v>
+      </c>
+      <c r="G153" t="s">
+        <v>822</v>
+      </c>
+      <c r="H153" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>824</v>
+      </c>
+      <c r="B154" t="s">
+        <v>137</v>
+      </c>
+      <c r="C154" t="s">
+        <v>825</v>
+      </c>
+      <c r="D154" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" t="s">
         <v>19</v>
       </c>
-      <c r="F147" t="s">
-        <v>764</v>
-      </c>
-      <c r="G147" t="s">
-        <v>765</v>
-      </c>
-      <c r="H147" t="s">
-        <v>766</v>
+      <c r="F154" t="s">
+        <v>826</v>
+      </c>
+      <c r="G154" t="s">
+        <v>262</v>
+      </c>
+      <c r="H154" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>828</v>
+      </c>
+      <c r="B155" t="s">
+        <v>137</v>
+      </c>
+      <c r="C155" t="s">
+        <v>829</v>
+      </c>
+      <c r="D155" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" t="s">
+        <v>19</v>
+      </c>
+      <c r="F155" t="s">
+        <v>830</v>
+      </c>
+      <c r="G155" t="s">
+        <v>262</v>
+      </c>
+      <c r="H155" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>832</v>
+      </c>
+      <c r="B156" t="s">
+        <v>813</v>
+      </c>
+      <c r="C156" t="s">
+        <v>833</v>
+      </c>
+      <c r="D156" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" t="s">
+        <v>218</v>
+      </c>
+      <c r="F156" t="s">
+        <v>834</v>
+      </c>
+      <c r="G156" t="s">
+        <v>835</v>
+      </c>
+      <c r="H156" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>837</v>
+      </c>
+      <c r="B157" t="s">
+        <v>137</v>
+      </c>
+      <c r="C157" t="s">
+        <v>838</v>
+      </c>
+      <c r="D157" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" t="s">
+        <v>19</v>
+      </c>
+      <c r="F157" t="s">
+        <v>839</v>
+      </c>
+      <c r="G157" t="s">
+        <v>262</v>
+      </c>
+      <c r="H157" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>841</v>
+      </c>
+      <c r="B158" t="s">
+        <v>807</v>
+      </c>
+      <c r="C158" t="s">
+        <v>842</v>
+      </c>
+      <c r="D158" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" t="s">
+        <v>218</v>
+      </c>
+      <c r="F158" t="s">
+        <v>843</v>
+      </c>
+      <c r="G158" t="s">
+        <v>844</v>
+      </c>
+      <c r="H158" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>846</v>
+      </c>
+      <c r="B159" t="s">
+        <v>137</v>
+      </c>
+      <c r="C159" t="s">
+        <v>847</v>
+      </c>
+      <c r="D159" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" t="s">
+        <v>19</v>
+      </c>
+      <c r="F159" t="s">
+        <v>848</v>
+      </c>
+      <c r="G159" t="s">
+        <v>262</v>
+      </c>
+      <c r="H159" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>850</v>
+      </c>
+      <c r="B160" t="s">
+        <v>137</v>
+      </c>
+      <c r="C160" t="s">
+        <v>851</v>
+      </c>
+      <c r="D160" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" t="s">
+        <v>19</v>
+      </c>
+      <c r="F160" t="s">
+        <v>852</v>
+      </c>
+      <c r="G160" t="s">
+        <v>262</v>
+      </c>
+      <c r="H160" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>854</v>
+      </c>
+      <c r="B161" t="s">
+        <v>137</v>
+      </c>
+      <c r="C161" t="s">
+        <v>855</v>
+      </c>
+      <c r="D161" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" t="s">
+        <v>19</v>
+      </c>
+      <c r="F161" t="s">
+        <v>856</v>
+      </c>
+      <c r="G161" t="s">
+        <v>262</v>
+      </c>
+      <c r="H161" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>858</v>
+      </c>
+      <c r="B162" t="s">
+        <v>859</v>
+      </c>
+      <c r="C162" t="s">
+        <v>860</v>
+      </c>
+      <c r="D162" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" t="s">
+        <v>218</v>
+      </c>
+      <c r="F162" t="s">
+        <v>861</v>
+      </c>
+      <c r="G162" t="s">
+        <v>862</v>
+      </c>
+      <c r="H162" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>864</v>
+      </c>
+      <c r="B163" t="s">
+        <v>813</v>
+      </c>
+      <c r="C163" t="s">
+        <v>865</v>
+      </c>
+      <c r="D163" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" t="s">
+        <v>218</v>
+      </c>
+      <c r="F163" t="s">
+        <v>866</v>
+      </c>
+      <c r="G163" t="s">
+        <v>867</v>
+      </c>
+      <c r="H163" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>869</v>
+      </c>
+      <c r="B164" t="s">
+        <v>137</v>
+      </c>
+      <c r="C164" t="s">
+        <v>870</v>
+      </c>
+      <c r="D164" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" t="s">
+        <v>19</v>
+      </c>
+      <c r="F164" t="s">
+        <v>871</v>
+      </c>
+      <c r="G164" t="s">
+        <v>262</v>
+      </c>
+      <c r="H164" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>873</v>
+      </c>
+      <c r="B165" t="s">
+        <v>649</v>
+      </c>
+      <c r="C165" t="s">
+        <v>874</v>
+      </c>
+      <c r="D165" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" t="s">
+        <v>218</v>
+      </c>
+      <c r="F165" t="s">
+        <v>875</v>
+      </c>
+      <c r="G165" t="s">
+        <v>876</v>
+      </c>
+      <c r="H165" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>878</v>
+      </c>
+      <c r="B166" t="s">
+        <v>375</v>
+      </c>
+      <c r="C166" t="s">
+        <v>879</v>
+      </c>
+      <c r="D166" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" t="s">
+        <v>218</v>
+      </c>
+      <c r="F166" t="s">
+        <v>880</v>
+      </c>
+      <c r="G166" t="s">
+        <v>881</v>
+      </c>
+      <c r="H166" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>883</v>
+      </c>
+      <c r="B167" t="s">
+        <v>346</v>
+      </c>
+      <c r="C167" t="s">
+        <v>884</v>
+      </c>
+      <c r="D167" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" t="s">
+        <v>218</v>
+      </c>
+      <c r="F167" t="s">
+        <v>885</v>
+      </c>
+      <c r="G167" t="s">
+        <v>886</v>
+      </c>
+      <c r="H167" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>888</v>
+      </c>
+      <c r="B168" t="s">
+        <v>346</v>
+      </c>
+      <c r="C168" t="s">
+        <v>889</v>
+      </c>
+      <c r="D168" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" t="s">
+        <v>218</v>
+      </c>
+      <c r="F168" t="s">
+        <v>890</v>
+      </c>
+      <c r="G168" t="s">
+        <v>891</v>
+      </c>
+      <c r="H168" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>893</v>
+      </c>
+      <c r="B169" t="s">
+        <v>352</v>
+      </c>
+      <c r="C169" t="s">
+        <v>894</v>
+      </c>
+      <c r="D169" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" t="s">
+        <v>218</v>
+      </c>
+      <c r="F169" t="s">
+        <v>895</v>
+      </c>
+      <c r="G169" t="s">
+        <v>896</v>
+      </c>
+      <c r="H169" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>898</v>
+      </c>
+      <c r="B170" t="s">
+        <v>649</v>
+      </c>
+      <c r="C170" t="s">
+        <v>899</v>
+      </c>
+      <c r="D170" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" t="s">
+        <v>218</v>
+      </c>
+      <c r="F170" t="s">
+        <v>900</v>
+      </c>
+      <c r="G170" t="s">
+        <v>901</v>
+      </c>
+      <c r="H170" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>903</v>
+      </c>
+      <c r="B171" t="s">
+        <v>813</v>
+      </c>
+      <c r="C171" t="s">
+        <v>904</v>
+      </c>
+      <c r="D171" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" t="s">
+        <v>218</v>
+      </c>
+      <c r="F171" t="s">
+        <v>905</v>
+      </c>
+      <c r="G171" t="s">
+        <v>906</v>
+      </c>
+      <c r="H171" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>908</v>
+      </c>
+      <c r="B172" t="s">
+        <v>801</v>
+      </c>
+      <c r="C172" t="s">
+        <v>909</v>
+      </c>
+      <c r="D172" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" t="s">
+        <v>218</v>
+      </c>
+      <c r="F172" t="s">
+        <v>910</v>
+      </c>
+      <c r="G172" t="s">
+        <v>911</v>
+      </c>
+      <c r="H172" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>913</v>
+      </c>
+      <c r="B173" t="s">
+        <v>223</v>
+      </c>
+      <c r="C173" t="s">
+        <v>914</v>
+      </c>
+      <c r="D173" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" t="s">
+        <v>19</v>
+      </c>
+      <c r="F173" t="s">
+        <v>915</v>
+      </c>
+      <c r="G173" t="s">
+        <v>272</v>
+      </c>
+      <c r="H173" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>917</v>
+      </c>
+      <c r="B174" t="s">
+        <v>795</v>
+      </c>
+      <c r="C174" t="s">
+        <v>918</v>
+      </c>
+      <c r="D174" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" t="s">
+        <v>218</v>
+      </c>
+      <c r="F174" t="s">
+        <v>919</v>
+      </c>
+      <c r="G174" t="s">
+        <v>920</v>
+      </c>
+      <c r="H174" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>922</v>
+      </c>
+      <c r="B175" t="s">
+        <v>795</v>
+      </c>
+      <c r="C175" t="s">
+        <v>923</v>
+      </c>
+      <c r="D175" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" t="s">
+        <v>218</v>
+      </c>
+      <c r="F175" t="s">
+        <v>924</v>
+      </c>
+      <c r="G175" t="s">
+        <v>925</v>
+      </c>
+      <c r="H175" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>927</v>
+      </c>
+      <c r="B176" t="s">
+        <v>795</v>
+      </c>
+      <c r="C176" t="s">
+        <v>928</v>
+      </c>
+      <c r="D176" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" t="s">
+        <v>218</v>
+      </c>
+      <c r="F176" t="s">
+        <v>929</v>
+      </c>
+      <c r="G176" t="s">
+        <v>930</v>
+      </c>
+      <c r="H176" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>932</v>
+      </c>
+      <c r="B177" t="s">
+        <v>223</v>
+      </c>
+      <c r="C177" t="s">
+        <v>933</v>
+      </c>
+      <c r="D177" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" t="s">
+        <v>19</v>
+      </c>
+      <c r="F177" t="s">
+        <v>934</v>
+      </c>
+      <c r="G177" t="s">
+        <v>272</v>
+      </c>
+      <c r="H177" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>936</v>
+      </c>
+      <c r="B178" t="s">
+        <v>937</v>
+      </c>
+      <c r="C178" t="s">
+        <v>938</v>
+      </c>
+      <c r="D178" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" t="s">
+        <v>218</v>
+      </c>
+      <c r="F178" t="s">
+        <v>939</v>
+      </c>
+      <c r="G178" t="s">
+        <v>940</v>
+      </c>
+      <c r="H178" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>942</v>
+      </c>
+      <c r="B179" t="s">
+        <v>795</v>
+      </c>
+      <c r="C179" t="s">
+        <v>943</v>
+      </c>
+      <c r="D179" t="s">
+        <v>11</v>
+      </c>
+      <c r="E179" t="s">
+        <v>218</v>
+      </c>
+      <c r="F179" t="s">
+        <v>944</v>
+      </c>
+      <c r="G179" t="s">
+        <v>945</v>
+      </c>
+      <c r="H179" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>947</v>
+      </c>
+      <c r="B180" t="s">
+        <v>937</v>
+      </c>
+      <c r="C180" t="s">
+        <v>948</v>
+      </c>
+      <c r="D180" t="s">
+        <v>11</v>
+      </c>
+      <c r="E180" t="s">
+        <v>218</v>
+      </c>
+      <c r="F180" t="s">
+        <v>949</v>
+      </c>
+      <c r="G180" t="s">
+        <v>950</v>
+      </c>
+      <c r="H180" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>952</v>
+      </c>
+      <c r="B181" t="s">
+        <v>953</v>
+      </c>
+      <c r="C181" t="s">
+        <v>954</v>
+      </c>
+      <c r="D181" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" t="s">
+        <v>218</v>
+      </c>
+      <c r="F181" t="s">
+        <v>955</v>
+      </c>
+      <c r="G181" t="s">
+        <v>956</v>
+      </c>
+      <c r="H181" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>958</v>
+      </c>
+      <c r="B182" t="s">
+        <v>795</v>
+      </c>
+      <c r="C182" t="s">
+        <v>959</v>
+      </c>
+      <c r="D182" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" t="s">
+        <v>218</v>
+      </c>
+      <c r="F182" t="s">
+        <v>960</v>
+      </c>
+      <c r="G182" t="s">
+        <v>961</v>
+      </c>
+      <c r="H182" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>963</v>
+      </c>
+      <c r="B183" t="s">
+        <v>807</v>
+      </c>
+      <c r="C183" t="s">
+        <v>964</v>
+      </c>
+      <c r="D183" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" t="s">
+        <v>218</v>
+      </c>
+      <c r="F183" t="s">
+        <v>965</v>
+      </c>
+      <c r="G183" t="s">
+        <v>966</v>
+      </c>
+      <c r="H183" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>968</v>
+      </c>
+      <c r="B184" t="s">
+        <v>795</v>
+      </c>
+      <c r="C184" t="s">
+        <v>969</v>
+      </c>
+      <c r="D184" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" t="s">
+        <v>218</v>
+      </c>
+      <c r="F184" t="s">
+        <v>970</v>
+      </c>
+      <c r="G184" t="s">
+        <v>971</v>
+      </c>
+      <c r="H184" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>973</v>
+      </c>
+      <c r="B185" t="s">
+        <v>801</v>
+      </c>
+      <c r="C185" t="s">
+        <v>974</v>
+      </c>
+      <c r="D185" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" t="s">
+        <v>218</v>
+      </c>
+      <c r="F185" t="s">
+        <v>975</v>
+      </c>
+      <c r="G185" t="s">
+        <v>976</v>
+      </c>
+      <c r="H185" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>978</v>
+      </c>
+      <c r="B186" t="s">
+        <v>937</v>
+      </c>
+      <c r="C186" t="s">
+        <v>979</v>
+      </c>
+      <c r="D186" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" t="s">
+        <v>218</v>
+      </c>
+      <c r="F186" t="s">
+        <v>980</v>
+      </c>
+      <c r="G186" t="s">
+        <v>981</v>
+      </c>
+      <c r="H186" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>983</v>
+      </c>
+      <c r="B187" t="s">
+        <v>795</v>
+      </c>
+      <c r="C187" t="s">
+        <v>984</v>
+      </c>
+      <c r="D187" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" t="s">
+        <v>218</v>
+      </c>
+      <c r="F187" t="s">
+        <v>985</v>
+      </c>
+      <c r="G187" t="s">
+        <v>986</v>
+      </c>
+      <c r="H187" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>988</v>
+      </c>
+      <c r="B188" t="s">
+        <v>937</v>
+      </c>
+      <c r="C188" t="s">
+        <v>989</v>
+      </c>
+      <c r="D188" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" t="s">
+        <v>218</v>
+      </c>
+      <c r="F188" t="s">
+        <v>990</v>
+      </c>
+      <c r="G188" t="s">
+        <v>991</v>
+      </c>
+      <c r="H188" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>993</v>
+      </c>
+      <c r="B189" t="s">
+        <v>994</v>
+      </c>
+      <c r="C189" t="s">
+        <v>995</v>
+      </c>
+      <c r="D189" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" t="s">
+        <v>218</v>
+      </c>
+      <c r="F189" t="s">
+        <v>996</v>
+      </c>
+      <c r="G189" t="s">
+        <v>997</v>
+      </c>
+      <c r="H189" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>999</v>
+      </c>
+      <c r="B190" t="s">
+        <v>223</v>
+      </c>
+      <c r="C190" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D190" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" t="s">
+        <v>19</v>
+      </c>
+      <c r="F190" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G190" t="s">
+        <v>272</v>
+      </c>
+      <c r="H190" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B191" t="s">
+        <v>216</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D191" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" t="s">
+        <v>218</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G191" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H191" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B192" t="s">
+        <v>779</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D192" t="s">
+        <v>11</v>
+      </c>
+      <c r="E192" t="s">
+        <v>218</v>
+      </c>
+      <c r="F192" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G192" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H192" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B193" t="s">
+        <v>813</v>
+      </c>
+      <c r="C193" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D193" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" t="s">
+        <v>218</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G193" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H193" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B194" t="s">
+        <v>795</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D194" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" t="s">
+        <v>218</v>
+      </c>
+      <c r="F194" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G194" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H194" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B195" t="s">
+        <v>795</v>
+      </c>
+      <c r="C195" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D195" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" t="s">
+        <v>218</v>
+      </c>
+      <c r="F195" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G195" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H195" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B196" t="s">
+        <v>795</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D196" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" t="s">
+        <v>218</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G196" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H196" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B197" t="s">
+        <v>166</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D197" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" t="s">
+        <v>19</v>
+      </c>
+      <c r="F197" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G197" t="s">
+        <v>277</v>
+      </c>
+      <c r="H197" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B198" t="s">
+        <v>801</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D198" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" t="s">
+        <v>218</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G198" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H198" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B199" t="s">
+        <v>621</v>
+      </c>
+      <c r="C199" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D199" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" t="s">
+        <v>218</v>
+      </c>
+      <c r="F199" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G199" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H199" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B200" t="s">
+        <v>690</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D200" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" t="s">
+        <v>218</v>
+      </c>
+      <c r="F200" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G200" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H200" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B201" t="s">
+        <v>254</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D201" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" t="s">
+        <v>19</v>
+      </c>
+      <c r="F201" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G201" t="s">
+        <v>287</v>
+      </c>
+      <c r="H201" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B202" t="s">
+        <v>254</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D202" t="s">
+        <v>11</v>
+      </c>
+      <c r="E202" t="s">
+        <v>19</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G202" t="s">
+        <v>287</v>
+      </c>
+      <c r="H202" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B203" t="s">
+        <v>807</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D203" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" t="s">
+        <v>218</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G203" t="s">
+        <v>810</v>
+      </c>
+      <c r="H203" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B204" t="s">
+        <v>779</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D204" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>218</v>
+      </c>
+      <c r="F204" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G204" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H204" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B205" t="s">
+        <v>216</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D205" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" t="s">
+        <v>218</v>
+      </c>
+      <c r="F205" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G205" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H205" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D206" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" t="s">
+        <v>218</v>
+      </c>
+      <c r="F206" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G206" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H206" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B207" t="s">
+        <v>223</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D207" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" t="s">
+        <v>19</v>
+      </c>
+      <c r="F207" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G207" t="s">
+        <v>303</v>
+      </c>
+      <c r="H207" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B208" t="s">
+        <v>36</v>
+      </c>
+      <c r="C208" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D208" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" t="s">
+        <v>19</v>
+      </c>
+      <c r="F208" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G208" t="s">
+        <v>1086</v>
+      </c>
+      <c r="H208" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C209" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D209" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" t="s">
+        <v>19</v>
+      </c>
+      <c r="F209" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G209" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H209" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C210" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D210" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" t="s">
+        <v>19</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G210" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H210" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C211" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D211" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" t="s">
+        <v>19</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G211" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H211" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B212" t="s">
+        <v>813</v>
+      </c>
+      <c r="C212" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D212" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" t="s">
+        <v>218</v>
+      </c>
+      <c r="F212" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G212" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H212" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B213" t="s">
+        <v>813</v>
+      </c>
+      <c r="C213" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D213" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" t="s">
+        <v>218</v>
+      </c>
+      <c r="F213" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G213" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H213" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B214" t="s">
+        <v>155</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D214" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" t="s">
+        <v>19</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G214" t="s">
+        <v>246</v>
+      </c>
+      <c r="H214" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B215" t="s">
+        <v>859</v>
+      </c>
+      <c r="C215" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D215" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G215" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H215" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B216" t="s">
+        <v>795</v>
+      </c>
+      <c r="C216" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D216" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" t="s">
+        <v>218</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G216" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H216" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B217" t="s">
+        <v>795</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D217" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" t="s">
+        <v>218</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G217" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H217" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B218" t="s">
+        <v>937</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D218" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" t="s">
+        <v>218</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G218" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H218" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B219" t="s">
+        <v>937</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D219" t="s">
+        <v>11</v>
+      </c>
+      <c r="E219" t="s">
+        <v>218</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G219" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H219" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B220" t="s">
+        <v>795</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D220" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" t="s">
+        <v>218</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G220" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H220" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B221" t="s">
+        <v>458</v>
+      </c>
+      <c r="C221" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D221" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" t="s">
+        <v>218</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G221" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H221" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B222" t="s">
+        <v>458</v>
+      </c>
+      <c r="C222" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D222" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" t="s">
+        <v>218</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G222" t="s">
+        <v>1156</v>
+      </c>
+      <c r="H222" t="s">
+        <v>1157</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-ingredient-product-detail.report.xlsx
+++ b/tools/importer/reports/import-ingredient-product-detail.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1157">
   <si>
     <t>_reportFile</t>
   </si>
@@ -661,7 +661,7 @@
     <t>global/en/ingredients/powders-concentrates/nzmp-frozen-wholemilk-concentrate.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/nzmp-frozen-wholemilk-concentrate</t>
@@ -670,7 +670,7 @@
     <t>ingredient-product-detail</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:25.188Z</t>
+    <t>2026-08-14T01:44:33.033Z</t>
   </si>
   <si>
     <t>Frozen Whole Milk Concentrate | NZMP.com</t>
@@ -1006,7 +1006,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-au</t>
   </si>
   <si>
-    <t>2026-08-14T01:34:19.627Z</t>
+    <t>2026-08-14T01:35:22.896Z</t>
   </si>
   <si>
     <t>Cheddar Cheese (Australia Specification) | NZMP Dairy Ingredients | NZMP.com</t>
@@ -1018,13 +1018,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:23.694Z</t>
+    <t>2026-08-14T01:36:15.923Z</t>
   </si>
   <si>
     <t>Cheddar Cheese Frozen | NZMP.com</t>
@@ -1039,7 +1039,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-manufacturing</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:33.759Z</t>
+    <t>2026-08-14T01:36:24.161Z</t>
   </si>
   <si>
     <t>Cheddar Cheese for Manufacturing | NZMP.com</t>
@@ -1051,13 +1051,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:40.959Z</t>
+    <t>2026-08-14T01:36:32.024Z</t>
   </si>
   <si>
     <t>Cheddar Cheese | NZMP Dairy Ingredients | NZMP.com</t>
@@ -1069,13 +1069,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:49.141Z</t>
+    <t>2026-08-14T01:36:40.029Z</t>
   </si>
   <si>
     <t>Coloured Cheddar Cheese | NZMP.com</t>
@@ -1087,13 +1087,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:56.362Z</t>
+    <t>2026-08-14T01:36:47.626Z</t>
   </si>
   <si>
     <t>Frozen Functional Cheddar Cheese | NZMP.com</t>
@@ -1105,13 +1105,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:04.559Z</t>
+    <t>2026-08-14T01:36:54.630Z</t>
   </si>
   <si>
     <t>Mature Cheddar | NZMP.com</t>
@@ -1126,7 +1126,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-cheddar-cheese-frozen</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:13.023Z</t>
+    <t>2026-08-14T01:37:02.427Z</t>
   </si>
   <si>
     <t>Organic Frozen Cheddar Cheese, Reduced Salt  | NZMP.com</t>
@@ -1138,13 +1138,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:20.559Z</t>
+    <t>2026-08-14T01:37:10.659Z</t>
   </si>
   <si>
     <t>Organic Mature Cheddar Cheese | NZMP.com</t>
@@ -1159,7 +1159,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-mild-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:30.171Z</t>
+    <t>2026-08-14T01:37:20.257Z</t>
   </si>
   <si>
     <t>Organic Mild Cheddar Cheese | NZMP.com</t>
@@ -1171,13 +1171,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:39.195Z</t>
+    <t>2026-08-14T01:37:28.686Z</t>
   </si>
   <si>
     <t>Strong Cheddar Cheese for Manufacturing | NZMP.com</t>
@@ -1192,7 +1192,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/young-cheddar-cheese-manufacturing-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:46.723Z</t>
+    <t>2026-08-14T01:37:35.638Z</t>
   </si>
   <si>
     <t>Young Cheddar Cheese for Manufacturing GDT Specification | NZMP.com</t>
@@ -1207,7 +1207,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/easy-shred-mozzarella-nz</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:55.022Z</t>
+    <t>2026-08-14T01:37:44.937Z</t>
   </si>
   <si>
     <t>Easy Shred Mozzarella | NZMP.com</t>
@@ -1234,7 +1234,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/frozen-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:04.860Z</t>
+    <t>2026-08-14T01:37:54.322Z</t>
   </si>
   <si>
     <t>Frozen Mozzarella | NZMP.com</t>
@@ -1249,7 +1249,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/iqf-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:13.085Z</t>
+    <t>2026-08-14T01:38:04.836Z</t>
   </si>
   <si>
     <t>Individually Quick Frozen Mozzarella | NZMP.com</t>
@@ -1264,7 +1264,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/lower-salt-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:22.024Z</t>
+    <t>2026-08-14T01:38:13.261Z</t>
   </si>
   <si>
     <t>Lower Salt Mozzarella | NZMP.com</t>
@@ -1279,7 +1279,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/medium-fat-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:32.323Z</t>
+    <t>2026-08-14T01:38:21.948Z</t>
   </si>
   <si>
     <t>Medium Fat Mozzarella | NZMP.com</t>
@@ -1291,13 +1291,10 @@
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-curd.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
-  </si>
-  <si>
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-curd</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:39.974Z</t>
+    <t>2026-08-14T01:38:29.639Z</t>
   </si>
   <si>
     <t>Mozzarella Curd | NZMP.com</t>
@@ -1309,13 +1306,13 @@
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-frozen-au.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-frozen-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:49.166Z</t>
+    <t>2026-08-14T01:38:39.928Z</t>
   </si>
   <si>
     <t>Premium Mozzarella Frozen (Made in Australia) | NZMP.com</t>
@@ -1330,7 +1327,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-frozen-nz</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:58.334Z</t>
+    <t>2026-08-14T01:38:49.223Z</t>
   </si>
   <si>
     <t>Premium Mozzarella Frozen (Made in New Zealand) | NZMP.com</t>
@@ -1345,7 +1342,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/premium-chilled-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:08.123Z</t>
+    <t>2026-08-14T01:38:57.588Z</t>
   </si>
   <si>
     <t>Premium Chilled Mozzarella | NZMP.com</t>
@@ -1360,7 +1357,7 @@
     <t>global/en/ingredients/cheese/new-zealand-cheeses/egmont-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:15.122Z</t>
+    <t>2026-08-14T01:39:05.359Z</t>
   </si>
   <si>
     <t>Egmont™ Cheese | NZMP.com</t>
@@ -1375,7 +1372,7 @@
     <t>global/en/ingredients/cheese/new-zealand-cheeses/noble-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:23.064Z</t>
+    <t>2026-08-14T01:39:12.825Z</t>
   </si>
   <si>
     <t>Noble™ Cheese | NZMP.com</t>
@@ -1387,13 +1384,13 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/colby-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/colby-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:30.160Z</t>
+    <t>2026-08-14T01:39:18.624Z</t>
   </si>
   <si>
     <t>Colby Cheese | NZMP.com</t>
@@ -1408,7 +1405,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/edam-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:38.122Z</t>
+    <t>2026-08-14T01:39:25.564Z</t>
   </si>
   <si>
     <t>Edam Cheese | NZMP.com</t>
@@ -1423,7 +1420,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/gouda-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:46.093Z</t>
+    <t>2026-08-14T01:39:32.499Z</t>
   </si>
   <si>
     <t>Gouda Cheese - NZMP Dairy Ingredients | NZMP.com</t>
@@ -1438,7 +1435,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/parmesan-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:53.223Z</t>
+    <t>2026-08-14T01:39:38.760Z</t>
   </si>
   <si>
     <t>Parmesan | NZMP.com</t>
@@ -1453,7 +1450,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/swiss-style-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:00.222Z</t>
+    <t>2026-08-14T01:39:45.410Z</t>
   </si>
   <si>
     <t>Swiss-Style Cheese | NZMP.com</t>
@@ -1468,7 +1465,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-15l-convenience-pack</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:09.445Z</t>
+    <t>2026-08-14T01:39:55.173Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat 15L/13.5KG Convenience Pack | NZMP.com</t>
@@ -1483,7 +1480,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-premium-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:17.380Z</t>
+    <t>2026-08-14T01:40:03.077Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Premium Grade GDT Specification | NZMP.com</t>
@@ -1498,7 +1495,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-premium</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:24.337Z</t>
+    <t>2026-08-14T01:40:10.722Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Premium Grade | NZMP.com</t>
@@ -1513,7 +1510,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-regular-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:32.037Z</t>
+    <t>2026-08-14T01:40:18.535Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Regular Grade GDT Specification | NZMP.com</t>
@@ -1528,7 +1525,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-regular</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:40.884Z</t>
+    <t>2026-08-14T01:40:27.112Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Regular Grade | NZMP.com</t>
@@ -1543,7 +1540,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/organic-anhydrous-milk-fat-premium</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:48.228Z</t>
+    <t>2026-08-14T01:40:34.204Z</t>
   </si>
   <si>
     <t>Organic Anhydrous Milk Fat Premium Grade | NZMP.com</t>
@@ -1558,7 +1555,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/lactic-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:57.225Z</t>
+    <t>2026-08-14T01:40:42.939Z</t>
   </si>
   <si>
     <t>Lactic Butter | NZMP.com</t>
@@ -1573,7 +1570,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/organic-salted-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:05.757Z</t>
+    <t>2026-08-14T01:40:50.896Z</t>
   </si>
   <si>
     <t>Organic Salted Butter | NZMP.com</t>
@@ -1588,7 +1585,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/organic-unsalted-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:13.771Z</t>
+    <t>2026-08-14T01:40:57.923Z</t>
   </si>
   <si>
     <t>Organic Unsalted Butter | NZMP.com</t>
@@ -1603,7 +1600,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/organic-unsalted-lactic-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:23.223Z</t>
+    <t>2026-08-14T01:41:05.494Z</t>
   </si>
   <si>
     <t>Organic Lactic Unsalted Butter | NZMP.com</t>
@@ -1618,7 +1615,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/salted-creamery-butter-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:30.596Z</t>
+    <t>2026-08-14T01:41:12.323Z</t>
   </si>
   <si>
     <t>Salted Creamery Butter GDT Specification | NZMP.com</t>
@@ -1633,7 +1630,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/salted-creamery-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:38.728Z</t>
+    <t>2026-08-14T01:41:18.846Z</t>
   </si>
   <si>
     <t>Salted Creamery Butter | NZMP.com</t>
@@ -1645,13 +1642,13 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-butter-convenience-pack.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-butter-convenience-pack</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:46.860Z</t>
+    <t>2026-08-14T01:41:29.060Z</t>
   </si>
   <si>
     <t>NZMP™ Unsalted Butter, 12.5kg Convenience Pack | NZMP.com</t>
@@ -1666,7 +1663,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-creamery-butter-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:55.505Z</t>
+    <t>2026-08-14T01:41:36.846Z</t>
   </si>
   <si>
     <t>Unsalted Creamery Butter GDT Specification | NZMP.com</t>
@@ -1681,7 +1678,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-creamery-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:21:49.560Z</t>
+    <t>2026-08-14T01:41:44.843Z</t>
   </si>
   <si>
     <t>Unsalted Creamery Butter | NZMP.com</t>
@@ -1696,7 +1693,7 @@
     <t>global/en/ingredients/dairy-fats-cream/cream-cheese/cream-cheese-traditional</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:03.353Z</t>
+    <t>2026-08-14T01:41:53.585Z</t>
   </si>
   <si>
     <t>Cream Cheese Traditional | NZMP.com</t>
@@ -1711,7 +1708,7 @@
     <t>global/en/ingredients/dairy-fats-cream/cream-powder/cream-powder-55</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:12.161Z</t>
+    <t>2026-08-14T01:42:02.959Z</t>
   </si>
   <si>
     <t>Cream Powder 55 | NZMP.com</t>
@@ -1726,7 +1723,7 @@
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder/regular-buttermilk-powder-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:20.527Z</t>
+    <t>2026-08-14T01:42:12.034Z</t>
   </si>
   <si>
     <t>Regular Buttermilk Powder (Australia Specification) | NZMP.com</t>
@@ -1741,7 +1738,7 @@
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder/regular-buttermilk-powder-uht-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:26.857Z</t>
+    <t>2026-08-14T01:42:21.925Z</t>
   </si>
   <si>
     <t>Regular Buttermilk Powder for UHT Milk GDT Specification | NZMP.com</t>
@@ -1756,7 +1753,7 @@
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder/regular-buttermilk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:36.708Z</t>
+    <t>2026-08-14T01:42:42.268Z</t>
   </si>
   <si>
     <t>Regular Buttermilk Powder | NZMP.com</t>
@@ -1771,7 +1768,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/fat-filled-milk-powder-for-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:45.947Z</t>
+    <t>2026-08-14T01:42:49.477Z</t>
   </si>
   <si>
     <t>Fat Filled Milk Powder for Yoghurt | NZMP.com</t>
@@ -1783,13 +1780,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/fat-filled-milk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/fat-filled-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:54.960Z</t>
+    <t>2026-08-14T01:42:58.923Z</t>
   </si>
   <si>
     <t>Fat Filled Milk Powder Instant Fortified | NZMP.com</t>
@@ -1801,13 +1798,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/gold-instant-whole-milk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/gold-instant-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:03.328Z</t>
+    <t>2026-08-14T01:43:07.035Z</t>
   </si>
   <si>
     <t>Gold Instant Whole Milk Powder | NZMP.com</t>
@@ -1822,7 +1819,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/instant-skim-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:11.088Z</t>
+    <t>2026-08-14T01:43:15.723Z</t>
   </si>
   <si>
     <t>Instant Skim Milk Powder | NZMP.com</t>
@@ -1837,7 +1834,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/instant-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:18.924Z</t>
+    <t>2026-08-14T01:43:24.557Z</t>
   </si>
   <si>
     <t>Instant Whole Milk Powder | NZMP Ingredients | NZMP.com</t>
@@ -1852,7 +1849,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-fortified-plus-instant-wmp</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:26.321Z</t>
+    <t>2026-08-14T01:43:31.943Z</t>
   </si>
   <si>
     <t>Fortified+ Instant Whole Milk Powder | NZMP.com</t>
@@ -1867,7 +1864,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-gold-instant-wmp</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:35.123Z</t>
+    <t>2026-08-14T01:43:41.630Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-gold-instant-wmp.html</t>
@@ -1876,13 +1873,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-low-cost-pure-instant-dairy-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-low-cost-pure-instant-dairy-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:43.175Z</t>
+    <t>2026-08-14T01:43:49.641Z</t>
   </si>
   <si>
     <t>Low-Cost Pure Instant Dairy Powder | NZMP.com</t>
@@ -1894,13 +1891,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-nutriwhite-dairy-based-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-nutriwhite-dairy-based-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:52.280Z</t>
+    <t>2026-08-14T01:43:58.900Z</t>
   </si>
   <si>
     <t>NutriWhite Dairy-Based Powder | NZMP Dairy Ingredients | NZMP.com</t>
@@ -1912,13 +1909,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-protein-plus-instant-milk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-protein-plus-instant-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:01.245Z</t>
+    <t>2026-08-14T01:44:08.425Z</t>
   </si>
   <si>
     <t>Protein+ Instant Milk Powder | NZMP.com</t>
@@ -1933,7 +1930,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/super-fortified-instant-smp</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:10.156Z</t>
+    <t>2026-08-14T01:44:16.966Z</t>
   </si>
   <si>
     <t>Super Fortified Instant Skim Milk Powder | NZMP.com</t>
@@ -1948,7 +1945,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/whole-milk-powder-instant-fortified</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:18.198Z</t>
+    <t>2026-08-14T01:44:25.490Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder Instant Fortified with Vitamins A &amp; D | NZMP.com</t>
@@ -1960,13 +1957,13 @@
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-demineralised-whey-powder-90.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","carousel-news"]</t>
+    <t>["columns-product","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-demineralised-whey-powder-90</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:31.261Z</t>
+    <t>2026-08-14T01:44:39.094Z</t>
   </si>
   <si>
     <t>SureStart™ Demineralised Whey Powder 90% | NZMP.com</t>
@@ -1981,7 +1978,7 @@
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-regular-skim-milk-powder-wetapp</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:39.058Z</t>
+    <t>2026-08-14T01:44:47.024Z</t>
   </si>
   <si>
     <t>Paediatric Grade Regular Skim Milk Powder | NZMP.com</t>
@@ -1996,7 +1993,7 @@
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-regular-whole-milk-powder-wetapp</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:46.289Z</t>
+    <t>2026-08-14T01:44:53.565Z</t>
   </si>
   <si>
     <t>Paediatric Grade Regular Whole Milk Powder | NZMP.com</t>
@@ -2011,7 +2008,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/organic-skim-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:54.988Z</t>
+    <t>2026-08-14T01:45:01.460Z</t>
   </si>
   <si>
     <t>Organic Skim Milk Powder | NZMP.com</t>
@@ -2026,7 +2023,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-high-heat-hs-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:25:03.060Z</t>
+    <t>2026-08-14T01:45:09.737Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder High Heat Heat Stable GDT Specification | NZMP.com</t>
@@ -2041,7 +2038,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-high-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:25:12.820Z</t>
+    <t>2026-08-14T01:45:17.860Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder High Heat | NZMP.com</t>
@@ -2056,7 +2053,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-low-heat-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:25:20.420Z</t>
+    <t>2026-08-14T01:45:24.376Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Low Heat GDT Specification | NZMP.com</t>
@@ -2071,7 +2068,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-low-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:14.609Z</t>
+    <t>2026-08-14T01:46:18.662Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Low Heat | NZMP.com</t>
@@ -2083,13 +2080,13 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat-au.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:24.471Z</t>
+    <t>2026-08-14T01:46:26.637Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Medium Heat (Australia Specification) | NZMP.com</t>
@@ -2104,7 +2101,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:32.036Z</t>
+    <t>2026-08-14T01:46:34.088Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Medium Heat GDT Specification | NZMP.com</t>
@@ -2119,7 +2116,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:40.541Z</t>
+    <t>2026-08-14T01:46:43.360Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Medium Heat | NZMP.com</t>
@@ -2134,7 +2131,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-uht-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:47.775Z</t>
+    <t>2026-08-14T01:46:51.521Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder for UHT Milk GDT Specification | NZMP.com</t>
@@ -2149,7 +2146,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-uht</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:55.557Z</t>
+    <t>2026-08-14T01:47:00.675Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder for UHT Milk | NZMP.com</t>
@@ -2164,7 +2161,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/smp-for-uht</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:02.437Z</t>
+    <t>2026-08-14T01:47:07.992Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/skim-milk-powder/smp-for-uht.html</t>
@@ -2176,7 +2173,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/super-fortified-instant-smp</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:11.234Z</t>
+    <t>2026-08-14T01:47:16.484Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/skim-milk-powder/super-fortified-instant-smp.html</t>
@@ -2188,7 +2185,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/surestart-regular-smp-low-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:19.248Z</t>
+    <t>2026-08-14T01:47:23.983Z</t>
   </si>
   <si>
     <t>SureStart™ Regular Skim Milk Powder Low Heat | NZMP Ingredients | NZMP.com</t>
@@ -2203,7 +2200,7 @@
     <t>global/en/ingredients/powders-concentrates/whey-powder/nzmp-whey-powder-621</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:27.257Z</t>
+    <t>2026-08-14T01:47:33.421Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Powder 621 | NZMP.com</t>
@@ -2218,7 +2215,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/organic-regular-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:35.578Z</t>
+    <t>2026-08-14T01:47:41.419Z</t>
   </si>
   <si>
     <t>Organic Whole Milk Powder | NZMP.com</t>
@@ -2233,7 +2230,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:43.681Z</t>
+    <t>2026-08-14T01:47:50.696Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder GDT Specification | NZMP.com</t>
@@ -2248,7 +2245,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-high-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:51.758Z</t>
+    <t>2026-08-14T01:48:00.589Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder High Heat | NZMP.com</t>
@@ -2263,7 +2260,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-repack</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:58.959Z</t>
+    <t>2026-08-14T01:48:07.619Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Repack | NZMP.com</t>
@@ -2278,7 +2275,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-uht-28-fat</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:07.505Z</t>
+    <t>2026-08-14T01:48:16.238Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder 28% Fat for UHT | NZMP.com</t>
@@ -2293,7 +2290,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-uht</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:16.195Z</t>
+    <t>2026-08-14T01:48:24.659Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for UHT Milk | NZMP.com</t>
@@ -2308,7 +2305,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:25.141Z</t>
+    <t>2026-08-14T01:48:32.240Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder | NZMP.com</t>
@@ -2323,7 +2320,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-blending</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:32.225Z</t>
+    <t>2026-08-14T01:48:40.406Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Blending | NZMP.com</t>
@@ -2338,7 +2335,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-tea</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:40.528Z</t>
+    <t>2026-08-14T01:48:48.410Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Tea | NZMP.com</t>
@@ -2350,13 +2347,13 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-yoghurt.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:48.780Z</t>
+    <t>2026-08-14T01:48:56.432Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Yoghurt | NZMP.com</t>
@@ -2371,7 +2368,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/whole-milk-powder-recombined-evaporated-milk</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:55.898Z</t>
+    <t>2026-08-14T01:49:05.260Z</t>
   </si>
   <si>
     <t>Whole Milk Powder for Recombined Evaporated Milk | NZMP.com</t>
@@ -2386,7 +2383,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/wmp-uht-perform</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:03.666Z</t>
+    <t>2026-08-14T01:49:12.961Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder UHT Perform - NZMP Ingredients | NZMP.com</t>
@@ -2398,13 +2395,13 @@
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-7051.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-7051</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:31.160Z</t>
+    <t>2026-08-14T01:50:39.923Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Hydrolysate 7051 | NZMP.com</t>
@@ -2416,13 +2413,13 @@
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-821.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-821</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:39.060Z</t>
+    <t>2026-08-14T01:50:48.060Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Hydrolysate 821 | NZMP.com</t>
@@ -2434,13 +2431,13 @@
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-917.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-917</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:46.974Z</t>
+    <t>2026-08-14T01:50:56.661Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Hydrolysate 917 | NZMP.com</t>
@@ -2452,13 +2449,13 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-470.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-470</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:54.400Z</t>
+    <t>2026-08-14T01:51:03.920Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 470 | NZMP.com</t>
@@ -2470,13 +2467,13 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-485.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-485</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:04.397Z</t>
+    <t>2026-08-14T01:51:14.071Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 485 | NZMP.com</t>
@@ -2515,7 +2512,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4851</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:14.149Z</t>
+    <t>2026-08-14T01:51:23.683Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4851 | NZMP.com</t>
@@ -2542,7 +2539,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:23.524Z</t>
+    <t>2026-08-14T01:51:33.624Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4861 | NZMP.com</t>
@@ -2590,13 +2587,13 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:35.766Z</t>
+    <t>2026-08-14T01:51:45.230Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4882 | NZMP.com</t>
@@ -2611,7 +2608,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4887</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:46.378Z</t>
+    <t>2026-08-14T01:51:54.159Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4887 | NZMP.com</t>
@@ -2638,7 +2635,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-sureprotein-mpc-4881</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:55.459Z</t>
+    <t>2026-08-14T01:52:04.114Z</t>
   </si>
   <si>
     <t>SureProtein™ Milk Protein Concentrate 4881 | NZMP.com</t>
@@ -2653,7 +2650,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/organic-milk-protein-concentrate-485</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:03.223Z</t>
+    <t>2026-08-14T01:52:13.022Z</t>
   </si>
   <si>
     <t>Organic Milk Protein Concentrate (Regular 85%) | NZMP.com</t>
@@ -2668,7 +2665,7 @@
     <t>global/en/ingredients/proteins/milk-protein-isolates/nzmp-milk-protein-isolate-4900</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:11.864Z</t>
+    <t>2026-08-14T01:52:21.729Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Isolate 4900 | NZMP.com</t>
@@ -2683,7 +2680,7 @@
     <t>global/en/ingredients/proteins/milk-protein-isolates/nzmp-softbar-1000</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:19.837Z</t>
+    <t>2026-08-14T01:52:29.172Z</t>
   </si>
   <si>
     <t>SureProtein™ Milk Protein Isolate SoftBar 1000 | NZMP.com</t>
@@ -2698,7 +2695,7 @@
     <t>global/en/ingredients/proteins/total-milk-proteins/nzmp-total-milk-protein-shortbar-1104</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:27.023Z</t>
+    <t>2026-08-14T01:52:37.097Z</t>
   </si>
   <si>
     <t>SureProtein™ Total Milk Protein ShortBar 1104 | NZMP.com</t>
@@ -2713,7 +2710,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-bioactive-whey-protein</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:36.202Z</t>
+    <t>2026-08-14T01:52:45.939Z</t>
   </si>
   <si>
     <t>Bioactive Whey Protein | NZMP.com</t>
@@ -2728,7 +2725,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-dairy-protein-crisps-crispbar</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:43.023Z</t>
+    <t>2026-08-14T01:52:54.158Z</t>
   </si>
   <si>
     <t>NZMP™ Dairy Protein Crisps 600 | NZMP.com</t>
@@ -2743,7 +2740,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flex-wpc-515</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:50.124Z</t>
+    <t>2026-08-14T01:53:01.874Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 515 | NZMP.com</t>
@@ -2770,7 +2767,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flow-wpc-510</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:58.520Z</t>
+    <t>2026-08-14T01:53:08.822Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 510 | NZMP.com</t>
@@ -2785,7 +2782,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-instant-whey-protein-concentrate-450</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:05.241Z</t>
+    <t>2026-08-14T01:53:16.060Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Concentrate 450 | NZMP.com</t>
@@ -2800,7 +2797,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-pro-optima-wpc-567</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:14.959Z</t>
+    <t>2026-08-14T01:53:26.564Z</t>
   </si>
   <si>
     <t>NZMP™ Pro-Optima™ Whey Protein Concentrate | NZMP.com</t>
@@ -2824,13 +2821,13 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-132.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-132</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:23.568Z</t>
+    <t>2026-08-14T01:53:33.622Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 132 | NZMP.com</t>
@@ -2845,7 +2842,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-162</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:31.064Z</t>
+    <t>2026-08-14T01:53:41.522Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 162 | NZMP.com</t>
@@ -2860,7 +2857,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-322</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:38.541Z</t>
+    <t>2026-08-14T01:53:49.958Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 322 | NZMP.com</t>
@@ -2872,13 +2869,13 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-352.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-352</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:46.260Z</t>
+    <t>2026-08-14T01:53:58.804Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 352 | NZMP.com</t>
@@ -2893,7 +2890,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-356</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:55.126Z</t>
+    <t>2026-08-14T01:54:07.224Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 356 | NZMP.com</t>
@@ -2908,7 +2905,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-392</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:03.101Z</t>
+    <t>2026-08-14T01:54:15.790Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 392 | NZMP.com</t>
@@ -2923,7 +2920,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-397</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:12.338Z</t>
+    <t>2026-08-14T01:54:23.819Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 397 | NZMP.com</t>
@@ -2938,7 +2935,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-457-decolorized</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:20.137Z</t>
+    <t>2026-08-14T01:54:33.675Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 457 | NZMP.com</t>
@@ -2953,7 +2950,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-472</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:29.223Z</t>
+    <t>2026-08-14T01:54:42.974Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 472 | NZMP.com</t>
@@ -2968,7 +2965,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-480-instantised</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:36.615Z</t>
+    <t>2026-08-14T01:54:50.322Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Concentrate 480 | NZMP.com</t>
@@ -2983,7 +2980,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-7009</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:44.423Z</t>
+    <t>2026-08-14T01:54:58.322Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 7009 | NZMP.com</t>
@@ -2995,13 +2992,13 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-550.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-550</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:52.271Z</t>
+    <t>2026-08-14T01:55:07.591Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 550 | NZMP.com</t>
@@ -3028,7 +3025,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/organic-whey-protein-concentrate-392</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:00.210Z</t>
+    <t>2026-08-14T01:55:15.558Z</t>
   </si>
   <si>
     <t>Organic Whey Protein Concentrate (Regular 80% Protein) | NZMP.com</t>
@@ -3043,7 +3040,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/lactoferrin</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:11.675Z</t>
+    <t>2026-08-14T01:55:25.689Z</t>
   </si>
   <si>
     <t>Lactoferrin - NZMP Dairy Ingredients | NZMP.com</t>
@@ -3058,7 +3055,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-clear-wpi-8855</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:22.459Z</t>
+    <t>2026-08-14T01:55:34.960Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Isolate 8855 | NZMP.com</t>
@@ -3073,7 +3070,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-instant-whey-protein-isolate-894</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:30.120Z</t>
+    <t>2026-08-14T01:55:42.802Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Isolate 894 | NZMP.com</t>
@@ -3088,7 +3085,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-instant-whey-protein-isolate-895</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:39.122Z</t>
+    <t>2026-08-14T01:55:50.560Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Isolate 895 | NZMP.com</t>
@@ -3103,7 +3100,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-optibar</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:47.659Z</t>
+    <t>2026-08-14T01:55:59.115Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Isolate 894 | NZMP.com</t>
@@ -3130,7 +3127,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-wpi-895</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:54.879Z</t>
+    <t>2026-08-14T01:56:06.224Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Isolate 895 | NZMP.com</t>
@@ -3145,7 +3142,7 @@
     <t>global/en/ingredients/specialty/complex-lipids/milk-phospholipids</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:03.923Z</t>
+    <t>2026-08-14T01:56:59.960Z</t>
   </si>
   <si>
     <t>Milk Phospholipids | NZMP.com</t>
@@ -3160,7 +3157,7 @@
     <t>global/en/ingredients/specialty/complex-lipids/surestart-mfgm-lipids</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:11.920Z</t>
+    <t>2026-08-14T01:57:08.825Z</t>
   </si>
   <si>
     <t>SureStart™ MFGM Lipids | NZMP.com</t>
@@ -3199,7 +3196,7 @@
     <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-softbar-917</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:19.760Z</t>
+    <t>2026-08-14T01:57:18.225Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-softbar-917.html</t>
@@ -3211,7 +3208,7 @@
     <t>global/en/ingredients/specialty/lactoferrin/nzmp-lactoferrin</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:30.370Z</t>
+    <t>2026-08-14T01:57:27.289Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/specialty/lactoferrin/nzmp-lactoferrin.html</t>
@@ -3223,7 +3220,7 @@
     <t>global/en/ingredients/specialty/lactoferrin/surestart-lactoferrin</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:40.029Z</t>
+    <t>2026-08-14T01:57:34.423Z</t>
   </si>
   <si>
     <t>Paediatric Lactoferrin - NZMP Dairy Ingredients | NZMP.com</t>
@@ -3235,13 +3232,13 @@
     <t>global/en/ingredients/specialty/prebiotics/galacto-oligosaccharide-gos-prebiotic-fibre.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","carousel-news"]</t>
+    <t>["columns-product","columns-feature","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/specialty/prebiotics/galacto-oligosaccharide-gos-prebiotic-fibre</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:47.087Z</t>
+    <t>2026-08-14T01:57:41.244Z</t>
   </si>
   <si>
     <t>Galacto-oligosaccharide (GOS) Prebiotic Fibre | NZMP.com</t>
@@ -3331,7 +3328,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/acid-casein-741</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:11.783Z</t>
+    <t>2026-08-14T01:49:20.157Z</t>
   </si>
   <si>
     <t>NZMP™ Mineral Acid Casein 741 | NZMP.com</t>
@@ -3346,7 +3343,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-720</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:20.067Z</t>
+    <t>2026-08-14T01:49:27.566Z</t>
   </si>
   <si>
     <t>NZMP™ Lactic Acid Casein 720 | NZMP.com</t>
@@ -3373,7 +3370,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/calcium-caseinate-380</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:29.514Z</t>
+    <t>2026-08-14T01:49:36.519Z</t>
   </si>
   <si>
     <t>NZMP™ Calcium Caseinate 380 | NZMP.com</t>
@@ -3388,7 +3385,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-calcium-caseinate-309</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:38.385Z</t>
+    <t>2026-08-14T01:49:43.201Z</t>
   </si>
   <si>
     <t>NZMP™ Calcium Caseinate 309 | NZMP.com</t>
@@ -3403,7 +3400,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-calcium-caseinate-385</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:44.925Z</t>
+    <t>2026-08-14T01:49:50.249Z</t>
   </si>
   <si>
     <t>NZMP™ Calcium Caseinate 385 | NZMP.com</t>
@@ -3418,7 +3415,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-sodium-caseinate-166</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:52.923Z</t>
+    <t>2026-08-14T01:49:58.924Z</t>
   </si>
   <si>
     <t>NZMP™ Sodium Caseinate 166 | NZMP.com</t>
@@ -3433,7 +3430,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-sodium-caseinate-167</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:59.659Z</t>
+    <t>2026-08-14T01:50:06.679Z</t>
   </si>
   <si>
     <t>NZMP™ Sodium Caseinate 167 | NZMP.com</t>
@@ -3448,7 +3445,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-sodium-caseinate-180</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:08.423Z</t>
+    <t>2026-08-14T01:50:14.760Z</t>
   </si>
   <si>
     <t>NZMP™ Sodium Caseinate 180 | NZMP.com</t>
@@ -3463,7 +3460,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/rennet-casein/nzmp-rennet-casein-771</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:15.159Z</t>
+    <t>2026-08-14T01:50:22.923Z</t>
   </si>
   <si>
     <t>NZMP™ Rennet Casein 771 | NZMP.com</t>
@@ -3478,7 +3475,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/rennet-casein/sureprotein-rennet-casein-779</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:22.578Z</t>
+    <t>2026-08-14T01:50:30.844Z</t>
   </si>
   <si>
     <t>NZMP™ Rennet Casein 779 | NZMP.com</t>
@@ -5863,2012 +5860,2012 @@
         <v>425</v>
       </c>
       <c r="B77" t="s">
+        <v>329</v>
+      </c>
+      <c r="C77" t="s">
         <v>426</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" t="s">
+        <v>218</v>
+      </c>
+      <c r="F77" t="s">
         <v>427</v>
       </c>
-      <c r="D77" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" t="s">
-        <v>218</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="G77" t="s">
         <v>428</v>
       </c>
-      <c r="G77" t="s">
+      <c r="H77" t="s">
         <v>429</v>
-      </c>
-      <c r="H77" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>430</v>
+      </c>
+      <c r="B78" t="s">
         <v>431</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>432</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" t="s">
+        <v>218</v>
+      </c>
+      <c r="F78" t="s">
         <v>433</v>
       </c>
-      <c r="D78" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" t="s">
-        <v>218</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="G78" t="s">
         <v>434</v>
       </c>
-      <c r="G78" t="s">
+      <c r="H78" t="s">
         <v>435</v>
-      </c>
-      <c r="H78" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B79" t="s">
         <v>346</v>
       </c>
       <c r="C79" t="s">
+        <v>437</v>
+      </c>
+      <c r="D79" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" t="s">
+        <v>218</v>
+      </c>
+      <c r="F79" t="s">
         <v>438</v>
       </c>
-      <c r="D79" t="s">
-        <v>11</v>
-      </c>
-      <c r="E79" t="s">
-        <v>218</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="G79" t="s">
         <v>439</v>
       </c>
-      <c r="G79" t="s">
+      <c r="H79" t="s">
         <v>440</v>
-      </c>
-      <c r="H79" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B80" t="s">
         <v>375</v>
       </c>
       <c r="C80" t="s">
+        <v>442</v>
+      </c>
+      <c r="D80" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" t="s">
+        <v>218</v>
+      </c>
+      <c r="F80" t="s">
         <v>443</v>
       </c>
-      <c r="D80" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" t="s">
-        <v>218</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="G80" t="s">
         <v>444</v>
       </c>
-      <c r="G80" t="s">
+      <c r="H80" t="s">
         <v>445</v>
-      </c>
-      <c r="H80" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B81" t="s">
         <v>364</v>
       </c>
       <c r="C81" t="s">
+        <v>447</v>
+      </c>
+      <c r="D81" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" t="s">
+        <v>218</v>
+      </c>
+      <c r="F81" t="s">
         <v>448</v>
       </c>
-      <c r="D81" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" t="s">
-        <v>218</v>
-      </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>449</v>
       </c>
-      <c r="G81" t="s">
+      <c r="H81" t="s">
         <v>450</v>
-      </c>
-      <c r="H81" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B82" t="s">
         <v>335</v>
       </c>
       <c r="C82" t="s">
+        <v>452</v>
+      </c>
+      <c r="D82" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" t="s">
+        <v>218</v>
+      </c>
+      <c r="F82" t="s">
         <v>453</v>
       </c>
-      <c r="D82" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" t="s">
-        <v>218</v>
-      </c>
-      <c r="F82" t="s">
+      <c r="G82" t="s">
         <v>454</v>
       </c>
-      <c r="G82" t="s">
+      <c r="H82" t="s">
         <v>455</v>
-      </c>
-      <c r="H82" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>456</v>
+      </c>
+      <c r="B83" t="s">
         <v>457</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>458</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" t="s">
+        <v>218</v>
+      </c>
+      <c r="F83" t="s">
         <v>459</v>
       </c>
-      <c r="D83" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" t="s">
-        <v>218</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="G83" t="s">
         <v>460</v>
       </c>
-      <c r="G83" t="s">
+      <c r="H83" t="s">
         <v>461</v>
-      </c>
-      <c r="H83" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B84" t="s">
         <v>346</v>
       </c>
       <c r="C84" t="s">
+        <v>463</v>
+      </c>
+      <c r="D84" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" t="s">
+        <v>218</v>
+      </c>
+      <c r="F84" t="s">
         <v>464</v>
       </c>
-      <c r="D84" t="s">
-        <v>11</v>
-      </c>
-      <c r="E84" t="s">
-        <v>218</v>
-      </c>
-      <c r="F84" t="s">
+      <c r="G84" t="s">
         <v>465</v>
       </c>
-      <c r="G84" t="s">
+      <c r="H84" t="s">
         <v>466</v>
-      </c>
-      <c r="H84" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B85" t="s">
         <v>346</v>
       </c>
       <c r="C85" t="s">
+        <v>468</v>
+      </c>
+      <c r="D85" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" t="s">
+        <v>218</v>
+      </c>
+      <c r="F85" t="s">
         <v>469</v>
       </c>
-      <c r="D85" t="s">
-        <v>11</v>
-      </c>
-      <c r="E85" t="s">
-        <v>218</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="G85" t="s">
         <v>470</v>
       </c>
-      <c r="G85" t="s">
+      <c r="H85" t="s">
         <v>471</v>
-      </c>
-      <c r="H85" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>472</v>
+      </c>
+      <c r="B86" t="s">
+        <v>329</v>
+      </c>
+      <c r="C86" t="s">
         <v>473</v>
       </c>
-      <c r="B86" t="s">
-        <v>426</v>
-      </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" t="s">
+        <v>218</v>
+      </c>
+      <c r="F86" t="s">
         <v>474</v>
       </c>
-      <c r="D86" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" t="s">
-        <v>218</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="G86" t="s">
         <v>475</v>
       </c>
-      <c r="G86" t="s">
+      <c r="H86" t="s">
         <v>476</v>
-      </c>
-      <c r="H86" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B87" t="s">
         <v>358</v>
       </c>
       <c r="C87" t="s">
+        <v>478</v>
+      </c>
+      <c r="D87" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s">
+        <v>218</v>
+      </c>
+      <c r="F87" t="s">
         <v>479</v>
       </c>
-      <c r="D87" t="s">
-        <v>11</v>
-      </c>
-      <c r="E87" t="s">
-        <v>218</v>
-      </c>
-      <c r="F87" t="s">
+      <c r="G87" t="s">
         <v>480</v>
       </c>
-      <c r="G87" t="s">
+      <c r="H87" t="s">
         <v>481</v>
-      </c>
-      <c r="H87" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B88" t="s">
         <v>216</v>
       </c>
       <c r="C88" t="s">
+        <v>483</v>
+      </c>
+      <c r="D88" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" t="s">
+        <v>218</v>
+      </c>
+      <c r="F88" t="s">
         <v>484</v>
       </c>
-      <c r="D88" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" t="s">
-        <v>218</v>
-      </c>
-      <c r="F88" t="s">
+      <c r="G88" t="s">
         <v>485</v>
       </c>
-      <c r="G88" t="s">
+      <c r="H88" t="s">
         <v>486</v>
-      </c>
-      <c r="H88" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B89" t="s">
         <v>216</v>
       </c>
       <c r="C89" t="s">
+        <v>488</v>
+      </c>
+      <c r="D89" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" t="s">
+        <v>218</v>
+      </c>
+      <c r="F89" t="s">
         <v>489</v>
       </c>
-      <c r="D89" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" t="s">
-        <v>218</v>
-      </c>
-      <c r="F89" t="s">
+      <c r="G89" t="s">
         <v>490</v>
       </c>
-      <c r="G89" t="s">
+      <c r="H89" t="s">
         <v>491</v>
-      </c>
-      <c r="H89" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B90" t="s">
         <v>335</v>
       </c>
       <c r="C90" t="s">
+        <v>493</v>
+      </c>
+      <c r="D90" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" t="s">
+        <v>218</v>
+      </c>
+      <c r="F90" t="s">
         <v>494</v>
       </c>
-      <c r="D90" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" t="s">
-        <v>218</v>
-      </c>
-      <c r="F90" t="s">
+      <c r="G90" t="s">
         <v>495</v>
       </c>
-      <c r="G90" t="s">
+      <c r="H90" t="s">
         <v>496</v>
-      </c>
-      <c r="H90" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B91" t="s">
         <v>216</v>
       </c>
       <c r="C91" t="s">
+        <v>498</v>
+      </c>
+      <c r="D91" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" t="s">
+        <v>218</v>
+      </c>
+      <c r="F91" t="s">
         <v>499</v>
       </c>
-      <c r="D91" t="s">
-        <v>11</v>
-      </c>
-      <c r="E91" t="s">
-        <v>218</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="G91" t="s">
         <v>500</v>
       </c>
-      <c r="G91" t="s">
+      <c r="H91" t="s">
         <v>501</v>
-      </c>
-      <c r="H91" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B92" t="s">
         <v>216</v>
       </c>
       <c r="C92" t="s">
+        <v>503</v>
+      </c>
+      <c r="D92" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" t="s">
+        <v>218</v>
+      </c>
+      <c r="F92" t="s">
         <v>504</v>
       </c>
-      <c r="D92" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" t="s">
-        <v>218</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="G92" t="s">
         <v>505</v>
       </c>
-      <c r="G92" t="s">
+      <c r="H92" t="s">
         <v>506</v>
-      </c>
-      <c r="H92" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B93" t="s">
         <v>364</v>
       </c>
       <c r="C93" t="s">
+        <v>508</v>
+      </c>
+      <c r="D93" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" t="s">
+        <v>218</v>
+      </c>
+      <c r="F93" t="s">
         <v>509</v>
       </c>
-      <c r="D93" t="s">
-        <v>11</v>
-      </c>
-      <c r="E93" t="s">
-        <v>218</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
         <v>510</v>
       </c>
-      <c r="G93" t="s">
+      <c r="H93" t="s">
         <v>511</v>
-      </c>
-      <c r="H93" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>512</v>
+      </c>
+      <c r="B94" t="s">
+        <v>329</v>
+      </c>
+      <c r="C94" t="s">
         <v>513</v>
       </c>
-      <c r="B94" t="s">
-        <v>426</v>
-      </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" t="s">
+        <v>218</v>
+      </c>
+      <c r="F94" t="s">
         <v>514</v>
       </c>
-      <c r="D94" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" t="s">
-        <v>218</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
         <v>515</v>
       </c>
-      <c r="G94" t="s">
+      <c r="H94" t="s">
         <v>516</v>
-      </c>
-      <c r="H94" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B95" t="s">
         <v>386</v>
       </c>
       <c r="C95" t="s">
+        <v>518</v>
+      </c>
+      <c r="D95" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" t="s">
+        <v>218</v>
+      </c>
+      <c r="F95" t="s">
         <v>519</v>
       </c>
-      <c r="D95" t="s">
-        <v>11</v>
-      </c>
-      <c r="E95" t="s">
-        <v>218</v>
-      </c>
-      <c r="F95" t="s">
+      <c r="G95" t="s">
         <v>520</v>
       </c>
-      <c r="G95" t="s">
+      <c r="H95" t="s">
         <v>521</v>
-      </c>
-      <c r="H95" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B96" t="s">
         <v>358</v>
       </c>
       <c r="C96" t="s">
+        <v>523</v>
+      </c>
+      <c r="D96" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" t="s">
+        <v>218</v>
+      </c>
+      <c r="F96" t="s">
         <v>524</v>
       </c>
-      <c r="D96" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" t="s">
-        <v>218</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="G96" t="s">
         <v>525</v>
       </c>
-      <c r="G96" t="s">
+      <c r="H96" t="s">
         <v>526</v>
-      </c>
-      <c r="H96" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B97" t="s">
         <v>358</v>
       </c>
       <c r="C97" t="s">
+        <v>528</v>
+      </c>
+      <c r="D97" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" t="s">
+        <v>218</v>
+      </c>
+      <c r="F97" t="s">
         <v>529</v>
       </c>
-      <c r="D97" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" t="s">
-        <v>218</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="G97" t="s">
         <v>530</v>
       </c>
-      <c r="G97" t="s">
+      <c r="H97" t="s">
         <v>531</v>
-      </c>
-      <c r="H97" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B98" t="s">
         <v>358</v>
       </c>
       <c r="C98" t="s">
+        <v>533</v>
+      </c>
+      <c r="D98" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" t="s">
+        <v>218</v>
+      </c>
+      <c r="F98" t="s">
         <v>534</v>
       </c>
-      <c r="D98" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" t="s">
-        <v>218</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="G98" t="s">
         <v>535</v>
       </c>
-      <c r="G98" t="s">
+      <c r="H98" t="s">
         <v>536</v>
-      </c>
-      <c r="H98" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B99" t="s">
         <v>335</v>
       </c>
       <c r="C99" t="s">
+        <v>538</v>
+      </c>
+      <c r="D99" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" t="s">
+        <v>218</v>
+      </c>
+      <c r="F99" t="s">
         <v>539</v>
       </c>
-      <c r="D99" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" t="s">
-        <v>218</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="G99" t="s">
         <v>540</v>
       </c>
-      <c r="G99" t="s">
+      <c r="H99" t="s">
         <v>541</v>
-      </c>
-      <c r="H99" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>542</v>
+      </c>
+      <c r="B100" t="s">
         <v>543</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>544</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" t="s">
+        <v>218</v>
+      </c>
+      <c r="F100" t="s">
         <v>545</v>
       </c>
-      <c r="D100" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" t="s">
-        <v>218</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="G100" t="s">
         <v>546</v>
       </c>
-      <c r="G100" t="s">
+      <c r="H100" t="s">
         <v>547</v>
-      </c>
-      <c r="H100" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s">
         <v>216</v>
       </c>
       <c r="C101" t="s">
+        <v>549</v>
+      </c>
+      <c r="D101" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" t="s">
+        <v>218</v>
+      </c>
+      <c r="F101" t="s">
         <v>550</v>
       </c>
-      <c r="D101" t="s">
-        <v>11</v>
-      </c>
-      <c r="E101" t="s">
-        <v>218</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="G101" t="s">
         <v>551</v>
       </c>
-      <c r="G101" t="s">
+      <c r="H101" t="s">
         <v>552</v>
-      </c>
-      <c r="H101" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B102" t="s">
         <v>335</v>
       </c>
       <c r="C102" t="s">
+        <v>554</v>
+      </c>
+      <c r="D102" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" t="s">
+        <v>218</v>
+      </c>
+      <c r="F102" t="s">
         <v>555</v>
       </c>
-      <c r="D102" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" t="s">
-        <v>218</v>
-      </c>
-      <c r="F102" t="s">
+      <c r="G102" t="s">
         <v>556</v>
       </c>
-      <c r="G102" t="s">
+      <c r="H102" t="s">
         <v>557</v>
-      </c>
-      <c r="H102" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B103" t="s">
         <v>216</v>
       </c>
       <c r="C103" t="s">
+        <v>559</v>
+      </c>
+      <c r="D103" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" t="s">
+        <v>218</v>
+      </c>
+      <c r="F103" t="s">
         <v>560</v>
       </c>
-      <c r="D103" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" t="s">
-        <v>218</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="G103" t="s">
         <v>561</v>
       </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
         <v>562</v>
-      </c>
-      <c r="H103" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B104" t="s">
         <v>346</v>
       </c>
       <c r="C104" t="s">
+        <v>564</v>
+      </c>
+      <c r="D104" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" t="s">
+        <v>218</v>
+      </c>
+      <c r="F104" t="s">
         <v>565</v>
       </c>
-      <c r="D104" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" t="s">
-        <v>218</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="G104" t="s">
         <v>566</v>
       </c>
-      <c r="G104" t="s">
+      <c r="H104" t="s">
         <v>567</v>
-      </c>
-      <c r="H104" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B105" t="s">
         <v>346</v>
       </c>
       <c r="C105" t="s">
+        <v>569</v>
+      </c>
+      <c r="D105" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" t="s">
+        <v>218</v>
+      </c>
+      <c r="F105" t="s">
         <v>570</v>
       </c>
-      <c r="D105" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" t="s">
-        <v>218</v>
-      </c>
-      <c r="F105" t="s">
+      <c r="G105" t="s">
         <v>571</v>
       </c>
-      <c r="G105" t="s">
+      <c r="H105" t="s">
         <v>572</v>
-      </c>
-      <c r="H105" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B106" t="s">
         <v>335</v>
       </c>
       <c r="C106" t="s">
+        <v>574</v>
+      </c>
+      <c r="D106" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" t="s">
+        <v>218</v>
+      </c>
+      <c r="F106" t="s">
         <v>575</v>
       </c>
-      <c r="D106" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" t="s">
-        <v>218</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="G106" t="s">
         <v>576</v>
       </c>
-      <c r="G106" t="s">
+      <c r="H106" t="s">
         <v>577</v>
-      </c>
-      <c r="H106" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B107" t="s">
         <v>346</v>
       </c>
       <c r="C107" t="s">
+        <v>579</v>
+      </c>
+      <c r="D107" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" t="s">
+        <v>218</v>
+      </c>
+      <c r="F107" t="s">
         <v>580</v>
       </c>
-      <c r="D107" t="s">
-        <v>11</v>
-      </c>
-      <c r="E107" t="s">
-        <v>218</v>
-      </c>
-      <c r="F107" t="s">
+      <c r="G107" t="s">
         <v>581</v>
       </c>
-      <c r="G107" t="s">
+      <c r="H107" t="s">
         <v>582</v>
-      </c>
-      <c r="H107" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B108" t="s">
         <v>335</v>
       </c>
       <c r="C108" t="s">
+        <v>584</v>
+      </c>
+      <c r="D108" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" t="s">
+        <v>218</v>
+      </c>
+      <c r="F108" t="s">
         <v>585</v>
       </c>
-      <c r="D108" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" t="s">
-        <v>218</v>
-      </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>586</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" t="s">
         <v>587</v>
-      </c>
-      <c r="H108" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
+        <v>588</v>
+      </c>
+      <c r="B109" t="s">
         <v>589</v>
       </c>
-      <c r="B109" t="s">
+      <c r="C109" t="s">
         <v>590</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" t="s">
+        <v>218</v>
+      </c>
+      <c r="F109" t="s">
         <v>591</v>
       </c>
-      <c r="D109" t="s">
-        <v>11</v>
-      </c>
-      <c r="E109" t="s">
-        <v>218</v>
-      </c>
-      <c r="F109" t="s">
+      <c r="G109" t="s">
         <v>592</v>
       </c>
-      <c r="G109" t="s">
+      <c r="H109" t="s">
         <v>593</v>
-      </c>
-      <c r="H109" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
+        <v>594</v>
+      </c>
+      <c r="B110" t="s">
         <v>595</v>
       </c>
-      <c r="B110" t="s">
+      <c r="C110" t="s">
         <v>596</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" t="s">
+        <v>218</v>
+      </c>
+      <c r="F110" t="s">
         <v>597</v>
       </c>
-      <c r="D110" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" t="s">
-        <v>218</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="G110" t="s">
         <v>598</v>
       </c>
-      <c r="G110" t="s">
+      <c r="H110" t="s">
         <v>599</v>
-      </c>
-      <c r="H110" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B111" t="s">
         <v>335</v>
       </c>
       <c r="C111" t="s">
+        <v>601</v>
+      </c>
+      <c r="D111" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" t="s">
+        <v>218</v>
+      </c>
+      <c r="F111" t="s">
         <v>602</v>
       </c>
-      <c r="D111" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" t="s">
-        <v>218</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="G111" t="s">
         <v>603</v>
       </c>
-      <c r="G111" t="s">
+      <c r="H111" t="s">
         <v>604</v>
-      </c>
-      <c r="H111" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B112" t="s">
         <v>335</v>
       </c>
       <c r="C112" t="s">
+        <v>606</v>
+      </c>
+      <c r="D112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" t="s">
+        <v>218</v>
+      </c>
+      <c r="F112" t="s">
         <v>607</v>
       </c>
-      <c r="D112" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" t="s">
-        <v>218</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="G112" t="s">
         <v>608</v>
       </c>
-      <c r="G112" t="s">
+      <c r="H112" t="s">
         <v>609</v>
-      </c>
-      <c r="H112" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B113" t="s">
         <v>335</v>
       </c>
       <c r="C113" t="s">
+        <v>611</v>
+      </c>
+      <c r="D113" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" t="s">
+        <v>218</v>
+      </c>
+      <c r="F113" t="s">
         <v>612</v>
       </c>
-      <c r="D113" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" t="s">
-        <v>218</v>
-      </c>
-      <c r="F113" t="s">
+      <c r="G113" t="s">
         <v>613</v>
       </c>
-      <c r="G113" t="s">
+      <c r="H113" t="s">
         <v>614</v>
-      </c>
-      <c r="H113" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>615</v>
+      </c>
+      <c r="B114" t="s">
+        <v>595</v>
+      </c>
+      <c r="C114" t="s">
         <v>616</v>
       </c>
-      <c r="B114" t="s">
-        <v>596</v>
-      </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" t="s">
+        <v>218</v>
+      </c>
+      <c r="F114" t="s">
         <v>617</v>
       </c>
-      <c r="D114" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" t="s">
-        <v>218</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
+        <v>598</v>
+      </c>
+      <c r="H114" t="s">
         <v>618</v>
-      </c>
-      <c r="G114" t="s">
-        <v>599</v>
-      </c>
-      <c r="H114" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>619</v>
+      </c>
+      <c r="B115" t="s">
         <v>620</v>
       </c>
-      <c r="B115" t="s">
+      <c r="C115" t="s">
         <v>621</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" t="s">
+        <v>218</v>
+      </c>
+      <c r="F115" t="s">
         <v>622</v>
       </c>
-      <c r="D115" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" t="s">
-        <v>218</v>
-      </c>
-      <c r="F115" t="s">
+      <c r="G115" t="s">
         <v>623</v>
       </c>
-      <c r="G115" t="s">
+      <c r="H115" t="s">
         <v>624</v>
-      </c>
-      <c r="H115" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>625</v>
+      </c>
+      <c r="B116" t="s">
         <v>626</v>
       </c>
-      <c r="B116" t="s">
+      <c r="C116" t="s">
         <v>627</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" t="s">
+        <v>218</v>
+      </c>
+      <c r="F116" t="s">
         <v>628</v>
       </c>
-      <c r="D116" t="s">
-        <v>11</v>
-      </c>
-      <c r="E116" t="s">
-        <v>218</v>
-      </c>
-      <c r="F116" t="s">
+      <c r="G116" t="s">
         <v>629</v>
       </c>
-      <c r="G116" t="s">
+      <c r="H116" t="s">
         <v>630</v>
-      </c>
-      <c r="H116" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
+        <v>631</v>
+      </c>
+      <c r="B117" t="s">
         <v>632</v>
       </c>
-      <c r="B117" t="s">
+      <c r="C117" t="s">
         <v>633</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" t="s">
+        <v>218</v>
+      </c>
+      <c r="F117" t="s">
         <v>634</v>
       </c>
-      <c r="D117" t="s">
-        <v>11</v>
-      </c>
-      <c r="E117" t="s">
-        <v>218</v>
-      </c>
-      <c r="F117" t="s">
+      <c r="G117" t="s">
         <v>635</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" t="s">
         <v>636</v>
-      </c>
-      <c r="H117" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>637</v>
+      </c>
+      <c r="B118" t="s">
+        <v>620</v>
+      </c>
+      <c r="C118" t="s">
         <v>638</v>
       </c>
-      <c r="B118" t="s">
-        <v>621</v>
-      </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" t="s">
+        <v>218</v>
+      </c>
+      <c r="F118" t="s">
         <v>639</v>
       </c>
-      <c r="D118" t="s">
-        <v>11</v>
-      </c>
-      <c r="E118" t="s">
-        <v>218</v>
-      </c>
-      <c r="F118" t="s">
+      <c r="G118" t="s">
         <v>640</v>
       </c>
-      <c r="G118" t="s">
+      <c r="H118" t="s">
         <v>641</v>
-      </c>
-      <c r="H118" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B119" t="s">
         <v>216</v>
       </c>
       <c r="C119" t="s">
+        <v>643</v>
+      </c>
+      <c r="D119" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" t="s">
+        <v>218</v>
+      </c>
+      <c r="F119" t="s">
         <v>644</v>
       </c>
-      <c r="D119" t="s">
-        <v>11</v>
-      </c>
-      <c r="E119" t="s">
-        <v>218</v>
-      </c>
-      <c r="F119" t="s">
+      <c r="G119" t="s">
         <v>645</v>
       </c>
-      <c r="G119" t="s">
+      <c r="H119" t="s">
         <v>646</v>
-      </c>
-      <c r="H119" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>647</v>
+      </c>
+      <c r="B120" t="s">
         <v>648</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
         <v>649</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" t="s">
+        <v>218</v>
+      </c>
+      <c r="F120" t="s">
         <v>650</v>
       </c>
-      <c r="D120" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" t="s">
-        <v>218</v>
-      </c>
-      <c r="F120" t="s">
+      <c r="G120" t="s">
         <v>651</v>
       </c>
-      <c r="G120" t="s">
+      <c r="H120" t="s">
         <v>652</v>
-      </c>
-      <c r="H120" t="s">
-        <v>653</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B121" t="s">
         <v>335</v>
       </c>
       <c r="C121" t="s">
+        <v>654</v>
+      </c>
+      <c r="D121" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" t="s">
+        <v>218</v>
+      </c>
+      <c r="F121" t="s">
         <v>655</v>
       </c>
-      <c r="D121" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" t="s">
-        <v>218</v>
-      </c>
-      <c r="F121" t="s">
+      <c r="G121" t="s">
         <v>656</v>
       </c>
-      <c r="G121" t="s">
+      <c r="H121" t="s">
         <v>657</v>
-      </c>
-      <c r="H121" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B122" t="s">
         <v>358</v>
       </c>
       <c r="C122" t="s">
+        <v>659</v>
+      </c>
+      <c r="D122" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" t="s">
+        <v>218</v>
+      </c>
+      <c r="F122" t="s">
         <v>660</v>
       </c>
-      <c r="D122" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" t="s">
-        <v>218</v>
-      </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>661</v>
       </c>
-      <c r="G122" t="s">
+      <c r="H122" t="s">
         <v>662</v>
-      </c>
-      <c r="H122" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B123" t="s">
         <v>346</v>
       </c>
       <c r="C123" t="s">
+        <v>664</v>
+      </c>
+      <c r="D123" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" t="s">
+        <v>218</v>
+      </c>
+      <c r="F123" t="s">
         <v>665</v>
       </c>
-      <c r="D123" t="s">
-        <v>11</v>
-      </c>
-      <c r="E123" t="s">
-        <v>218</v>
-      </c>
-      <c r="F123" t="s">
+      <c r="G123" t="s">
         <v>666</v>
       </c>
-      <c r="G123" t="s">
+      <c r="H123" t="s">
         <v>667</v>
-      </c>
-      <c r="H123" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>668</v>
+      </c>
+      <c r="B124" t="s">
+        <v>329</v>
+      </c>
+      <c r="C124" t="s">
         <v>669</v>
       </c>
-      <c r="B124" t="s">
-        <v>426</v>
-      </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" t="s">
+        <v>218</v>
+      </c>
+      <c r="F124" t="s">
         <v>670</v>
       </c>
-      <c r="D124" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" t="s">
-        <v>218</v>
-      </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>671</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>672</v>
-      </c>
-      <c r="H124" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B125" t="s">
         <v>335</v>
       </c>
       <c r="C125" t="s">
+        <v>674</v>
+      </c>
+      <c r="D125" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" t="s">
+        <v>218</v>
+      </c>
+      <c r="F125" t="s">
         <v>675</v>
       </c>
-      <c r="D125" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" t="s">
-        <v>218</v>
-      </c>
-      <c r="F125" t="s">
+      <c r="G125" t="s">
         <v>676</v>
       </c>
-      <c r="G125" t="s">
+      <c r="H125" t="s">
         <v>677</v>
-      </c>
-      <c r="H125" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B126" t="s">
         <v>335</v>
       </c>
       <c r="C126" t="s">
+        <v>679</v>
+      </c>
+      <c r="D126" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" t="s">
+        <v>218</v>
+      </c>
+      <c r="F126" t="s">
         <v>680</v>
       </c>
-      <c r="D126" t="s">
-        <v>11</v>
-      </c>
-      <c r="E126" t="s">
-        <v>218</v>
-      </c>
-      <c r="F126" t="s">
+      <c r="G126" t="s">
         <v>681</v>
       </c>
-      <c r="G126" t="s">
+      <c r="H126" t="s">
         <v>682</v>
-      </c>
-      <c r="H126" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B127" t="s">
         <v>335</v>
       </c>
       <c r="C127" t="s">
+        <v>684</v>
+      </c>
+      <c r="D127" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" t="s">
+        <v>218</v>
+      </c>
+      <c r="F127" t="s">
         <v>685</v>
       </c>
-      <c r="D127" t="s">
-        <v>11</v>
-      </c>
-      <c r="E127" t="s">
-        <v>218</v>
-      </c>
-      <c r="F127" t="s">
+      <c r="G127" t="s">
         <v>686</v>
       </c>
-      <c r="G127" t="s">
+      <c r="H127" t="s">
         <v>687</v>
-      </c>
-      <c r="H127" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>688</v>
+      </c>
+      <c r="B128" t="s">
         <v>689</v>
       </c>
-      <c r="B128" t="s">
+      <c r="C128" t="s">
         <v>690</v>
       </c>
-      <c r="C128" t="s">
+      <c r="D128" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" t="s">
+        <v>218</v>
+      </c>
+      <c r="F128" t="s">
         <v>691</v>
       </c>
-      <c r="D128" t="s">
-        <v>11</v>
-      </c>
-      <c r="E128" t="s">
-        <v>218</v>
-      </c>
-      <c r="F128" t="s">
+      <c r="G128" t="s">
         <v>692</v>
       </c>
-      <c r="G128" t="s">
+      <c r="H128" t="s">
         <v>693</v>
-      </c>
-      <c r="H128" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B129" t="s">
         <v>335</v>
       </c>
       <c r="C129" t="s">
+        <v>695</v>
+      </c>
+      <c r="D129" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" t="s">
+        <v>218</v>
+      </c>
+      <c r="F129" t="s">
         <v>696</v>
       </c>
-      <c r="D129" t="s">
-        <v>11</v>
-      </c>
-      <c r="E129" t="s">
-        <v>218</v>
-      </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
         <v>697</v>
       </c>
-      <c r="G129" t="s">
+      <c r="H129" t="s">
         <v>698</v>
-      </c>
-      <c r="H129" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>699</v>
+      </c>
+      <c r="B130" t="s">
+        <v>689</v>
+      </c>
+      <c r="C130" t="s">
         <v>700</v>
       </c>
-      <c r="B130" t="s">
-        <v>690</v>
-      </c>
-      <c r="C130" t="s">
+      <c r="D130" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" t="s">
+        <v>218</v>
+      </c>
+      <c r="F130" t="s">
         <v>701</v>
       </c>
-      <c r="D130" t="s">
-        <v>11</v>
-      </c>
-      <c r="E130" t="s">
-        <v>218</v>
-      </c>
-      <c r="F130" t="s">
+      <c r="G130" t="s">
         <v>702</v>
       </c>
-      <c r="G130" t="s">
+      <c r="H130" t="s">
         <v>703</v>
-      </c>
-      <c r="H130" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B131" t="s">
         <v>375</v>
       </c>
       <c r="C131" t="s">
+        <v>705</v>
+      </c>
+      <c r="D131" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" t="s">
+        <v>218</v>
+      </c>
+      <c r="F131" t="s">
         <v>706</v>
       </c>
-      <c r="D131" t="s">
-        <v>11</v>
-      </c>
-      <c r="E131" t="s">
-        <v>218</v>
-      </c>
-      <c r="F131" t="s">
+      <c r="G131" t="s">
         <v>707</v>
       </c>
-      <c r="G131" t="s">
+      <c r="H131" t="s">
         <v>708</v>
-      </c>
-      <c r="H131" t="s">
-        <v>709</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>709</v>
+      </c>
+      <c r="B132" t="s">
+        <v>329</v>
+      </c>
+      <c r="C132" t="s">
         <v>710</v>
       </c>
-      <c r="B132" t="s">
-        <v>426</v>
-      </c>
-      <c r="C132" t="s">
+      <c r="D132" t="s">
+        <v>11</v>
+      </c>
+      <c r="E132" t="s">
+        <v>218</v>
+      </c>
+      <c r="F132" t="s">
         <v>711</v>
       </c>
-      <c r="D132" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" t="s">
-        <v>218</v>
-      </c>
-      <c r="F132" t="s">
+      <c r="G132" t="s">
         <v>712</v>
       </c>
-      <c r="G132" t="s">
+      <c r="H132" t="s">
         <v>713</v>
-      </c>
-      <c r="H132" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>714</v>
+      </c>
+      <c r="B133" t="s">
+        <v>329</v>
+      </c>
+      <c r="C133" t="s">
         <v>715</v>
       </c>
-      <c r="B133" t="s">
-        <v>426</v>
-      </c>
-      <c r="C133" t="s">
+      <c r="D133" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" t="s">
+        <v>218</v>
+      </c>
+      <c r="F133" t="s">
         <v>716</v>
       </c>
-      <c r="D133" t="s">
-        <v>11</v>
-      </c>
-      <c r="E133" t="s">
-        <v>218</v>
-      </c>
-      <c r="F133" t="s">
+      <c r="G133" t="s">
+        <v>712</v>
+      </c>
+      <c r="H133" t="s">
         <v>717</v>
-      </c>
-      <c r="G133" t="s">
-        <v>713</v>
-      </c>
-      <c r="H133" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>718</v>
+      </c>
+      <c r="B134" t="s">
+        <v>620</v>
+      </c>
+      <c r="C134" t="s">
         <v>719</v>
       </c>
-      <c r="B134" t="s">
-        <v>621</v>
-      </c>
-      <c r="C134" t="s">
+      <c r="D134" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" t="s">
+        <v>218</v>
+      </c>
+      <c r="F134" t="s">
         <v>720</v>
       </c>
-      <c r="D134" t="s">
-        <v>11</v>
-      </c>
-      <c r="E134" t="s">
-        <v>218</v>
-      </c>
-      <c r="F134" t="s">
+      <c r="G134" t="s">
+        <v>640</v>
+      </c>
+      <c r="H134" t="s">
         <v>721</v>
-      </c>
-      <c r="G134" t="s">
-        <v>641</v>
-      </c>
-      <c r="H134" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>722</v>
+      </c>
+      <c r="B135" t="s">
+        <v>648</v>
+      </c>
+      <c r="C135" t="s">
         <v>723</v>
       </c>
-      <c r="B135" t="s">
-        <v>649</v>
-      </c>
-      <c r="C135" t="s">
+      <c r="D135" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" t="s">
+        <v>218</v>
+      </c>
+      <c r="F135" t="s">
         <v>724</v>
       </c>
-      <c r="D135" t="s">
-        <v>11</v>
-      </c>
-      <c r="E135" t="s">
-        <v>218</v>
-      </c>
-      <c r="F135" t="s">
+      <c r="G135" t="s">
         <v>725</v>
       </c>
-      <c r="G135" t="s">
+      <c r="H135" t="s">
         <v>726</v>
-      </c>
-      <c r="H135" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>727</v>
+      </c>
+      <c r="B136" t="s">
+        <v>329</v>
+      </c>
+      <c r="C136" t="s">
         <v>728</v>
       </c>
-      <c r="B136" t="s">
-        <v>426</v>
-      </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" t="s">
+        <v>218</v>
+      </c>
+      <c r="F136" t="s">
         <v>729</v>
       </c>
-      <c r="D136" t="s">
-        <v>11</v>
-      </c>
-      <c r="E136" t="s">
-        <v>218</v>
-      </c>
-      <c r="F136" t="s">
+      <c r="G136" t="s">
         <v>730</v>
       </c>
-      <c r="G136" t="s">
+      <c r="H136" t="s">
         <v>731</v>
-      </c>
-      <c r="H136" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B137" t="s">
         <v>346</v>
       </c>
       <c r="C137" t="s">
+        <v>733</v>
+      </c>
+      <c r="D137" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" t="s">
+        <v>218</v>
+      </c>
+      <c r="F137" t="s">
         <v>734</v>
       </c>
-      <c r="D137" t="s">
-        <v>11</v>
-      </c>
-      <c r="E137" t="s">
-        <v>218</v>
-      </c>
-      <c r="F137" t="s">
+      <c r="G137" t="s">
         <v>735</v>
       </c>
-      <c r="G137" t="s">
+      <c r="H137" t="s">
         <v>736</v>
-      </c>
-      <c r="H137" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B138" t="s">
         <v>335</v>
       </c>
       <c r="C138" t="s">
+        <v>738</v>
+      </c>
+      <c r="D138" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" t="s">
+        <v>218</v>
+      </c>
+      <c r="F138" t="s">
         <v>739</v>
       </c>
-      <c r="D138" t="s">
-        <v>11</v>
-      </c>
-      <c r="E138" t="s">
-        <v>218</v>
-      </c>
-      <c r="F138" t="s">
+      <c r="G138" t="s">
         <v>740</v>
       </c>
-      <c r="G138" t="s">
+      <c r="H138" t="s">
         <v>741</v>
-      </c>
-      <c r="H138" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B139" t="s">
         <v>335</v>
       </c>
       <c r="C139" t="s">
+        <v>743</v>
+      </c>
+      <c r="D139" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" t="s">
+        <v>218</v>
+      </c>
+      <c r="F139" t="s">
         <v>744</v>
       </c>
-      <c r="D139" t="s">
-        <v>11</v>
-      </c>
-      <c r="E139" t="s">
-        <v>218</v>
-      </c>
-      <c r="F139" t="s">
+      <c r="G139" t="s">
         <v>745</v>
       </c>
-      <c r="G139" t="s">
+      <c r="H139" t="s">
         <v>746</v>
-      </c>
-      <c r="H139" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B140" t="s">
         <v>216</v>
       </c>
       <c r="C140" t="s">
+        <v>748</v>
+      </c>
+      <c r="D140" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" t="s">
+        <v>218</v>
+      </c>
+      <c r="F140" t="s">
         <v>749</v>
       </c>
-      <c r="D140" t="s">
-        <v>11</v>
-      </c>
-      <c r="E140" t="s">
-        <v>218</v>
-      </c>
-      <c r="F140" t="s">
+      <c r="G140" t="s">
         <v>750</v>
       </c>
-      <c r="G140" t="s">
+      <c r="H140" t="s">
         <v>751</v>
-      </c>
-      <c r="H140" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B141" t="s">
         <v>335</v>
       </c>
       <c r="C141" t="s">
+        <v>753</v>
+      </c>
+      <c r="D141" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" t="s">
+        <v>218</v>
+      </c>
+      <c r="F141" t="s">
         <v>754</v>
       </c>
-      <c r="D141" t="s">
-        <v>11</v>
-      </c>
-      <c r="E141" t="s">
-        <v>218</v>
-      </c>
-      <c r="F141" t="s">
+      <c r="G141" t="s">
         <v>755</v>
       </c>
-      <c r="G141" t="s">
+      <c r="H141" t="s">
         <v>756</v>
-      </c>
-      <c r="H141" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B142" t="s">
         <v>335</v>
       </c>
       <c r="C142" t="s">
+        <v>758</v>
+      </c>
+      <c r="D142" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" t="s">
+        <v>218</v>
+      </c>
+      <c r="F142" t="s">
         <v>759</v>
       </c>
-      <c r="D142" t="s">
-        <v>11</v>
-      </c>
-      <c r="E142" t="s">
-        <v>218</v>
-      </c>
-      <c r="F142" t="s">
+      <c r="G142" t="s">
         <v>760</v>
       </c>
-      <c r="G142" t="s">
+      <c r="H142" t="s">
         <v>761</v>
-      </c>
-      <c r="H142" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>762</v>
+      </c>
+      <c r="B143" t="s">
+        <v>626</v>
+      </c>
+      <c r="C143" t="s">
         <v>763</v>
       </c>
-      <c r="B143" t="s">
-        <v>627</v>
-      </c>
-      <c r="C143" t="s">
+      <c r="D143" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" t="s">
+        <v>218</v>
+      </c>
+      <c r="F143" t="s">
         <v>764</v>
       </c>
-      <c r="D143" t="s">
-        <v>11</v>
-      </c>
-      <c r="E143" t="s">
-        <v>218</v>
-      </c>
-      <c r="F143" t="s">
+      <c r="G143" t="s">
         <v>765</v>
       </c>
-      <c r="G143" t="s">
+      <c r="H143" t="s">
         <v>766</v>
-      </c>
-      <c r="H143" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>767</v>
+      </c>
+      <c r="B144" t="s">
+        <v>329</v>
+      </c>
+      <c r="C144" t="s">
         <v>768</v>
       </c>
-      <c r="B144" t="s">
-        <v>426</v>
-      </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" t="s">
+        <v>218</v>
+      </c>
+      <c r="F144" t="s">
         <v>769</v>
       </c>
-      <c r="D144" t="s">
-        <v>11</v>
-      </c>
-      <c r="E144" t="s">
-        <v>218</v>
-      </c>
-      <c r="F144" t="s">
+      <c r="G144" t="s">
         <v>770</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" t="s">
         <v>771</v>
-      </c>
-      <c r="H144" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B145" t="s">
         <v>216</v>
       </c>
       <c r="C145" t="s">
+        <v>773</v>
+      </c>
+      <c r="D145" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" t="s">
+        <v>218</v>
+      </c>
+      <c r="F145" t="s">
         <v>774</v>
       </c>
-      <c r="D145" t="s">
-        <v>11</v>
-      </c>
-      <c r="E145" t="s">
-        <v>218</v>
-      </c>
-      <c r="F145" t="s">
+      <c r="G145" t="s">
         <v>775</v>
       </c>
-      <c r="G145" t="s">
+      <c r="H145" t="s">
         <v>776</v>
-      </c>
-      <c r="H145" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>777</v>
+      </c>
+      <c r="B146" t="s">
         <v>778</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" t="s">
         <v>779</v>
       </c>
-      <c r="C146" t="s">
+      <c r="D146" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" t="s">
+        <v>218</v>
+      </c>
+      <c r="F146" t="s">
         <v>780</v>
       </c>
-      <c r="D146" t="s">
-        <v>11</v>
-      </c>
-      <c r="E146" t="s">
-        <v>218</v>
-      </c>
-      <c r="F146" t="s">
+      <c r="G146" t="s">
         <v>781</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" t="s">
         <v>782</v>
-      </c>
-      <c r="H146" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>783</v>
+      </c>
+      <c r="B147" t="s">
+        <v>329</v>
+      </c>
+      <c r="C147" t="s">
         <v>784</v>
       </c>
-      <c r="B147" t="s">
-        <v>426</v>
-      </c>
-      <c r="C147" t="s">
+      <c r="D147" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" t="s">
+        <v>218</v>
+      </c>
+      <c r="F147" t="s">
         <v>785</v>
       </c>
-      <c r="D147" t="s">
-        <v>11</v>
-      </c>
-      <c r="E147" t="s">
-        <v>218</v>
-      </c>
-      <c r="F147" t="s">
+      <c r="G147" t="s">
         <v>786</v>
       </c>
-      <c r="G147" t="s">
+      <c r="H147" t="s">
         <v>787</v>
-      </c>
-      <c r="H147" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B148" t="s">
         <v>346</v>
       </c>
       <c r="C148" t="s">
+        <v>789</v>
+      </c>
+      <c r="D148" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" t="s">
+        <v>218</v>
+      </c>
+      <c r="F148" t="s">
         <v>790</v>
       </c>
-      <c r="D148" t="s">
-        <v>11</v>
-      </c>
-      <c r="E148" t="s">
-        <v>218</v>
-      </c>
-      <c r="F148" t="s">
+      <c r="G148" t="s">
         <v>791</v>
       </c>
-      <c r="G148" t="s">
+      <c r="H148" t="s">
         <v>792</v>
-      </c>
-      <c r="H148" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>793</v>
+      </c>
+      <c r="B149" t="s">
         <v>794</v>
       </c>
-      <c r="B149" t="s">
+      <c r="C149" t="s">
         <v>795</v>
       </c>
-      <c r="C149" t="s">
+      <c r="D149" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" t="s">
+        <v>218</v>
+      </c>
+      <c r="F149" t="s">
         <v>796</v>
       </c>
-      <c r="D149" t="s">
-        <v>11</v>
-      </c>
-      <c r="E149" t="s">
-        <v>218</v>
-      </c>
-      <c r="F149" t="s">
+      <c r="G149" t="s">
         <v>797</v>
       </c>
-      <c r="G149" t="s">
+      <c r="H149" t="s">
         <v>798</v>
-      </c>
-      <c r="H149" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>799</v>
+      </c>
+      <c r="B150" t="s">
         <v>800</v>
       </c>
-      <c r="B150" t="s">
+      <c r="C150" t="s">
         <v>801</v>
       </c>
-      <c r="C150" t="s">
+      <c r="D150" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" t="s">
+        <v>218</v>
+      </c>
+      <c r="F150" t="s">
         <v>802</v>
       </c>
-      <c r="D150" t="s">
-        <v>11</v>
-      </c>
-      <c r="E150" t="s">
-        <v>218</v>
-      </c>
-      <c r="F150" t="s">
+      <c r="G150" t="s">
         <v>803</v>
       </c>
-      <c r="G150" t="s">
+      <c r="H150" t="s">
         <v>804</v>
-      </c>
-      <c r="H150" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>805</v>
+      </c>
+      <c r="B151" t="s">
         <v>806</v>
       </c>
-      <c r="B151" t="s">
+      <c r="C151" t="s">
         <v>807</v>
       </c>
-      <c r="C151" t="s">
+      <c r="D151" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" t="s">
+        <v>218</v>
+      </c>
+      <c r="F151" t="s">
         <v>808</v>
       </c>
-      <c r="D151" t="s">
-        <v>11</v>
-      </c>
-      <c r="E151" t="s">
-        <v>218</v>
-      </c>
-      <c r="F151" t="s">
+      <c r="G151" t="s">
         <v>809</v>
       </c>
-      <c r="G151" t="s">
+      <c r="H151" t="s">
         <v>810</v>
-      </c>
-      <c r="H151" t="s">
-        <v>811</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>811</v>
+      </c>
+      <c r="B152" t="s">
         <v>812</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
         <v>813</v>
       </c>
-      <c r="C152" t="s">
+      <c r="D152" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" t="s">
+        <v>218</v>
+      </c>
+      <c r="F152" t="s">
         <v>814</v>
       </c>
-      <c r="D152" t="s">
-        <v>11</v>
-      </c>
-      <c r="E152" t="s">
-        <v>218</v>
-      </c>
-      <c r="F152" t="s">
+      <c r="G152" t="s">
         <v>815</v>
       </c>
-      <c r="G152" t="s">
+      <c r="H152" t="s">
         <v>816</v>
-      </c>
-      <c r="H152" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>817</v>
+      </c>
+      <c r="B153" t="s">
         <v>818</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" t="s">
         <v>819</v>
       </c>
-      <c r="C153" t="s">
+      <c r="D153" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" t="s">
+        <v>218</v>
+      </c>
+      <c r="F153" t="s">
         <v>820</v>
       </c>
-      <c r="D153" t="s">
-        <v>11</v>
-      </c>
-      <c r="E153" t="s">
-        <v>218</v>
-      </c>
-      <c r="F153" t="s">
+      <c r="G153" t="s">
         <v>821</v>
       </c>
-      <c r="G153" t="s">
+      <c r="H153" t="s">
         <v>822</v>
-      </c>
-      <c r="H153" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B154" t="s">
         <v>137</v>
       </c>
       <c r="C154" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D154" t="s">
         <v>11</v>
@@ -7877,24 +7874,24 @@
         <v>19</v>
       </c>
       <c r="F154" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="G154" t="s">
         <v>262</v>
       </c>
       <c r="H154" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B155" t="s">
         <v>137</v>
       </c>
       <c r="C155" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D155" t="s">
         <v>11</v>
@@ -7903,50 +7900,50 @@
         <v>19</v>
       </c>
       <c r="F155" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="G155" t="s">
         <v>262</v>
       </c>
       <c r="H155" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
+        <v>831</v>
+      </c>
+      <c r="B156" t="s">
+        <v>812</v>
+      </c>
+      <c r="C156" t="s">
         <v>832</v>
       </c>
-      <c r="B156" t="s">
-        <v>813</v>
-      </c>
-      <c r="C156" t="s">
+      <c r="D156" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" t="s">
+        <v>218</v>
+      </c>
+      <c r="F156" t="s">
         <v>833</v>
       </c>
-      <c r="D156" t="s">
-        <v>11</v>
-      </c>
-      <c r="E156" t="s">
-        <v>218</v>
-      </c>
-      <c r="F156" t="s">
+      <c r="G156" t="s">
         <v>834</v>
       </c>
-      <c r="G156" t="s">
+      <c r="H156" t="s">
         <v>835</v>
-      </c>
-      <c r="H156" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B157" t="s">
         <v>137</v>
       </c>
       <c r="C157" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D157" t="s">
         <v>11</v>
@@ -7955,50 +7952,50 @@
         <v>19</v>
       </c>
       <c r="F157" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G157" t="s">
         <v>262</v>
       </c>
       <c r="H157" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
+        <v>840</v>
+      </c>
+      <c r="B158" t="s">
+        <v>806</v>
+      </c>
+      <c r="C158" t="s">
         <v>841</v>
       </c>
-      <c r="B158" t="s">
-        <v>807</v>
-      </c>
-      <c r="C158" t="s">
+      <c r="D158" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" t="s">
+        <v>218</v>
+      </c>
+      <c r="F158" t="s">
         <v>842</v>
       </c>
-      <c r="D158" t="s">
-        <v>11</v>
-      </c>
-      <c r="E158" t="s">
-        <v>218</v>
-      </c>
-      <c r="F158" t="s">
+      <c r="G158" t="s">
         <v>843</v>
       </c>
-      <c r="G158" t="s">
+      <c r="H158" t="s">
         <v>844</v>
-      </c>
-      <c r="H158" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B159" t="s">
         <v>137</v>
       </c>
       <c r="C159" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D159" t="s">
         <v>11</v>
@@ -8007,24 +8004,24 @@
         <v>19</v>
       </c>
       <c r="F159" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G159" t="s">
         <v>262</v>
       </c>
       <c r="H159" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B160" t="s">
         <v>137</v>
       </c>
       <c r="C160" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D160" t="s">
         <v>11</v>
@@ -8033,24 +8030,24 @@
         <v>19</v>
       </c>
       <c r="F160" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="G160" t="s">
         <v>262</v>
       </c>
       <c r="H160" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B161" t="s">
         <v>137</v>
       </c>
       <c r="C161" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D161" t="s">
         <v>11</v>
@@ -8059,76 +8056,76 @@
         <v>19</v>
       </c>
       <c r="F161" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="G161" t="s">
         <v>262</v>
       </c>
       <c r="H161" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>857</v>
+      </c>
+      <c r="B162" t="s">
         <v>858</v>
       </c>
-      <c r="B162" t="s">
+      <c r="C162" t="s">
         <v>859</v>
       </c>
-      <c r="C162" t="s">
+      <c r="D162" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" t="s">
+        <v>218</v>
+      </c>
+      <c r="F162" t="s">
         <v>860</v>
       </c>
-      <c r="D162" t="s">
-        <v>11</v>
-      </c>
-      <c r="E162" t="s">
-        <v>218</v>
-      </c>
-      <c r="F162" t="s">
+      <c r="G162" t="s">
         <v>861</v>
       </c>
-      <c r="G162" t="s">
+      <c r="H162" t="s">
         <v>862</v>
-      </c>
-      <c r="H162" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
+        <v>863</v>
+      </c>
+      <c r="B163" t="s">
+        <v>812</v>
+      </c>
+      <c r="C163" t="s">
         <v>864</v>
       </c>
-      <c r="B163" t="s">
-        <v>813</v>
-      </c>
-      <c r="C163" t="s">
+      <c r="D163" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" t="s">
+        <v>218</v>
+      </c>
+      <c r="F163" t="s">
         <v>865</v>
       </c>
-      <c r="D163" t="s">
-        <v>11</v>
-      </c>
-      <c r="E163" t="s">
-        <v>218</v>
-      </c>
-      <c r="F163" t="s">
+      <c r="G163" t="s">
         <v>866</v>
       </c>
-      <c r="G163" t="s">
+      <c r="H163" t="s">
         <v>867</v>
-      </c>
-      <c r="H163" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B164" t="s">
         <v>137</v>
       </c>
       <c r="C164" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D164" t="s">
         <v>11</v>
@@ -8137,232 +8134,232 @@
         <v>19</v>
       </c>
       <c r="F164" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G164" t="s">
         <v>262</v>
       </c>
       <c r="H164" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
+        <v>872</v>
+      </c>
+      <c r="B165" t="s">
+        <v>648</v>
+      </c>
+      <c r="C165" t="s">
         <v>873</v>
       </c>
-      <c r="B165" t="s">
-        <v>649</v>
-      </c>
-      <c r="C165" t="s">
+      <c r="D165" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" t="s">
+        <v>218</v>
+      </c>
+      <c r="F165" t="s">
         <v>874</v>
       </c>
-      <c r="D165" t="s">
-        <v>11</v>
-      </c>
-      <c r="E165" t="s">
-        <v>218</v>
-      </c>
-      <c r="F165" t="s">
+      <c r="G165" t="s">
         <v>875</v>
       </c>
-      <c r="G165" t="s">
+      <c r="H165" t="s">
         <v>876</v>
-      </c>
-      <c r="H165" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B166" t="s">
         <v>375</v>
       </c>
       <c r="C166" t="s">
+        <v>878</v>
+      </c>
+      <c r="D166" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" t="s">
+        <v>218</v>
+      </c>
+      <c r="F166" t="s">
         <v>879</v>
       </c>
-      <c r="D166" t="s">
-        <v>11</v>
-      </c>
-      <c r="E166" t="s">
-        <v>218</v>
-      </c>
-      <c r="F166" t="s">
+      <c r="G166" t="s">
         <v>880</v>
       </c>
-      <c r="G166" t="s">
+      <c r="H166" t="s">
         <v>881</v>
-      </c>
-      <c r="H166" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B167" t="s">
         <v>346</v>
       </c>
       <c r="C167" t="s">
+        <v>883</v>
+      </c>
+      <c r="D167" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" t="s">
+        <v>218</v>
+      </c>
+      <c r="F167" t="s">
         <v>884</v>
       </c>
-      <c r="D167" t="s">
-        <v>11</v>
-      </c>
-      <c r="E167" t="s">
-        <v>218</v>
-      </c>
-      <c r="F167" t="s">
+      <c r="G167" t="s">
         <v>885</v>
       </c>
-      <c r="G167" t="s">
+      <c r="H167" t="s">
         <v>886</v>
-      </c>
-      <c r="H167" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B168" t="s">
         <v>346</v>
       </c>
       <c r="C168" t="s">
+        <v>888</v>
+      </c>
+      <c r="D168" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" t="s">
+        <v>218</v>
+      </c>
+      <c r="F168" t="s">
         <v>889</v>
       </c>
-      <c r="D168" t="s">
-        <v>11</v>
-      </c>
-      <c r="E168" t="s">
-        <v>218</v>
-      </c>
-      <c r="F168" t="s">
+      <c r="G168" t="s">
         <v>890</v>
       </c>
-      <c r="G168" t="s">
+      <c r="H168" t="s">
         <v>891</v>
-      </c>
-      <c r="H168" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B169" t="s">
         <v>352</v>
       </c>
       <c r="C169" t="s">
+        <v>893</v>
+      </c>
+      <c r="D169" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" t="s">
+        <v>218</v>
+      </c>
+      <c r="F169" t="s">
         <v>894</v>
       </c>
-      <c r="D169" t="s">
-        <v>11</v>
-      </c>
-      <c r="E169" t="s">
-        <v>218</v>
-      </c>
-      <c r="F169" t="s">
+      <c r="G169" t="s">
         <v>895</v>
       </c>
-      <c r="G169" t="s">
+      <c r="H169" t="s">
         <v>896</v>
-      </c>
-      <c r="H169" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
+        <v>897</v>
+      </c>
+      <c r="B170" t="s">
+        <v>648</v>
+      </c>
+      <c r="C170" t="s">
         <v>898</v>
       </c>
-      <c r="B170" t="s">
-        <v>649</v>
-      </c>
-      <c r="C170" t="s">
+      <c r="D170" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" t="s">
+        <v>218</v>
+      </c>
+      <c r="F170" t="s">
         <v>899</v>
       </c>
-      <c r="D170" t="s">
-        <v>11</v>
-      </c>
-      <c r="E170" t="s">
-        <v>218</v>
-      </c>
-      <c r="F170" t="s">
+      <c r="G170" t="s">
         <v>900</v>
       </c>
-      <c r="G170" t="s">
+      <c r="H170" t="s">
         <v>901</v>
-      </c>
-      <c r="H170" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
+        <v>902</v>
+      </c>
+      <c r="B171" t="s">
+        <v>812</v>
+      </c>
+      <c r="C171" t="s">
         <v>903</v>
       </c>
-      <c r="B171" t="s">
-        <v>813</v>
-      </c>
-      <c r="C171" t="s">
+      <c r="D171" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" t="s">
+        <v>218</v>
+      </c>
+      <c r="F171" t="s">
         <v>904</v>
       </c>
-      <c r="D171" t="s">
-        <v>11</v>
-      </c>
-      <c r="E171" t="s">
-        <v>218</v>
-      </c>
-      <c r="F171" t="s">
+      <c r="G171" t="s">
         <v>905</v>
       </c>
-      <c r="G171" t="s">
+      <c r="H171" t="s">
         <v>906</v>
-      </c>
-      <c r="H171" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
+        <v>907</v>
+      </c>
+      <c r="B172" t="s">
+        <v>800</v>
+      </c>
+      <c r="C172" t="s">
         <v>908</v>
       </c>
-      <c r="B172" t="s">
-        <v>801</v>
-      </c>
-      <c r="C172" t="s">
+      <c r="D172" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" t="s">
+        <v>218</v>
+      </c>
+      <c r="F172" t="s">
         <v>909</v>
       </c>
-      <c r="D172" t="s">
-        <v>11</v>
-      </c>
-      <c r="E172" t="s">
-        <v>218</v>
-      </c>
-      <c r="F172" t="s">
+      <c r="G172" t="s">
         <v>910</v>
       </c>
-      <c r="G172" t="s">
+      <c r="H172" t="s">
         <v>911</v>
-      </c>
-      <c r="H172" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B173" t="s">
         <v>223</v>
       </c>
       <c r="C173" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D173" t="s">
         <v>11</v>
@@ -8371,102 +8368,102 @@
         <v>19</v>
       </c>
       <c r="F173" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G173" t="s">
         <v>272</v>
       </c>
       <c r="H173" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>916</v>
+      </c>
+      <c r="B174" t="s">
+        <v>794</v>
+      </c>
+      <c r="C174" t="s">
         <v>917</v>
       </c>
-      <c r="B174" t="s">
-        <v>795</v>
-      </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" t="s">
+        <v>218</v>
+      </c>
+      <c r="F174" t="s">
         <v>918</v>
       </c>
-      <c r="D174" t="s">
-        <v>11</v>
-      </c>
-      <c r="E174" t="s">
-        <v>218</v>
-      </c>
-      <c r="F174" t="s">
+      <c r="G174" t="s">
         <v>919</v>
       </c>
-      <c r="G174" t="s">
+      <c r="H174" t="s">
         <v>920</v>
-      </c>
-      <c r="H174" t="s">
-        <v>921</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>921</v>
+      </c>
+      <c r="B175" t="s">
+        <v>794</v>
+      </c>
+      <c r="C175" t="s">
         <v>922</v>
       </c>
-      <c r="B175" t="s">
-        <v>795</v>
-      </c>
-      <c r="C175" t="s">
+      <c r="D175" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" t="s">
+        <v>218</v>
+      </c>
+      <c r="F175" t="s">
         <v>923</v>
       </c>
-      <c r="D175" t="s">
-        <v>11</v>
-      </c>
-      <c r="E175" t="s">
-        <v>218</v>
-      </c>
-      <c r="F175" t="s">
+      <c r="G175" t="s">
         <v>924</v>
       </c>
-      <c r="G175" t="s">
+      <c r="H175" t="s">
         <v>925</v>
-      </c>
-      <c r="H175" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>926</v>
+      </c>
+      <c r="B176" t="s">
+        <v>794</v>
+      </c>
+      <c r="C176" t="s">
         <v>927</v>
       </c>
-      <c r="B176" t="s">
-        <v>795</v>
-      </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" t="s">
+        <v>218</v>
+      </c>
+      <c r="F176" t="s">
         <v>928</v>
       </c>
-      <c r="D176" t="s">
-        <v>11</v>
-      </c>
-      <c r="E176" t="s">
-        <v>218</v>
-      </c>
-      <c r="F176" t="s">
+      <c r="G176" t="s">
         <v>929</v>
       </c>
-      <c r="G176" t="s">
+      <c r="H176" t="s">
         <v>930</v>
-      </c>
-      <c r="H176" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B177" t="s">
         <v>223</v>
       </c>
       <c r="C177" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="D177" t="s">
         <v>11</v>
@@ -8475,336 +8472,336 @@
         <v>19</v>
       </c>
       <c r="F177" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G177" t="s">
         <v>272</v>
       </c>
       <c r="H177" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>935</v>
+      </c>
+      <c r="B178" t="s">
         <v>936</v>
       </c>
-      <c r="B178" t="s">
+      <c r="C178" t="s">
         <v>937</v>
       </c>
-      <c r="C178" t="s">
+      <c r="D178" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" t="s">
+        <v>218</v>
+      </c>
+      <c r="F178" t="s">
         <v>938</v>
       </c>
-      <c r="D178" t="s">
-        <v>11</v>
-      </c>
-      <c r="E178" t="s">
-        <v>218</v>
-      </c>
-      <c r="F178" t="s">
+      <c r="G178" t="s">
         <v>939</v>
       </c>
-      <c r="G178" t="s">
+      <c r="H178" t="s">
         <v>940</v>
-      </c>
-      <c r="H178" t="s">
-        <v>941</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>941</v>
+      </c>
+      <c r="B179" t="s">
+        <v>794</v>
+      </c>
+      <c r="C179" t="s">
         <v>942</v>
       </c>
-      <c r="B179" t="s">
-        <v>795</v>
-      </c>
-      <c r="C179" t="s">
+      <c r="D179" t="s">
+        <v>11</v>
+      </c>
+      <c r="E179" t="s">
+        <v>218</v>
+      </c>
+      <c r="F179" t="s">
         <v>943</v>
       </c>
-      <c r="D179" t="s">
-        <v>11</v>
-      </c>
-      <c r="E179" t="s">
-        <v>218</v>
-      </c>
-      <c r="F179" t="s">
+      <c r="G179" t="s">
         <v>944</v>
       </c>
-      <c r="G179" t="s">
+      <c r="H179" t="s">
         <v>945</v>
-      </c>
-      <c r="H179" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
+        <v>946</v>
+      </c>
+      <c r="B180" t="s">
+        <v>936</v>
+      </c>
+      <c r="C180" t="s">
         <v>947</v>
       </c>
-      <c r="B180" t="s">
-        <v>937</v>
-      </c>
-      <c r="C180" t="s">
+      <c r="D180" t="s">
+        <v>11</v>
+      </c>
+      <c r="E180" t="s">
+        <v>218</v>
+      </c>
+      <c r="F180" t="s">
         <v>948</v>
       </c>
-      <c r="D180" t="s">
-        <v>11</v>
-      </c>
-      <c r="E180" t="s">
-        <v>218</v>
-      </c>
-      <c r="F180" t="s">
+      <c r="G180" t="s">
         <v>949</v>
       </c>
-      <c r="G180" t="s">
+      <c r="H180" t="s">
         <v>950</v>
-      </c>
-      <c r="H180" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>951</v>
+      </c>
+      <c r="B181" t="s">
         <v>952</v>
       </c>
-      <c r="B181" t="s">
+      <c r="C181" t="s">
         <v>953</v>
       </c>
-      <c r="C181" t="s">
+      <c r="D181" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" t="s">
+        <v>218</v>
+      </c>
+      <c r="F181" t="s">
         <v>954</v>
       </c>
-      <c r="D181" t="s">
-        <v>11</v>
-      </c>
-      <c r="E181" t="s">
-        <v>218</v>
-      </c>
-      <c r="F181" t="s">
+      <c r="G181" t="s">
         <v>955</v>
       </c>
-      <c r="G181" t="s">
+      <c r="H181" t="s">
         <v>956</v>
-      </c>
-      <c r="H181" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>957</v>
+      </c>
+      <c r="B182" t="s">
+        <v>794</v>
+      </c>
+      <c r="C182" t="s">
         <v>958</v>
       </c>
-      <c r="B182" t="s">
-        <v>795</v>
-      </c>
-      <c r="C182" t="s">
+      <c r="D182" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" t="s">
+        <v>218</v>
+      </c>
+      <c r="F182" t="s">
         <v>959</v>
       </c>
-      <c r="D182" t="s">
-        <v>11</v>
-      </c>
-      <c r="E182" t="s">
-        <v>218</v>
-      </c>
-      <c r="F182" t="s">
+      <c r="G182" t="s">
         <v>960</v>
       </c>
-      <c r="G182" t="s">
+      <c r="H182" t="s">
         <v>961</v>
-      </c>
-      <c r="H182" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>962</v>
+      </c>
+      <c r="B183" t="s">
+        <v>806</v>
+      </c>
+      <c r="C183" t="s">
         <v>963</v>
       </c>
-      <c r="B183" t="s">
-        <v>807</v>
-      </c>
-      <c r="C183" t="s">
+      <c r="D183" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" t="s">
+        <v>218</v>
+      </c>
+      <c r="F183" t="s">
         <v>964</v>
       </c>
-      <c r="D183" t="s">
-        <v>11</v>
-      </c>
-      <c r="E183" t="s">
-        <v>218</v>
-      </c>
-      <c r="F183" t="s">
+      <c r="G183" t="s">
         <v>965</v>
       </c>
-      <c r="G183" t="s">
+      <c r="H183" t="s">
         <v>966</v>
-      </c>
-      <c r="H183" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
+        <v>967</v>
+      </c>
+      <c r="B184" t="s">
+        <v>794</v>
+      </c>
+      <c r="C184" t="s">
         <v>968</v>
       </c>
-      <c r="B184" t="s">
-        <v>795</v>
-      </c>
-      <c r="C184" t="s">
+      <c r="D184" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" t="s">
+        <v>218</v>
+      </c>
+      <c r="F184" t="s">
         <v>969</v>
       </c>
-      <c r="D184" t="s">
-        <v>11</v>
-      </c>
-      <c r="E184" t="s">
-        <v>218</v>
-      </c>
-      <c r="F184" t="s">
+      <c r="G184" t="s">
         <v>970</v>
       </c>
-      <c r="G184" t="s">
+      <c r="H184" t="s">
         <v>971</v>
-      </c>
-      <c r="H184" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
+        <v>972</v>
+      </c>
+      <c r="B185" t="s">
+        <v>800</v>
+      </c>
+      <c r="C185" t="s">
         <v>973</v>
       </c>
-      <c r="B185" t="s">
-        <v>801</v>
-      </c>
-      <c r="C185" t="s">
+      <c r="D185" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" t="s">
+        <v>218</v>
+      </c>
+      <c r="F185" t="s">
         <v>974</v>
       </c>
-      <c r="D185" t="s">
-        <v>11</v>
-      </c>
-      <c r="E185" t="s">
-        <v>218</v>
-      </c>
-      <c r="F185" t="s">
+      <c r="G185" t="s">
         <v>975</v>
       </c>
-      <c r="G185" t="s">
+      <c r="H185" t="s">
         <v>976</v>
-      </c>
-      <c r="H185" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
+        <v>977</v>
+      </c>
+      <c r="B186" t="s">
+        <v>936</v>
+      </c>
+      <c r="C186" t="s">
         <v>978</v>
       </c>
-      <c r="B186" t="s">
-        <v>937</v>
-      </c>
-      <c r="C186" t="s">
+      <c r="D186" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" t="s">
+        <v>218</v>
+      </c>
+      <c r="F186" t="s">
         <v>979</v>
       </c>
-      <c r="D186" t="s">
-        <v>11</v>
-      </c>
-      <c r="E186" t="s">
-        <v>218</v>
-      </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>980</v>
       </c>
-      <c r="G186" t="s">
+      <c r="H186" t="s">
         <v>981</v>
-      </c>
-      <c r="H186" t="s">
-        <v>982</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
+        <v>982</v>
+      </c>
+      <c r="B187" t="s">
+        <v>794</v>
+      </c>
+      <c r="C187" t="s">
         <v>983</v>
       </c>
-      <c r="B187" t="s">
-        <v>795</v>
-      </c>
-      <c r="C187" t="s">
+      <c r="D187" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" t="s">
+        <v>218</v>
+      </c>
+      <c r="F187" t="s">
         <v>984</v>
       </c>
-      <c r="D187" t="s">
-        <v>11</v>
-      </c>
-      <c r="E187" t="s">
-        <v>218</v>
-      </c>
-      <c r="F187" t="s">
+      <c r="G187" t="s">
         <v>985</v>
       </c>
-      <c r="G187" t="s">
+      <c r="H187" t="s">
         <v>986</v>
-      </c>
-      <c r="H187" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>987</v>
+      </c>
+      <c r="B188" t="s">
+        <v>936</v>
+      </c>
+      <c r="C188" t="s">
         <v>988</v>
       </c>
-      <c r="B188" t="s">
-        <v>937</v>
-      </c>
-      <c r="C188" t="s">
+      <c r="D188" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" t="s">
+        <v>218</v>
+      </c>
+      <c r="F188" t="s">
         <v>989</v>
       </c>
-      <c r="D188" t="s">
-        <v>11</v>
-      </c>
-      <c r="E188" t="s">
-        <v>218</v>
-      </c>
-      <c r="F188" t="s">
+      <c r="G188" t="s">
         <v>990</v>
       </c>
-      <c r="G188" t="s">
+      <c r="H188" t="s">
         <v>991</v>
-      </c>
-      <c r="H188" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>992</v>
+      </c>
+      <c r="B189" t="s">
         <v>993</v>
       </c>
-      <c r="B189" t="s">
+      <c r="C189" t="s">
         <v>994</v>
       </c>
-      <c r="C189" t="s">
+      <c r="D189" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" t="s">
+        <v>218</v>
+      </c>
+      <c r="F189" t="s">
         <v>995</v>
       </c>
-      <c r="D189" t="s">
-        <v>11</v>
-      </c>
-      <c r="E189" t="s">
-        <v>218</v>
-      </c>
-      <c r="F189" t="s">
+      <c r="G189" t="s">
         <v>996</v>
       </c>
-      <c r="G189" t="s">
+      <c r="H189" t="s">
         <v>997</v>
-      </c>
-      <c r="H189" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B190" t="s">
         <v>223</v>
       </c>
       <c r="C190" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="D190" t="s">
         <v>11</v>
@@ -8813,180 +8810,180 @@
         <v>19</v>
       </c>
       <c r="F190" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G190" t="s">
         <v>272</v>
       </c>
       <c r="H190" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B191" t="s">
         <v>216</v>
       </c>
       <c r="C191" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D191" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" t="s">
+        <v>218</v>
+      </c>
+      <c r="F191" t="s">
         <v>1004</v>
       </c>
-      <c r="D191" t="s">
-        <v>11</v>
-      </c>
-      <c r="E191" t="s">
-        <v>218</v>
-      </c>
-      <c r="F191" t="s">
+      <c r="G191" t="s">
         <v>1005</v>
       </c>
-      <c r="G191" t="s">
+      <c r="H191" t="s">
         <v>1006</v>
-      </c>
-      <c r="H191" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B192" t="s">
+        <v>778</v>
+      </c>
+      <c r="C192" t="s">
         <v>1008</v>
       </c>
-      <c r="B192" t="s">
-        <v>779</v>
-      </c>
-      <c r="C192" t="s">
+      <c r="D192" t="s">
+        <v>11</v>
+      </c>
+      <c r="E192" t="s">
+        <v>218</v>
+      </c>
+      <c r="F192" t="s">
         <v>1009</v>
       </c>
-      <c r="D192" t="s">
-        <v>11</v>
-      </c>
-      <c r="E192" t="s">
-        <v>218</v>
-      </c>
-      <c r="F192" t="s">
+      <c r="G192" t="s">
         <v>1010</v>
       </c>
-      <c r="G192" t="s">
+      <c r="H192" t="s">
         <v>1011</v>
-      </c>
-      <c r="H192" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B193" t="s">
+        <v>812</v>
+      </c>
+      <c r="C193" t="s">
         <v>1013</v>
       </c>
-      <c r="B193" t="s">
-        <v>813</v>
-      </c>
-      <c r="C193" t="s">
+      <c r="D193" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" t="s">
+        <v>218</v>
+      </c>
+      <c r="F193" t="s">
         <v>1014</v>
       </c>
-      <c r="D193" t="s">
-        <v>11</v>
-      </c>
-      <c r="E193" t="s">
-        <v>218</v>
-      </c>
-      <c r="F193" t="s">
+      <c r="G193" t="s">
         <v>1015</v>
       </c>
-      <c r="G193" t="s">
+      <c r="H193" t="s">
         <v>1016</v>
-      </c>
-      <c r="H193" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B194" t="s">
+        <v>794</v>
+      </c>
+      <c r="C194" t="s">
         <v>1018</v>
       </c>
-      <c r="B194" t="s">
-        <v>795</v>
-      </c>
-      <c r="C194" t="s">
+      <c r="D194" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" t="s">
+        <v>218</v>
+      </c>
+      <c r="F194" t="s">
         <v>1019</v>
       </c>
-      <c r="D194" t="s">
-        <v>11</v>
-      </c>
-      <c r="E194" t="s">
-        <v>218</v>
-      </c>
-      <c r="F194" t="s">
+      <c r="G194" t="s">
         <v>1020</v>
       </c>
-      <c r="G194" t="s">
+      <c r="H194" t="s">
         <v>1021</v>
-      </c>
-      <c r="H194" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B195" t="s">
+        <v>794</v>
+      </c>
+      <c r="C195" t="s">
         <v>1023</v>
       </c>
-      <c r="B195" t="s">
-        <v>795</v>
-      </c>
-      <c r="C195" t="s">
+      <c r="D195" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" t="s">
+        <v>218</v>
+      </c>
+      <c r="F195" t="s">
         <v>1024</v>
       </c>
-      <c r="D195" t="s">
-        <v>11</v>
-      </c>
-      <c r="E195" t="s">
-        <v>218</v>
-      </c>
-      <c r="F195" t="s">
+      <c r="G195" t="s">
         <v>1025</v>
       </c>
-      <c r="G195" t="s">
+      <c r="H195" t="s">
         <v>1026</v>
-      </c>
-      <c r="H195" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B196" t="s">
+        <v>794</v>
+      </c>
+      <c r="C196" t="s">
         <v>1028</v>
       </c>
-      <c r="B196" t="s">
-        <v>795</v>
-      </c>
-      <c r="C196" t="s">
+      <c r="D196" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" t="s">
+        <v>218</v>
+      </c>
+      <c r="F196" t="s">
         <v>1029</v>
       </c>
-      <c r="D196" t="s">
-        <v>11</v>
-      </c>
-      <c r="E196" t="s">
-        <v>218</v>
-      </c>
-      <c r="F196" t="s">
+      <c r="G196" t="s">
         <v>1030</v>
       </c>
-      <c r="G196" t="s">
+      <c r="H196" t="s">
         <v>1031</v>
-      </c>
-      <c r="H196" t="s">
-        <v>1032</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B197" t="s">
         <v>166</v>
       </c>
       <c r="C197" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D197" t="s">
         <v>11</v>
@@ -8995,102 +8992,102 @@
         <v>19</v>
       </c>
       <c r="F197" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="G197" t="s">
         <v>277</v>
       </c>
       <c r="H197" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B198" t="s">
+        <v>800</v>
+      </c>
+      <c r="C198" t="s">
         <v>1037</v>
       </c>
-      <c r="B198" t="s">
-        <v>801</v>
-      </c>
-      <c r="C198" t="s">
+      <c r="D198" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" t="s">
+        <v>218</v>
+      </c>
+      <c r="F198" t="s">
         <v>1038</v>
       </c>
-      <c r="D198" t="s">
-        <v>11</v>
-      </c>
-      <c r="E198" t="s">
-        <v>218</v>
-      </c>
-      <c r="F198" t="s">
+      <c r="G198" t="s">
         <v>1039</v>
       </c>
-      <c r="G198" t="s">
+      <c r="H198" t="s">
         <v>1040</v>
-      </c>
-      <c r="H198" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B199" t="s">
+        <v>620</v>
+      </c>
+      <c r="C199" t="s">
         <v>1042</v>
       </c>
-      <c r="B199" t="s">
-        <v>621</v>
-      </c>
-      <c r="C199" t="s">
+      <c r="D199" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" t="s">
+        <v>218</v>
+      </c>
+      <c r="F199" t="s">
         <v>1043</v>
       </c>
-      <c r="D199" t="s">
-        <v>11</v>
-      </c>
-      <c r="E199" t="s">
-        <v>218</v>
-      </c>
-      <c r="F199" t="s">
+      <c r="G199" t="s">
         <v>1044</v>
       </c>
-      <c r="G199" t="s">
+      <c r="H199" t="s">
         <v>1045</v>
-      </c>
-      <c r="H199" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B200" t="s">
+        <v>689</v>
+      </c>
+      <c r="C200" t="s">
         <v>1047</v>
       </c>
-      <c r="B200" t="s">
-        <v>690</v>
-      </c>
-      <c r="C200" t="s">
+      <c r="D200" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" t="s">
+        <v>218</v>
+      </c>
+      <c r="F200" t="s">
         <v>1048</v>
       </c>
-      <c r="D200" t="s">
-        <v>11</v>
-      </c>
-      <c r="E200" t="s">
-        <v>218</v>
-      </c>
-      <c r="F200" t="s">
+      <c r="G200" t="s">
         <v>1049</v>
       </c>
-      <c r="G200" t="s">
+      <c r="H200" t="s">
         <v>1050</v>
-      </c>
-      <c r="H200" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B201" t="s">
         <v>254</v>
       </c>
       <c r="C201" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="D201" t="s">
         <v>11</v>
@@ -9099,24 +9096,24 @@
         <v>19</v>
       </c>
       <c r="F201" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G201" t="s">
         <v>287</v>
       </c>
       <c r="H201" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B202" t="s">
         <v>254</v>
       </c>
       <c r="C202" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="D202" t="s">
         <v>11</v>
@@ -9125,128 +9122,128 @@
         <v>19</v>
       </c>
       <c r="F202" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G202" t="s">
         <v>287</v>
       </c>
       <c r="H202" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B203" t="s">
+        <v>806</v>
+      </c>
+      <c r="C203" t="s">
         <v>1060</v>
       </c>
-      <c r="B203" t="s">
-        <v>807</v>
-      </c>
-      <c r="C203" t="s">
+      <c r="D203" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" t="s">
+        <v>218</v>
+      </c>
+      <c r="F203" t="s">
         <v>1061</v>
       </c>
-      <c r="D203" t="s">
-        <v>11</v>
-      </c>
-      <c r="E203" t="s">
-        <v>218</v>
-      </c>
-      <c r="F203" t="s">
+      <c r="G203" t="s">
+        <v>809</v>
+      </c>
+      <c r="H203" t="s">
         <v>1062</v>
-      </c>
-      <c r="G203" t="s">
-        <v>810</v>
-      </c>
-      <c r="H203" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B204" t="s">
+        <v>778</v>
+      </c>
+      <c r="C204" t="s">
         <v>1064</v>
       </c>
-      <c r="B204" t="s">
-        <v>779</v>
-      </c>
-      <c r="C204" t="s">
+      <c r="D204" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>218</v>
+      </c>
+      <c r="F204" t="s">
         <v>1065</v>
       </c>
-      <c r="D204" t="s">
-        <v>11</v>
-      </c>
-      <c r="E204" t="s">
-        <v>218</v>
-      </c>
-      <c r="F204" t="s">
+      <c r="G204" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H204" t="s">
         <v>1066</v>
-      </c>
-      <c r="G204" t="s">
-        <v>1011</v>
-      </c>
-      <c r="H204" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B205" t="s">
         <v>216</v>
       </c>
       <c r="C205" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D205" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" t="s">
+        <v>218</v>
+      </c>
+      <c r="F205" t="s">
         <v>1069</v>
       </c>
-      <c r="D205" t="s">
-        <v>11</v>
-      </c>
-      <c r="E205" t="s">
-        <v>218</v>
-      </c>
-      <c r="F205" t="s">
+      <c r="G205" t="s">
         <v>1070</v>
       </c>
-      <c r="G205" t="s">
+      <c r="H205" t="s">
         <v>1071</v>
-      </c>
-      <c r="H205" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B206" t="s">
         <v>1073</v>
       </c>
-      <c r="B206" t="s">
+      <c r="C206" t="s">
         <v>1074</v>
       </c>
-      <c r="C206" t="s">
+      <c r="D206" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" t="s">
+        <v>218</v>
+      </c>
+      <c r="F206" t="s">
         <v>1075</v>
       </c>
-      <c r="D206" t="s">
-        <v>11</v>
-      </c>
-      <c r="E206" t="s">
-        <v>218</v>
-      </c>
-      <c r="F206" t="s">
+      <c r="G206" t="s">
         <v>1076</v>
       </c>
-      <c r="G206" t="s">
+      <c r="H206" t="s">
         <v>1077</v>
-      </c>
-      <c r="H206" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B207" t="s">
         <v>223</v>
       </c>
       <c r="C207" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="D207" t="s">
         <v>11</v>
@@ -9255,24 +9252,24 @@
         <v>19</v>
       </c>
       <c r="F207" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="G207" t="s">
         <v>303</v>
       </c>
       <c r="H207" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B208" t="s">
         <v>36</v>
       </c>
       <c r="C208" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D208" t="s">
         <v>11</v>
@@ -9281,24 +9278,24 @@
         <v>19</v>
       </c>
       <c r="F208" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G208" t="s">
         <v>1085</v>
       </c>
-      <c r="G208" t="s">
+      <c r="H208" t="s">
         <v>1086</v>
-      </c>
-      <c r="H208" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B209" t="s">
         <v>1088</v>
       </c>
-      <c r="B209" t="s">
+      <c r="C209" t="s">
         <v>1089</v>
-      </c>
-      <c r="C209" t="s">
-        <v>1090</v>
       </c>
       <c r="D209" t="s">
         <v>11</v>
@@ -9307,24 +9304,24 @@
         <v>19</v>
       </c>
       <c r="F209" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G209" t="s">
         <v>1091</v>
       </c>
-      <c r="G209" t="s">
+      <c r="H209" t="s">
         <v>1092</v>
-      </c>
-      <c r="H209" t="s">
-        <v>1093</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C210" t="s">
         <v>1094</v>
-      </c>
-      <c r="B210" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C210" t="s">
-        <v>1095</v>
       </c>
       <c r="D210" t="s">
         <v>11</v>
@@ -9333,24 +9330,24 @@
         <v>19</v>
       </c>
       <c r="F210" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G210" t="s">
         <v>1096</v>
       </c>
-      <c r="G210" t="s">
+      <c r="H210" t="s">
         <v>1097</v>
-      </c>
-      <c r="H210" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C211" t="s">
         <v>1099</v>
-      </c>
-      <c r="B211" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C211" t="s">
-        <v>1100</v>
       </c>
       <c r="D211" t="s">
         <v>11</v>
@@ -9359,76 +9356,76 @@
         <v>19</v>
       </c>
       <c r="F211" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G211" t="s">
         <v>1101</v>
       </c>
-      <c r="G211" t="s">
+      <c r="H211" t="s">
         <v>1102</v>
-      </c>
-      <c r="H211" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B212" t="s">
+        <v>812</v>
+      </c>
+      <c r="C212" t="s">
         <v>1104</v>
       </c>
-      <c r="B212" t="s">
-        <v>813</v>
-      </c>
-      <c r="C212" t="s">
+      <c r="D212" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" t="s">
+        <v>218</v>
+      </c>
+      <c r="F212" t="s">
         <v>1105</v>
       </c>
-      <c r="D212" t="s">
-        <v>11</v>
-      </c>
-      <c r="E212" t="s">
-        <v>218</v>
-      </c>
-      <c r="F212" t="s">
+      <c r="G212" t="s">
         <v>1106</v>
       </c>
-      <c r="G212" t="s">
+      <c r="H212" t="s">
         <v>1107</v>
-      </c>
-      <c r="H212" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B213" t="s">
+        <v>812</v>
+      </c>
+      <c r="C213" t="s">
         <v>1109</v>
       </c>
-      <c r="B213" t="s">
-        <v>813</v>
-      </c>
-      <c r="C213" t="s">
+      <c r="D213" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" t="s">
+        <v>218</v>
+      </c>
+      <c r="F213" t="s">
         <v>1110</v>
       </c>
-      <c r="D213" t="s">
-        <v>11</v>
-      </c>
-      <c r="E213" t="s">
-        <v>218</v>
-      </c>
-      <c r="F213" t="s">
+      <c r="G213" t="s">
         <v>1111</v>
       </c>
-      <c r="G213" t="s">
+      <c r="H213" t="s">
         <v>1112</v>
-      </c>
-      <c r="H213" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B214" t="s">
         <v>155</v>
       </c>
       <c r="C214" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D214" t="s">
         <v>11</v>
@@ -9437,221 +9434,221 @@
         <v>19</v>
       </c>
       <c r="F214" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="G214" t="s">
         <v>246</v>
       </c>
       <c r="H214" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B215" t="s">
+        <v>858</v>
+      </c>
+      <c r="C215" t="s">
         <v>1118</v>
       </c>
-      <c r="B215" t="s">
-        <v>859</v>
-      </c>
-      <c r="C215" t="s">
+      <c r="D215" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+      <c r="F215" t="s">
         <v>1119</v>
       </c>
-      <c r="D215" t="s">
-        <v>11</v>
-      </c>
-      <c r="E215" t="s">
-        <v>218</v>
-      </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>1120</v>
       </c>
-      <c r="G215" t="s">
+      <c r="H215" t="s">
         <v>1121</v>
-      </c>
-      <c r="H215" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B216" t="s">
+        <v>794</v>
+      </c>
+      <c r="C216" t="s">
         <v>1123</v>
       </c>
-      <c r="B216" t="s">
-        <v>795</v>
-      </c>
-      <c r="C216" t="s">
+      <c r="D216" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" t="s">
+        <v>218</v>
+      </c>
+      <c r="F216" t="s">
         <v>1124</v>
       </c>
-      <c r="D216" t="s">
-        <v>11</v>
-      </c>
-      <c r="E216" t="s">
-        <v>218</v>
-      </c>
-      <c r="F216" t="s">
+      <c r="G216" t="s">
         <v>1125</v>
       </c>
-      <c r="G216" t="s">
+      <c r="H216" t="s">
         <v>1126</v>
-      </c>
-      <c r="H216" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B217" t="s">
+        <v>794</v>
+      </c>
+      <c r="C217" t="s">
         <v>1128</v>
       </c>
-      <c r="B217" t="s">
-        <v>795</v>
-      </c>
-      <c r="C217" t="s">
+      <c r="D217" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" t="s">
+        <v>218</v>
+      </c>
+      <c r="F217" t="s">
         <v>1129</v>
       </c>
-      <c r="D217" t="s">
-        <v>11</v>
-      </c>
-      <c r="E217" t="s">
-        <v>218</v>
-      </c>
-      <c r="F217" t="s">
+      <c r="G217" t="s">
         <v>1130</v>
       </c>
-      <c r="G217" t="s">
+      <c r="H217" t="s">
         <v>1131</v>
-      </c>
-      <c r="H217" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B218" t="s">
+        <v>936</v>
+      </c>
+      <c r="C218" t="s">
         <v>1133</v>
       </c>
-      <c r="B218" t="s">
-        <v>937</v>
-      </c>
-      <c r="C218" t="s">
+      <c r="D218" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" t="s">
+        <v>218</v>
+      </c>
+      <c r="F218" t="s">
         <v>1134</v>
       </c>
-      <c r="D218" t="s">
-        <v>11</v>
-      </c>
-      <c r="E218" t="s">
-        <v>218</v>
-      </c>
-      <c r="F218" t="s">
+      <c r="G218" t="s">
         <v>1135</v>
       </c>
-      <c r="G218" t="s">
+      <c r="H218" t="s">
         <v>1136</v>
-      </c>
-      <c r="H218" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B219" t="s">
+        <v>936</v>
+      </c>
+      <c r="C219" t="s">
         <v>1138</v>
       </c>
-      <c r="B219" t="s">
-        <v>937</v>
-      </c>
-      <c r="C219" t="s">
+      <c r="D219" t="s">
+        <v>11</v>
+      </c>
+      <c r="E219" t="s">
+        <v>218</v>
+      </c>
+      <c r="F219" t="s">
         <v>1139</v>
       </c>
-      <c r="D219" t="s">
-        <v>11</v>
-      </c>
-      <c r="E219" t="s">
-        <v>218</v>
-      </c>
-      <c r="F219" t="s">
+      <c r="G219" t="s">
         <v>1140</v>
       </c>
-      <c r="G219" t="s">
+      <c r="H219" t="s">
         <v>1141</v>
-      </c>
-      <c r="H219" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B220" t="s">
+        <v>794</v>
+      </c>
+      <c r="C220" t="s">
         <v>1143</v>
       </c>
-      <c r="B220" t="s">
-        <v>795</v>
-      </c>
-      <c r="C220" t="s">
+      <c r="D220" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" t="s">
+        <v>218</v>
+      </c>
+      <c r="F220" t="s">
         <v>1144</v>
       </c>
-      <c r="D220" t="s">
-        <v>11</v>
-      </c>
-      <c r="E220" t="s">
-        <v>218</v>
-      </c>
-      <c r="F220" t="s">
+      <c r="G220" t="s">
         <v>1145</v>
       </c>
-      <c r="G220" t="s">
+      <c r="H220" t="s">
         <v>1146</v>
-      </c>
-      <c r="H220" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B221" t="s">
+        <v>457</v>
+      </c>
+      <c r="C221" t="s">
         <v>1148</v>
       </c>
-      <c r="B221" t="s">
-        <v>458</v>
-      </c>
-      <c r="C221" t="s">
+      <c r="D221" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" t="s">
+        <v>218</v>
+      </c>
+      <c r="F221" t="s">
         <v>1149</v>
       </c>
-      <c r="D221" t="s">
-        <v>11</v>
-      </c>
-      <c r="E221" t="s">
-        <v>218</v>
-      </c>
-      <c r="F221" t="s">
+      <c r="G221" t="s">
         <v>1150</v>
       </c>
-      <c r="G221" t="s">
+      <c r="H221" t="s">
         <v>1151</v>
-      </c>
-      <c r="H221" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B222" t="s">
+        <v>457</v>
+      </c>
+      <c r="C222" t="s">
         <v>1153</v>
       </c>
-      <c r="B222" t="s">
-        <v>458</v>
-      </c>
-      <c r="C222" t="s">
+      <c r="D222" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" t="s">
+        <v>218</v>
+      </c>
+      <c r="F222" t="s">
         <v>1154</v>
       </c>
-      <c r="D222" t="s">
-        <v>11</v>
-      </c>
-      <c r="E222" t="s">
-        <v>218</v>
-      </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
         <v>1155</v>
       </c>
-      <c r="G222" t="s">
+      <c r="H222" t="s">
         <v>1156</v>
-      </c>
-      <c r="H222" t="s">
-        <v>1157</v>
       </c>
     </row>
   </sheetData>

--- a/tools/importer/reports/import-ingredient-product-detail.report.xlsx
+++ b/tools/importer/reports/import-ingredient-product-detail.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1157">
   <si>
     <t>_reportFile</t>
   </si>
@@ -61,10 +61,607 @@
     <t>https://www.nzmp.com/global/en.html</t>
   </si>
   <si>
+    <t>global/en/about-nzmp/global-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-category","cards-value","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients</t>
+  </si>
+  <si>
+    <t>category-landing</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:45:38.779Z</t>
+  </si>
+  <si>
+    <t>NZMP's Global Ingredients Network | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/news.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/news</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:31.458Z</t>
+  </si>
+  <si>
+    <t>NZMP Newsfeed: News, Updates &amp; Events | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/news.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/our-way-of-farming.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/our-way-of-farming</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:41.127Z</t>
+  </si>
+  <si>
+    <t>Our Way of Farming | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/our-way-of-farming.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/safety-and-quality.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/safety-and-quality</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:51.860Z</t>
+  </si>
+  <si>
+    <t>NZMP Ingredient Safety &amp; Quality Processes | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/safety-and-quality.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/active-lifestyle.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-feature","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/active-lifestyle</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:01.179Z</t>
+  </si>
+  <si>
+    <t>Active Lifestyle | NZMP Dairy Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/active-lifestyle.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/beverages.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-feature","columns-feature","columns-feature","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/beverages</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:11.096Z</t>
+  </si>
+  <si>
+    <t>Beverages | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/beverages.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/consumer-milk-powders.report.json</t>
+  </si>
+  <si>
+    <t>global/en/applications/consumer-milk-powders</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:19.849Z</t>
+  </si>
+  <si>
+    <t>Consumer Milk Powders | NZMP Dairy Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/consumer-milk-powders.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/food-manufacture.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/food-manufacture</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:30.462Z</t>
+  </si>
+  <si>
+    <t>Food Manufacture | NZMP Dairy Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/food-manufacture.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/medical-nutrition.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-feature","cards-value","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/medical-nutrition</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:39.833Z</t>
+  </si>
+  <si>
+    <t>Medical Nutrition | NZMP Dairy Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/medical-nutrition.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/paediatric-nutrition.report.json</t>
+  </si>
+  <si>
+    <t>global/en/applications/paediatric-nutrition</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:03.662Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/paediatric-nutrition.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/yoghurts-and-cultured-products.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-feature","columns-feature","cards-value","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/yoghurts-and-cultured-products</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:17.092Z</t>
+  </si>
+  <si>
+    <t>Yoghurts and Cultured Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/yoghurts-and-cultured-products.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity.report.json</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:04.268Z</t>
+  </si>
+  <si>
+    <t>Innovation and Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/price-risk-management.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/price-risk-management</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:55:19.165Z</t>
+  </si>
+  <si>
+    <t>Price Risk Management | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/price-risk-management.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/third-party-manufacturing.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/third-party-manufacturing</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:55:26.273Z</t>
+  </si>
+  <si>
+    <t>Third Party Manufacturing | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/third-party-manufacturing.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-australian-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-australian-ingredients</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:45:46.523Z</t>
+  </si>
+  <si>
+    <t>Our Australian Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients/our-australian-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-european-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-european-ingredients</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:45:56.282Z</t>
+  </si>
+  <si>
+    <t>Our European Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients/our-european-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-global-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","cards-category","cards-category","cards-value","cards-value","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-global-ingredients</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:09.109Z</t>
+  </si>
+  <si>
+    <t>Our Global Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients/our-global-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-new-zealand-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-new-zealand-ingredients</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:18.260Z</t>
+  </si>
+  <si>
+    <t>Our New Zealand Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients/our-new-zealand-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-north-american-ingredients.report.json</t>
+  </si>
+  <si>
+    <t>global/en/about-nzmp/global-ingredients/our-north-american-ingredients</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:46:24.482Z</t>
+  </si>
+  <si>
+    <t>Our North American Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/about-nzmp/global-ingredients/our-north-american-ingredients.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/organic-dairy/organic-product-claims.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/organic-dairy/organic-product-claims</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:47.471Z</t>
+  </si>
+  <si>
+    <t>Organic Product Claims | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/organic-dairy/organic-product-claims.html</t>
+  </si>
+  <si>
+    <t>global/en/applications/organic-dairy/organic-supply.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/applications/organic-dairy/organic-supply</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:47:54.925Z</t>
+  </si>
+  <si>
+    <t>Organic Supply | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/applications/organic-dairy/organic-supply.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cheddar-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:24.667Z</t>
+  </si>
+  <si>
+    <t>Cheddar Cheese - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cheddar-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cream-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/cream-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:35.558Z</t>
+  </si>
+  <si>
+    <t>Cream Cheese - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/cream-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:44.089Z</t>
+  </si>
+  <si>
+    <t>Mozzarella Cheese - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/new-zealand-cheeses.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/new-zealand-cheeses</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:57.621Z</t>
+  </si>
+  <si>
+    <t>Uniquely from New Zealand Cheese - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/new-zealand-cheeses.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:04.959Z</t>
+  </si>
+  <si>
+    <t>Parmesan and Popular cheeses | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/parmesan-and-popular-cheeses.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/repack-cheese.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/repack-cheese</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:11.863Z</t>
+  </si>
+  <si>
+    <t>Repack Cheese - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/repack-cheese.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:20.764Z</t>
+  </si>
+  <si>
+    <t>Anhydrous Milk Fat | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/butter.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/butter</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:27.460Z</t>
+  </si>
+  <si>
+    <t>Butter - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/dairy-fats-cream/butter.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/cream-powder.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/cream-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:34.663Z</t>
+  </si>
+  <si>
+    <t>Cream Powder - Dairy Fats Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/dairy-fats-cream/cream-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/repack-butter.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/repack-butter</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:41.822Z</t>
+  </si>
+  <si>
+    <t>Repack Butter - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/dairy-fats-cream/repack-butter.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/uht-cream.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-category"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/dairy-fats-cream/uht-cream</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:47.598Z</t>
+  </si>
+  <si>
+    <t>UHT Cream | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/dairy-fats-cream/uht-cream.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/buttermilk-powder.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/buttermilk-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:49:54.464Z</t>
+  </si>
+  <si>
+    <t>Buttermilk Powder - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/buttermilk-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/instant-milk-powder.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/instant-milk-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:02.024Z</t>
+  </si>
+  <si>
+    <t>Instant Milk Powder - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/instant-milk-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/lactose.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/lactose</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:08.323Z</t>
+  </si>
+  <si>
+    <t>Lactose - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/lactose.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/powders-concentrates/nzmp-frozen-wholemilk-concentrate.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/nzmp-frozen-wholemilk-concentrate</t>
@@ -73,7 +670,7 @@
     <t>ingredient-product-detail</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:25.188Z</t>
+    <t>2026-08-14T01:44:33.033Z</t>
   </si>
   <si>
     <t>Frozen Whole Milk Concentrate | NZMP.com</t>
@@ -82,16 +679,334 @@
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/nzmp-frozen-wholemilk-concentrate.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:13.822Z</t>
+  </si>
+  <si>
+    <t>Paediatric Grade Powders | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/paediatric-grade-powders.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/skim-milk-powder.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/skim-milk-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:21.160Z</t>
+  </si>
+  <si>
+    <t>Skim Milk Powder - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/skim-milk-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/whey-powder.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/whey-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:28.059Z</t>
+  </si>
+  <si>
+    <t>Whey Powder - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/whey-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/whole-milk-powder.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/powders-concentrates/whole-milk-powder</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:36.482Z</t>
+  </si>
+  <si>
+    <t>Whole Milk Powder | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/whole-milk-powder.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/caseins-and-caseinates.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/caseins-and-caseinates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:43.522Z</t>
+  </si>
+  <si>
+    <t>Caseins and Caseinates | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/caseins-and-caseinates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/functional-proteins.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/functional-proteins</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:58.239Z</t>
+  </si>
+  <si>
+    <t>Functional Proteins - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/functional-proteins.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/hydrolysates.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/hydrolysates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:04.924Z</t>
+  </si>
+  <si>
+    <t>Hydrolysates - Ingredients &amp; Products | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/hydrolysates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:13.056Z</t>
+  </si>
+  <si>
+    <t>Milk Protein Concentrates - Proteins | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/nzmp-dpc.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/nzmp-dpc</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:10.880Z</t>
+  </si>
+  <si>
+    <t>NZMP CrispBar Dairy Protein Crisp | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/nzmp-dpc.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:18.624Z</t>
+  </si>
+  <si>
+    <t>Whey Protein Concentrates | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-isolates.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-isolates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:48.058Z</t>
+  </si>
+  <si>
+    <t>Whey Protein Isolates | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-isolates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/complex-lipids.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/complex-lipids</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:01.158Z</t>
+  </si>
+  <si>
+    <t>MFGM Complex Lipids | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/complex-lipids.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/hydrolysates.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/hydrolysates</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:08.624Z</t>
+  </si>
+  <si>
+    <t>Hydrolysates - Specialty Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/lactoferrin.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","columns-feature","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/lactoferrin</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:29.630Z</t>
+  </si>
+  <si>
+    <t>Lactoferrin - Speciality Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/lactoferrin.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/lactose.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/lactose</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:37.970Z</t>
+  </si>
+  <si>
+    <t>Lactose - Speciality Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/lactose.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/prebiotics.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/prebiotics</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:45.151Z</t>
+  </si>
+  <si>
+    <t>Prebiotics - Speciality Ingredients | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/prebiotics.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-category","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:12.757Z</t>
+  </si>
+  <si>
+    <t>World-Leading Global Dairy Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-global-expertise.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-protein-expertise.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-value","cards-value","cards-value","cards-value","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-protein-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:55:04.443Z</t>
+  </si>
+  <si>
+    <t>Our Protein Expertise - Innovation &amp; Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-protein-expertise.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/the-fonterra-research-and-development-centre.report.json</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/the-fonterra-research-and-development-centre</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:55:12.107Z</t>
+  </si>
+  <si>
+    <t>The Fonterra Research and Development Centre | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/the-fonterra-research-and-development-centre.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/third-party-manufacturing/private-label-solutions.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","columns-feature","columns-feature","cards-teaser"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/third-party-manufacturing/private-label-solutions</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:55:35.658Z</t>
+  </si>
+  <si>
+    <t>Our Private Label Solutions | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/third-party-manufacturing/private-label-solutions.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-au.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:15.215Z</t>
+    <t>2026-08-14T01:35:22.896Z</t>
   </si>
   <si>
     <t>Cheddar Cheese (Australia Specification) | NZMP Dairy Ingredients | NZMP.com</t>
@@ -103,13 +1018,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-frozen</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:23.694Z</t>
+    <t>2026-08-14T01:36:15.923Z</t>
   </si>
   <si>
     <t>Cheddar Cheese Frozen | NZMP.com</t>
@@ -124,7 +1039,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese-manufacturing</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:33.759Z</t>
+    <t>2026-08-14T01:36:24.161Z</t>
   </si>
   <si>
     <t>Cheddar Cheese for Manufacturing | NZMP.com</t>
@@ -136,13 +1051,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:40.959Z</t>
+    <t>2026-08-14T01:36:32.024Z</t>
   </si>
   <si>
     <t>Cheddar Cheese | NZMP Dairy Ingredients | NZMP.com</t>
@@ -154,13 +1069,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/coloured-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:49.141Z</t>
+    <t>2026-08-14T01:36:40.029Z</t>
   </si>
   <si>
     <t>Coloured Cheddar Cheese | NZMP.com</t>
@@ -172,13 +1087,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/frozen-functional-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:15:56.362Z</t>
+    <t>2026-08-14T01:36:47.626Z</t>
   </si>
   <si>
     <t>Frozen Functional Cheddar Cheese | NZMP.com</t>
@@ -190,13 +1105,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/mature-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:04.559Z</t>
+    <t>2026-08-14T01:36:54.630Z</t>
   </si>
   <si>
     <t>Mature Cheddar | NZMP.com</t>
@@ -211,7 +1126,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-cheddar-cheese-frozen</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:13.023Z</t>
+    <t>2026-08-14T01:37:02.427Z</t>
   </si>
   <si>
     <t>Organic Frozen Cheddar Cheese, Reduced Salt  | NZMP.com</t>
@@ -223,13 +1138,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-mature-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:20.559Z</t>
+    <t>2026-08-14T01:37:10.659Z</t>
   </si>
   <si>
     <t>Organic Mature Cheddar Cheese | NZMP.com</t>
@@ -244,7 +1159,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/organic-mild-cheddar-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:30.171Z</t>
+    <t>2026-08-14T01:37:20.257Z</t>
   </si>
   <si>
     <t>Organic Mild Cheddar Cheese | NZMP.com</t>
@@ -256,13 +1171,13 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/cheddar-cheese/strong-cheddar-cheese-manufacturing</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:39.195Z</t>
+    <t>2026-08-14T01:37:28.686Z</t>
   </si>
   <si>
     <t>Strong Cheddar Cheese for Manufacturing | NZMP.com</t>
@@ -277,7 +1192,7 @@
     <t>global/en/ingredients/cheese/cheddar-cheese/young-cheddar-cheese-manufacturing-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:46.723Z</t>
+    <t>2026-08-14T01:37:35.638Z</t>
   </si>
   <si>
     <t>Young Cheddar Cheese for Manufacturing GDT Specification | NZMP.com</t>
@@ -292,7 +1207,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/easy-shred-mozzarella-nz</t>
   </si>
   <si>
-    <t>2026-08-13T21:16:55.022Z</t>
+    <t>2026-08-14T01:37:44.937Z</t>
   </si>
   <si>
     <t>Easy Shred Mozzarella | NZMP.com</t>
@@ -301,13 +1216,25 @@
     <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/easy-shred-mozzarella-nz.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/european-mozzarella.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/cheese/mozzarella-options/european-mozzarella</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:48:51.698Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/cheese/mozzarella-options/european-mozzarella.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/cheese/mozzarella-options/frozen-mozzarella.report.json</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/mozzarella-options/frozen-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:04.860Z</t>
+    <t>2026-08-14T01:37:54.322Z</t>
   </si>
   <si>
     <t>Frozen Mozzarella | NZMP.com</t>
@@ -322,7 +1249,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/iqf-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:13.085Z</t>
+    <t>2026-08-14T01:38:04.836Z</t>
   </si>
   <si>
     <t>Individually Quick Frozen Mozzarella | NZMP.com</t>
@@ -337,7 +1264,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/lower-salt-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:22.024Z</t>
+    <t>2026-08-14T01:38:13.261Z</t>
   </si>
   <si>
     <t>Lower Salt Mozzarella | NZMP.com</t>
@@ -352,7 +1279,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/medium-fat-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:32.323Z</t>
+    <t>2026-08-14T01:38:21.948Z</t>
   </si>
   <si>
     <t>Medium Fat Mozzarella | NZMP.com</t>
@@ -367,7 +1294,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-curd</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:39.974Z</t>
+    <t>2026-08-14T01:38:29.639Z</t>
   </si>
   <si>
     <t>Mozzarella Curd | NZMP.com</t>
@@ -379,13 +1306,13 @@
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-frozen-au.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-frozen-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:49.166Z</t>
+    <t>2026-08-14T01:38:39.928Z</t>
   </si>
   <si>
     <t>Premium Mozzarella Frozen (Made in Australia) | NZMP.com</t>
@@ -400,7 +1327,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/mozzarella-frozen-nz</t>
   </si>
   <si>
-    <t>2026-08-13T21:17:58.334Z</t>
+    <t>2026-08-14T01:38:49.223Z</t>
   </si>
   <si>
     <t>Premium Mozzarella Frozen (Made in New Zealand) | NZMP.com</t>
@@ -415,7 +1342,7 @@
     <t>global/en/ingredients/cheese/mozzarella-options/premium-chilled-mozzarella</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:08.123Z</t>
+    <t>2026-08-14T01:38:57.588Z</t>
   </si>
   <si>
     <t>Premium Chilled Mozzarella | NZMP.com</t>
@@ -430,7 +1357,7 @@
     <t>global/en/ingredients/cheese/new-zealand-cheeses/egmont-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:15.122Z</t>
+    <t>2026-08-14T01:39:05.359Z</t>
   </si>
   <si>
     <t>Egmont™ Cheese | NZMP.com</t>
@@ -445,7 +1372,7 @@
     <t>global/en/ingredients/cheese/new-zealand-cheeses/noble-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:23.064Z</t>
+    <t>2026-08-14T01:39:12.825Z</t>
   </si>
   <si>
     <t>Noble™ Cheese | NZMP.com</t>
@@ -457,13 +1384,13 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/colby-cheese.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/colby-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:30.160Z</t>
+    <t>2026-08-14T01:39:18.624Z</t>
   </si>
   <si>
     <t>Colby Cheese | NZMP.com</t>
@@ -478,7 +1405,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/edam-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:38.122Z</t>
+    <t>2026-08-14T01:39:25.564Z</t>
   </si>
   <si>
     <t>Edam Cheese | NZMP.com</t>
@@ -493,7 +1420,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/gouda-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:46.093Z</t>
+    <t>2026-08-14T01:39:32.499Z</t>
   </si>
   <si>
     <t>Gouda Cheese - NZMP Dairy Ingredients | NZMP.com</t>
@@ -508,7 +1435,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/parmesan-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:18:53.223Z</t>
+    <t>2026-08-14T01:39:38.760Z</t>
   </si>
   <si>
     <t>Parmesan | NZMP.com</t>
@@ -523,7 +1450,7 @@
     <t>global/en/ingredients/cheese/parmesan-and-popular-cheeses/swiss-style-cheese</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:00.222Z</t>
+    <t>2026-08-14T01:39:45.410Z</t>
   </si>
   <si>
     <t>Swiss-Style Cheese | NZMP.com</t>
@@ -538,7 +1465,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-15l-convenience-pack</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:09.445Z</t>
+    <t>2026-08-14T01:39:55.173Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat 15L/13.5KG Convenience Pack | NZMP.com</t>
@@ -553,7 +1480,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-premium-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:17.380Z</t>
+    <t>2026-08-14T01:40:03.077Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Premium Grade GDT Specification | NZMP.com</t>
@@ -568,7 +1495,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-premium</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:24.337Z</t>
+    <t>2026-08-14T01:40:10.722Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Premium Grade | NZMP.com</t>
@@ -583,7 +1510,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-regular-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:32.037Z</t>
+    <t>2026-08-14T01:40:18.535Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Regular Grade GDT Specification | NZMP.com</t>
@@ -598,7 +1525,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/anhydrous-milk-fat-regular</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:40.884Z</t>
+    <t>2026-08-14T01:40:27.112Z</t>
   </si>
   <si>
     <t>Anhydrous Milk Fat Regular Grade | NZMP.com</t>
@@ -613,7 +1540,7 @@
     <t>global/en/ingredients/dairy-fats-cream/anhydrous-milk-fat/organic-anhydrous-milk-fat-premium</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:48.228Z</t>
+    <t>2026-08-14T01:40:34.204Z</t>
   </si>
   <si>
     <t>Organic Anhydrous Milk Fat Premium Grade | NZMP.com</t>
@@ -628,7 +1555,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/lactic-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:19:57.225Z</t>
+    <t>2026-08-14T01:40:42.939Z</t>
   </si>
   <si>
     <t>Lactic Butter | NZMP.com</t>
@@ -643,7 +1570,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/organic-salted-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:05.757Z</t>
+    <t>2026-08-14T01:40:50.896Z</t>
   </si>
   <si>
     <t>Organic Salted Butter | NZMP.com</t>
@@ -658,7 +1585,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/organic-unsalted-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:13.771Z</t>
+    <t>2026-08-14T01:40:57.923Z</t>
   </si>
   <si>
     <t>Organic Unsalted Butter | NZMP.com</t>
@@ -673,7 +1600,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/organic-unsalted-lactic-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:23.223Z</t>
+    <t>2026-08-14T01:41:05.494Z</t>
   </si>
   <si>
     <t>Organic Lactic Unsalted Butter | NZMP.com</t>
@@ -688,7 +1615,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/salted-creamery-butter-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:30.596Z</t>
+    <t>2026-08-14T01:41:12.323Z</t>
   </si>
   <si>
     <t>Salted Creamery Butter GDT Specification | NZMP.com</t>
@@ -703,7 +1630,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/salted-creamery-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:38.728Z</t>
+    <t>2026-08-14T01:41:18.846Z</t>
   </si>
   <si>
     <t>Salted Creamery Butter | NZMP.com</t>
@@ -715,13 +1642,13 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-butter-convenience-pack.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-butter-convenience-pack</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:46.860Z</t>
+    <t>2026-08-14T01:41:29.060Z</t>
   </si>
   <si>
     <t>NZMP™ Unsalted Butter, 12.5kg Convenience Pack | NZMP.com</t>
@@ -736,7 +1663,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-creamery-butter-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:20:55.505Z</t>
+    <t>2026-08-14T01:41:36.846Z</t>
   </si>
   <si>
     <t>Unsalted Creamery Butter GDT Specification | NZMP.com</t>
@@ -751,7 +1678,7 @@
     <t>global/en/ingredients/dairy-fats-cream/butter/unsalted-creamery-butter</t>
   </si>
   <si>
-    <t>2026-08-13T21:21:49.560Z</t>
+    <t>2026-08-14T01:41:44.843Z</t>
   </si>
   <si>
     <t>Unsalted Creamery Butter | NZMP.com</t>
@@ -766,7 +1693,7 @@
     <t>global/en/ingredients/dairy-fats-cream/cream-cheese/cream-cheese-traditional</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:03.353Z</t>
+    <t>2026-08-14T01:41:53.585Z</t>
   </si>
   <si>
     <t>Cream Cheese Traditional | NZMP.com</t>
@@ -781,7 +1708,7 @@
     <t>global/en/ingredients/dairy-fats-cream/cream-powder/cream-powder-55</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:12.161Z</t>
+    <t>2026-08-14T01:42:02.959Z</t>
   </si>
   <si>
     <t>Cream Powder 55 | NZMP.com</t>
@@ -796,7 +1723,7 @@
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder/regular-buttermilk-powder-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:20.527Z</t>
+    <t>2026-08-14T01:42:12.034Z</t>
   </si>
   <si>
     <t>Regular Buttermilk Powder (Australia Specification) | NZMP.com</t>
@@ -811,7 +1738,7 @@
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder/regular-buttermilk-powder-uht-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:26.857Z</t>
+    <t>2026-08-14T01:42:21.925Z</t>
   </si>
   <si>
     <t>Regular Buttermilk Powder for UHT Milk GDT Specification | NZMP.com</t>
@@ -826,7 +1753,7 @@
     <t>global/en/ingredients/powders-concentrates/buttermilk-powder/regular-buttermilk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:36.708Z</t>
+    <t>2026-08-14T01:42:42.268Z</t>
   </si>
   <si>
     <t>Regular Buttermilk Powder | NZMP.com</t>
@@ -841,7 +1768,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/fat-filled-milk-powder-for-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:45.947Z</t>
+    <t>2026-08-14T01:42:49.477Z</t>
   </si>
   <si>
     <t>Fat Filled Milk Powder for Yoghurt | NZMP.com</t>
@@ -853,13 +1780,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/fat-filled-milk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/fat-filled-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:22:54.960Z</t>
+    <t>2026-08-14T01:42:58.923Z</t>
   </si>
   <si>
     <t>Fat Filled Milk Powder Instant Fortified | NZMP.com</t>
@@ -871,13 +1798,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/gold-instant-whole-milk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/gold-instant-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:03.328Z</t>
+    <t>2026-08-14T01:43:07.035Z</t>
   </si>
   <si>
     <t>Gold Instant Whole Milk Powder | NZMP.com</t>
@@ -892,7 +1819,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/instant-skim-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:11.088Z</t>
+    <t>2026-08-14T01:43:15.723Z</t>
   </si>
   <si>
     <t>Instant Skim Milk Powder | NZMP.com</t>
@@ -907,7 +1834,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/instant-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:18.924Z</t>
+    <t>2026-08-14T01:43:24.557Z</t>
   </si>
   <si>
     <t>Instant Whole Milk Powder | NZMP Ingredients | NZMP.com</t>
@@ -922,7 +1849,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-fortified-plus-instant-wmp</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:26.321Z</t>
+    <t>2026-08-14T01:43:31.943Z</t>
   </si>
   <si>
     <t>Fortified+ Instant Whole Milk Powder | NZMP.com</t>
@@ -937,7 +1864,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-gold-instant-wmp</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:35.123Z</t>
+    <t>2026-08-14T01:43:41.630Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-gold-instant-wmp.html</t>
@@ -946,13 +1873,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-low-cost-pure-instant-dairy-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-low-cost-pure-instant-dairy-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:43.175Z</t>
+    <t>2026-08-14T01:43:49.641Z</t>
   </si>
   <si>
     <t>Low-Cost Pure Instant Dairy Powder | NZMP.com</t>
@@ -964,13 +1891,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-nutriwhite-dairy-based-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-nutriwhite-dairy-based-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:23:52.280Z</t>
+    <t>2026-08-14T01:43:58.900Z</t>
   </si>
   <si>
     <t>NutriWhite Dairy-Based Powder | NZMP Dairy Ingredients | NZMP.com</t>
@@ -982,13 +1909,13 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-protein-plus-instant-milk-powder.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/nzmp-protein-plus-instant-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:01.245Z</t>
+    <t>2026-08-14T01:44:08.425Z</t>
   </si>
   <si>
     <t>Protein+ Instant Milk Powder | NZMP.com</t>
@@ -1003,7 +1930,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/super-fortified-instant-smp</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:10.156Z</t>
+    <t>2026-08-14T01:44:16.966Z</t>
   </si>
   <si>
     <t>Super Fortified Instant Skim Milk Powder | NZMP.com</t>
@@ -1018,7 +1945,7 @@
     <t>global/en/ingredients/powders-concentrates/instant-milk-powder/whole-milk-powder-instant-fortified</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:18.198Z</t>
+    <t>2026-08-14T01:44:25.490Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder Instant Fortified with Vitamins A &amp; D | NZMP.com</t>
@@ -1030,13 +1957,13 @@
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-demineralised-whey-powder-90.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","carousel-news"]</t>
+    <t>["columns-product","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-demineralised-whey-powder-90</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:31.261Z</t>
+    <t>2026-08-14T01:44:39.094Z</t>
   </si>
   <si>
     <t>SureStart™ Demineralised Whey Powder 90% | NZMP.com</t>
@@ -1051,7 +1978,7 @@
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-regular-skim-milk-powder-wetapp</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:39.058Z</t>
+    <t>2026-08-14T01:44:47.024Z</t>
   </si>
   <si>
     <t>Paediatric Grade Regular Skim Milk Powder | NZMP.com</t>
@@ -1066,7 +1993,7 @@
     <t>global/en/ingredients/powders-concentrates/paediatric-grade-powders/surestart-regular-whole-milk-powder-wetapp</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:46.289Z</t>
+    <t>2026-08-14T01:44:53.565Z</t>
   </si>
   <si>
     <t>Paediatric Grade Regular Whole Milk Powder | NZMP.com</t>
@@ -1081,7 +2008,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/organic-skim-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:24:54.988Z</t>
+    <t>2026-08-14T01:45:01.460Z</t>
   </si>
   <si>
     <t>Organic Skim Milk Powder | NZMP.com</t>
@@ -1096,7 +2023,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-high-heat-hs-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:25:03.060Z</t>
+    <t>2026-08-14T01:45:09.737Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder High Heat Heat Stable GDT Specification | NZMP.com</t>
@@ -1111,7 +2038,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-high-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:25:12.820Z</t>
+    <t>2026-08-14T01:45:17.860Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder High Heat | NZMP.com</t>
@@ -1126,7 +2053,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-low-heat-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:25:20.420Z</t>
+    <t>2026-08-14T01:45:24.376Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Low Heat GDT Specification | NZMP.com</t>
@@ -1141,7 +2068,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-low-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:14.609Z</t>
+    <t>2026-08-14T01:46:18.662Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Low Heat | NZMP.com</t>
@@ -1153,13 +2080,13 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat-au.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat-au</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:24.471Z</t>
+    <t>2026-08-14T01:46:26.637Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Medium Heat (Australia Specification) | NZMP.com</t>
@@ -1174,7 +2101,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:32.036Z</t>
+    <t>2026-08-14T01:46:34.088Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Medium Heat GDT Specification | NZMP.com</t>
@@ -1189,7 +2116,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-medium-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:40.541Z</t>
+    <t>2026-08-14T01:46:43.360Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder Medium Heat | NZMP.com</t>
@@ -1204,7 +2131,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-uht-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:47.775Z</t>
+    <t>2026-08-14T01:46:51.521Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder for UHT Milk GDT Specification | NZMP.com</t>
@@ -1219,7 +2146,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/regular-skim-milk-powder-uht</t>
   </si>
   <si>
-    <t>2026-08-13T21:26:55.557Z</t>
+    <t>2026-08-14T01:47:00.675Z</t>
   </si>
   <si>
     <t>Regular Skim Milk Powder for UHT Milk | NZMP.com</t>
@@ -1234,7 +2161,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/smp-for-uht</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:02.437Z</t>
+    <t>2026-08-14T01:47:07.992Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/skim-milk-powder/smp-for-uht.html</t>
@@ -1246,7 +2173,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/super-fortified-instant-smp</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:11.234Z</t>
+    <t>2026-08-14T01:47:16.484Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/powders-concentrates/skim-milk-powder/super-fortified-instant-smp.html</t>
@@ -1258,7 +2185,7 @@
     <t>global/en/ingredients/powders-concentrates/skim-milk-powder/surestart-regular-smp-low-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:19.248Z</t>
+    <t>2026-08-14T01:47:23.983Z</t>
   </si>
   <si>
     <t>SureStart™ Regular Skim Milk Powder Low Heat | NZMP Ingredients | NZMP.com</t>
@@ -1273,7 +2200,7 @@
     <t>global/en/ingredients/powders-concentrates/whey-powder/nzmp-whey-powder-621</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:27.257Z</t>
+    <t>2026-08-14T01:47:33.421Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Powder 621 | NZMP.com</t>
@@ -1288,7 +2215,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/organic-regular-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:35.578Z</t>
+    <t>2026-08-14T01:47:41.419Z</t>
   </si>
   <si>
     <t>Organic Whole Milk Powder | NZMP.com</t>
@@ -1303,7 +2230,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-gdt</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:43.681Z</t>
+    <t>2026-08-14T01:47:50.696Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder GDT Specification | NZMP.com</t>
@@ -1318,7 +2245,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-high-heat</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:51.758Z</t>
+    <t>2026-08-14T01:48:00.589Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder High Heat | NZMP.com</t>
@@ -1333,7 +2260,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-repack</t>
   </si>
   <si>
-    <t>2026-08-13T21:27:58.959Z</t>
+    <t>2026-08-14T01:48:07.619Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Repack | NZMP.com</t>
@@ -1348,7 +2275,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-uht-28-fat</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:07.505Z</t>
+    <t>2026-08-14T01:48:16.238Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder 28% Fat for UHT | NZMP.com</t>
@@ -1363,7 +2290,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder-uht</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:16.195Z</t>
+    <t>2026-08-14T01:48:24.659Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for UHT Milk | NZMP.com</t>
@@ -1378,7 +2305,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-whole-milk-powder</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:25.141Z</t>
+    <t>2026-08-14T01:48:32.240Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder | NZMP.com</t>
@@ -1393,7 +2320,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-blending</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:32.225Z</t>
+    <t>2026-08-14T01:48:40.406Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Blending | NZMP.com</t>
@@ -1408,7 +2335,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-tea</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:40.528Z</t>
+    <t>2026-08-14T01:48:48.410Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Tea | NZMP.com</t>
@@ -1420,13 +2347,13 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-yoghurt.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/regular-wmp-for-yoghurt</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:48.780Z</t>
+    <t>2026-08-14T01:48:56.432Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder for Yoghurt | NZMP.com</t>
@@ -1441,7 +2368,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/whole-milk-powder-recombined-evaporated-milk</t>
   </si>
   <si>
-    <t>2026-08-13T21:28:55.898Z</t>
+    <t>2026-08-14T01:49:05.260Z</t>
   </si>
   <si>
     <t>Whole Milk Powder for Recombined Evaporated Milk | NZMP.com</t>
@@ -1456,7 +2383,7 @@
     <t>global/en/ingredients/powders-concentrates/whole-milk-powder/wmp-uht-perform</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:03.666Z</t>
+    <t>2026-08-14T01:49:12.961Z</t>
   </si>
   <si>
     <t>Regular Whole Milk Powder UHT Perform - NZMP Ingredients | NZMP.com</t>
@@ -1468,13 +2395,13 @@
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-7051.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-7051</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:31.160Z</t>
+    <t>2026-08-14T01:50:39.923Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Hydrolysate 7051 | NZMP.com</t>
@@ -1486,13 +2413,13 @@
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-821.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-821</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:39.060Z</t>
+    <t>2026-08-14T01:50:48.060Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Hydrolysate 821 | NZMP.com</t>
@@ -1504,13 +2431,13 @@
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-917.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/hydrolysates/nzmp-whey-protein-hydrolysate-917</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:46.974Z</t>
+    <t>2026-08-14T01:50:56.661Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Hydrolysate 917 | NZMP.com</t>
@@ -1522,13 +2449,13 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-470.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-470</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:54.400Z</t>
+    <t>2026-08-14T01:51:03.920Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 470 | NZMP.com</t>
@@ -1540,13 +2467,13 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-485.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-485</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:04.397Z</t>
+    <t>2026-08-14T01:51:14.071Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 485 | NZMP.com</t>
@@ -1555,13 +2482,37 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-milk-protein-concentrate-485.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4424-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4424-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:20.860Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4424-yoghurt.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-470-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-470-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:29.757Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-470-yoghurt.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4851.report.json</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4851</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:14.149Z</t>
+    <t>2026-08-14T01:51:23.683Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4851 | NZMP.com</t>
@@ -1570,13 +2521,25 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4851.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:35.757Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861-yoghurt.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861.report.json</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:23.524Z</t>
+    <t>2026-08-14T01:51:33.624Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4861 | NZMP.com</t>
@@ -1585,16 +2548,52 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4861.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4862-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4862-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:43.260Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4862-yoghurt.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4867.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4867</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:49.341Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4867.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:51:56.622Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882-yoghurt.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4882</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:35.766Z</t>
+    <t>2026-08-14T01:51:45.230Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4882 | NZMP.com</t>
@@ -1609,7 +2608,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4887</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:46.378Z</t>
+    <t>2026-08-14T01:51:54.159Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Concentrate 4887 | NZMP.com</t>
@@ -1618,13 +2617,25 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-mpc-4887.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-shortbar-milk-protein-concentrate-4857.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-shortbar-milk-protein-concentrate-4857</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:04.924Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/milk-protein-concentrates/nzmp-shortbar-milk-protein-concentrate-4857.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-sureprotein-mpc-4881.report.json</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/milk-protein-concentrates/nzmp-sureprotein-mpc-4881</t>
   </si>
   <si>
-    <t>2026-08-13T21:31:55.459Z</t>
+    <t>2026-08-14T01:52:04.114Z</t>
   </si>
   <si>
     <t>SureProtein™ Milk Protein Concentrate 4881 | NZMP.com</t>
@@ -1639,7 +2650,7 @@
     <t>global/en/ingredients/proteins/milk-protein-concentrates/organic-milk-protein-concentrate-485</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:03.223Z</t>
+    <t>2026-08-14T01:52:13.022Z</t>
   </si>
   <si>
     <t>Organic Milk Protein Concentrate (Regular 85%) | NZMP.com</t>
@@ -1654,7 +2665,7 @@
     <t>global/en/ingredients/proteins/milk-protein-isolates/nzmp-milk-protein-isolate-4900</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:11.864Z</t>
+    <t>2026-08-14T01:52:21.729Z</t>
   </si>
   <si>
     <t>NZMP™ Milk Protein Isolate 4900 | NZMP.com</t>
@@ -1669,7 +2680,7 @@
     <t>global/en/ingredients/proteins/milk-protein-isolates/nzmp-softbar-1000</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:19.837Z</t>
+    <t>2026-08-14T01:52:29.172Z</t>
   </si>
   <si>
     <t>SureProtein™ Milk Protein Isolate SoftBar 1000 | NZMP.com</t>
@@ -1684,7 +2695,7 @@
     <t>global/en/ingredients/proteins/total-milk-proteins/nzmp-total-milk-protein-shortbar-1104</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:27.023Z</t>
+    <t>2026-08-14T01:52:37.097Z</t>
   </si>
   <si>
     <t>SureProtein™ Total Milk Protein ShortBar 1104 | NZMP.com</t>
@@ -1699,7 +2710,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-bioactive-whey-protein</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:36.202Z</t>
+    <t>2026-08-14T01:52:45.939Z</t>
   </si>
   <si>
     <t>Bioactive Whey Protein | NZMP.com</t>
@@ -1714,7 +2725,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-dairy-protein-crisps-crispbar</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:43.023Z</t>
+    <t>2026-08-14T01:52:54.158Z</t>
   </si>
   <si>
     <t>NZMP™ Dairy Protein Crisps 600 | NZMP.com</t>
@@ -1729,7 +2740,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flex-wpc-515</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:50.124Z</t>
+    <t>2026-08-14T01:53:01.874Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 515 | NZMP.com</t>
@@ -1738,13 +2749,25 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flex-wpc-515.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flexbar.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flexbar</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:26.525Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flexbar.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flow-wpc-510.report.json</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-flow-wpc-510</t>
   </si>
   <si>
-    <t>2026-08-13T21:32:58.520Z</t>
+    <t>2026-08-14T01:53:08.822Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 510 | NZMP.com</t>
@@ -1759,7 +2782,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-instant-whey-protein-concentrate-450</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:05.241Z</t>
+    <t>2026-08-14T01:53:16.060Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Concentrate 450 | NZMP.com</t>
@@ -1774,7 +2797,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-pro-optima-wpc-567</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:14.959Z</t>
+    <t>2026-08-14T01:53:26.564Z</t>
   </si>
   <si>
     <t>NZMP™ Pro-Optima™ Whey Protein Concentrate | NZMP.com</t>
@@ -1783,16 +2806,28 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-pro-optima-wpc-567.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-surestart-whey-protein-concentrate-392.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-surestart-whey-protein-concentrate-392</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:34.460Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-surestart-whey-protein-concentrate-392.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-132.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-132</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:23.568Z</t>
+    <t>2026-08-14T01:53:33.622Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 132 | NZMP.com</t>
@@ -1807,7 +2842,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-162</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:31.064Z</t>
+    <t>2026-08-14T01:53:41.522Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 162 | NZMP.com</t>
@@ -1822,7 +2857,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-322</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:38.541Z</t>
+    <t>2026-08-14T01:53:49.958Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 322 | NZMP.com</t>
@@ -1834,13 +2869,13 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-352.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-352</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:46.260Z</t>
+    <t>2026-08-14T01:53:58.804Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 352 | NZMP.com</t>
@@ -1855,7 +2890,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-356</t>
   </si>
   <si>
-    <t>2026-08-13T21:33:55.126Z</t>
+    <t>2026-08-14T01:54:07.224Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 356 | NZMP.com</t>
@@ -1870,7 +2905,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-392</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:03.101Z</t>
+    <t>2026-08-14T01:54:15.790Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 392 | NZMP.com</t>
@@ -1885,7 +2920,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-397</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:12.338Z</t>
+    <t>2026-08-14T01:54:23.819Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 397 | NZMP.com</t>
@@ -1900,7 +2935,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-457-decolorized</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:20.137Z</t>
+    <t>2026-08-14T01:54:33.675Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 457 | NZMP.com</t>
@@ -1915,7 +2950,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-472</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:29.223Z</t>
+    <t>2026-08-14T01:54:42.974Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 472 | NZMP.com</t>
@@ -1930,7 +2965,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-480-instantised</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:36.615Z</t>
+    <t>2026-08-14T01:54:50.322Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Concentrate 480 | NZMP.com</t>
@@ -1945,7 +2980,7 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-whey-protein-concentrate-7009</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:44.423Z</t>
+    <t>2026-08-14T01:54:58.322Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 7009 | NZMP.com</t>
@@ -1957,13 +2992,13 @@
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-550.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
+    <t>["columns-product","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","columns-feature","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","cards-benefit","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-550</t>
   </si>
   <si>
-    <t>2026-08-13T21:34:52.271Z</t>
+    <t>2026-08-14T01:55:07.591Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Concentrate 550 | NZMP.com</t>
@@ -1972,13 +3007,25 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-550.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-gelling-yoghurt.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-gelling-yoghurt</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:41.460Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-concentrates/nzmp-wpc-gelling-yoghurt.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/organic-whey-protein-concentrate-392.report.json</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-concentrates/organic-whey-protein-concentrate-392</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:00.210Z</t>
+    <t>2026-08-14T01:55:15.558Z</t>
   </si>
   <si>
     <t>Organic Whey Protein Concentrate (Regular 80% Protein) | NZMP.com</t>
@@ -1993,7 +3040,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/lactoferrin</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:11.675Z</t>
+    <t>2026-08-14T01:55:25.689Z</t>
   </si>
   <si>
     <t>Lactoferrin - NZMP Dairy Ingredients | NZMP.com</t>
@@ -2008,7 +3055,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-clear-wpi-8855</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:22.459Z</t>
+    <t>2026-08-14T01:55:34.960Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Isolate 8855 | NZMP.com</t>
@@ -2023,7 +3070,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-instant-whey-protein-isolate-894</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:30.120Z</t>
+    <t>2026-08-14T01:55:42.802Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Isolate 894 | NZMP.com</t>
@@ -2038,7 +3085,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-instant-whey-protein-isolate-895</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:39.122Z</t>
+    <t>2026-08-14T01:55:50.560Z</t>
   </si>
   <si>
     <t>NZMP™ Instant Whey Protein Isolate 895 | NZMP.com</t>
@@ -2053,7 +3100,7 @@
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-optibar</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:47.659Z</t>
+    <t>2026-08-14T01:55:59.115Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Isolate 894 | NZMP.com</t>
@@ -2062,13 +3109,25 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-isolates/nzmp-optibar.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-shortbar-825.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-shortbar-825</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:52:55.259Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/whey-protein-isolates/nzmp-shortbar-825.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-wpi-895.report.json</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/whey-protein-isolates/nzmp-wpi-895</t>
   </si>
   <si>
-    <t>2026-08-13T21:35:54.879Z</t>
+    <t>2026-08-14T01:56:06.224Z</t>
   </si>
   <si>
     <t>NZMP™ Whey Protein Isolate 895 | NZMP.com</t>
@@ -2083,7 +3142,7 @@
     <t>global/en/ingredients/specialty/complex-lipids/milk-phospholipids</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:03.923Z</t>
+    <t>2026-08-14T01:56:59.960Z</t>
   </si>
   <si>
     <t>Milk Phospholipids | NZMP.com</t>
@@ -2098,7 +3157,7 @@
     <t>global/en/ingredients/specialty/complex-lipids/surestart-mfgm-lipids</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:11.920Z</t>
+    <t>2026-08-14T01:57:08.825Z</t>
   </si>
   <si>
     <t>SureStart™ MFGM Lipids | NZMP.com</t>
@@ -2107,13 +3166,37 @@
     <t>https://www.nzmp.com/global/en/ingredients/specialty/complex-lipids/surestart-mfgm-lipids.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-817.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-817</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:15.653Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-817.html</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-shortbar-911.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-shortbar-911</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:22.328Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-shortbar-911.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-softbar-917.report.json</t>
   </si>
   <si>
     <t>global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-softbar-917</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:19.760Z</t>
+    <t>2026-08-14T01:57:18.225Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/specialty/hydrolysates/nzmp-whey-protein-hydrolysate-softbar-917.html</t>
@@ -2125,7 +3208,7 @@
     <t>global/en/ingredients/specialty/lactoferrin/nzmp-lactoferrin</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:30.370Z</t>
+    <t>2026-08-14T01:57:27.289Z</t>
   </si>
   <si>
     <t>https://www.nzmp.com/global/en/ingredients/specialty/lactoferrin/nzmp-lactoferrin.html</t>
@@ -2137,7 +3220,7 @@
     <t>global/en/ingredients/specialty/lactoferrin/surestart-lactoferrin</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:40.029Z</t>
+    <t>2026-08-14T01:57:34.423Z</t>
   </si>
   <si>
     <t>Paediatric Lactoferrin - NZMP Dairy Ingredients | NZMP.com</t>
@@ -2149,13 +3232,13 @@
     <t>global/en/ingredients/specialty/prebiotics/galacto-oligosaccharide-gos-prebiotic-fibre.report.json</t>
   </si>
   <si>
-    <t>["breadcrumb","columns-product","columns-feature","carousel-news"]</t>
+    <t>["columns-product","columns-feature","carousel-news"]</t>
   </si>
   <si>
     <t>global/en/ingredients/specialty/prebiotics/galacto-oligosaccharide-gos-prebiotic-fibre</t>
   </si>
   <si>
-    <t>2026-08-13T21:36:47.087Z</t>
+    <t>2026-08-14T01:57:41.244Z</t>
   </si>
   <si>
     <t>Galacto-oligosaccharide (GOS) Prebiotic Fibre | NZMP.com</t>
@@ -2164,13 +3247,88 @@
     <t>https://www.nzmp.com/global/en/ingredients/specialty/prebiotics/galacto-oligosaccharide-gos-prebiotic-fibre.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/specialty/prebiotics/surestart-galacto-oligosaccharide-gos.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/specialty/prebiotics/surestart-galacto-oligosaccharide-gos</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:53:52.286Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/specialty/prebiotics/surestart-galacto-oligosaccharide-gos.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/china-dairy-expertise.report.json</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/china-dairy-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:22.422Z</t>
+  </si>
+  <si>
+    <t>Our China Dairy Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-global-expertise/china-dairy-expertise.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/europe-dairy-expertise.report.json</t>
+  </si>
+  <si>
+    <t>["breadcrumb","columns-banner","columns-feature","cards-value"]</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/europe-dairy-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:30.887Z</t>
+  </si>
+  <si>
+    <t>Our Europe Dairy Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-global-expertise/europe-dairy-expertise.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/middle-east-africa-dairy-expertise.report.json</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/middle-east-africa-dairy-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:42.257Z</t>
+  </si>
+  <si>
+    <t>Our Middle East &amp; Africa Dairy Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-global-expertise/middle-east-africa-dairy-expertise.html</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/south-southeast-asia-dairy-expertise.report.json</t>
+  </si>
+  <si>
+    <t>global/en/solutions/innovation-and-ingenuity/our-global-expertise/south-southeast-asia-dairy-expertise</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:54:50.940Z</t>
+  </si>
+  <si>
+    <t>Our South &amp; Southeast Asia Dairy Expertise | NZMP.com</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/solutions/innovation-and-ingenuity/our-global-expertise/south-southeast-asia-dairy-expertise.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/acid-casein-741.report.json</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/acid-casein-741</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:11.783Z</t>
+    <t>2026-08-14T01:49:20.157Z</t>
   </si>
   <si>
     <t>NZMP™ Mineral Acid Casein 741 | NZMP.com</t>
@@ -2185,7 +3343,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-720</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:20.067Z</t>
+    <t>2026-08-14T01:49:27.566Z</t>
   </si>
   <si>
     <t>NZMP™ Lactic Acid Casein 720 | NZMP.com</t>
@@ -2194,13 +3352,25 @@
     <t>https://www.nzmp.com/global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-720.html</t>
   </si>
   <si>
+    <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-730.report.json</t>
+  </si>
+  <si>
+    <t>global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-730</t>
+  </si>
+  <si>
+    <t>2026-08-13T23:50:51.273Z</t>
+  </si>
+  <si>
+    <t>https://www.nzmp.com/global/en/ingredients/proteins/caseins-and-caseinates/acid-casein/nzmp-lactic-casein-730.html</t>
+  </si>
+  <si>
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/calcium-caseinate-380.report.json</t>
   </si>
   <si>
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/calcium-caseinate-380</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:29.514Z</t>
+    <t>2026-08-14T01:49:36.519Z</t>
   </si>
   <si>
     <t>NZMP™ Calcium Caseinate 380 | NZMP.com</t>
@@ -2215,7 +3385,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-calcium-caseinate-309</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:38.385Z</t>
+    <t>2026-08-14T01:49:43.201Z</t>
   </si>
   <si>
     <t>NZMP™ Calcium Caseinate 309 | NZMP.com</t>
@@ -2230,7 +3400,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-calcium-caseinate-385</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:44.925Z</t>
+    <t>2026-08-14T01:49:50.249Z</t>
   </si>
   <si>
     <t>NZMP™ Calcium Caseinate 385 | NZMP.com</t>
@@ -2245,7 +3415,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-sodium-caseinate-166</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:52.923Z</t>
+    <t>2026-08-14T01:49:58.924Z</t>
   </si>
   <si>
     <t>NZMP™ Sodium Caseinate 166 | NZMP.com</t>
@@ -2260,7 +3430,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-sodium-caseinate-167</t>
   </si>
   <si>
-    <t>2026-08-13T21:29:59.659Z</t>
+    <t>2026-08-14T01:50:06.679Z</t>
   </si>
   <si>
     <t>NZMP™ Sodium Caseinate 167 | NZMP.com</t>
@@ -2275,7 +3445,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/caseinates/nzmp-sodium-caseinate-180</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:08.423Z</t>
+    <t>2026-08-14T01:50:14.760Z</t>
   </si>
   <si>
     <t>NZMP™ Sodium Caseinate 180 | NZMP.com</t>
@@ -2290,7 +3460,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/rennet-casein/nzmp-rennet-casein-771</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:15.159Z</t>
+    <t>2026-08-14T01:50:22.923Z</t>
   </si>
   <si>
     <t>NZMP™ Rennet Casein 771 | NZMP.com</t>
@@ -2305,7 +3475,7 @@
     <t>global/en/ingredients/proteins/caseins-and-caseinates/rennet-casein/sureprotein-rennet-casein-779</t>
   </si>
   <si>
-    <t>2026-08-13T21:30:22.578Z</t>
+    <t>2026-08-14T01:50:30.844Z</t>
   </si>
   <si>
     <t>NZMP™ Rennet Casein 779 | NZMP.com</t>
@@ -2700,7 +3870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -2844,10 +4014,10 @@
         <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
@@ -2856,24 +4026,24 @@
         <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -2882,24 +4052,24 @@
         <v>19</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
@@ -2908,21 +4078,21 @@
         <v>19</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
         <v>54</v>
@@ -2974,10 +4144,10 @@
         <v>64</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
@@ -2986,21 +4156,21 @@
         <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
         <v>71</v>
@@ -3015,18 +4185,18 @@
         <v>72</v>
       </c>
       <c r="G12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" t="s">
         <v>73</v>
-      </c>
-      <c r="H12" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s">
         <v>75</v>
-      </c>
-      <c r="B13" t="s">
-        <v>70</v>
       </c>
       <c r="C13" t="s">
         <v>76</v>
@@ -3052,10 +4222,10 @@
         <v>80</v>
       </c>
       <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
         <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
@@ -3064,21 +4234,21 @@
         <v>19</v>
       </c>
       <c r="F14" t="s">
+        <v>82</v>
+      </c>
+      <c r="G14" t="s">
         <v>83</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>84</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
         <v>86</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
       </c>
       <c r="C15" t="s">
         <v>87</v>
@@ -3104,10 +4274,10 @@
         <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
@@ -3116,24 +4286,24 @@
         <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
@@ -3142,24 +4312,24 @@
         <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>103</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
@@ -3168,24 +4338,24 @@
         <v>19</v>
       </c>
       <c r="F18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G18" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H18" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
@@ -3194,24 +4364,24 @@
         <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G19" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="H19" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
@@ -3220,24 +4390,24 @@
         <v>19</v>
       </c>
       <c r="F20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
@@ -3246,24 +4416,24 @@
         <v>19</v>
       </c>
       <c r="F21" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
@@ -3272,24 +4442,24 @@
         <v>19</v>
       </c>
       <c r="F22" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="H22" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>131</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
@@ -3298,24 +4468,24 @@
         <v>19</v>
       </c>
       <c r="F23" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G23" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -3324,24 +4494,24 @@
         <v>19</v>
       </c>
       <c r="F24" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G24" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H24" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
@@ -3350,24 +4520,24 @@
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G25" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H25" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="C26" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
@@ -3376,24 +4546,24 @@
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G26" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="H26" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C27" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D27" t="s">
         <v>11</v>
@@ -3402,24 +4572,24 @@
         <v>19</v>
       </c>
       <c r="F27" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G27" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="H27" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="D28" t="s">
         <v>11</v>
@@ -3428,24 +4598,24 @@
         <v>19</v>
       </c>
       <c r="F28" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="D29" t="s">
         <v>11</v>
@@ -3454,24 +4624,24 @@
         <v>19</v>
       </c>
       <c r="F29" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="G29" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="H29" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B30" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="D30" t="s">
         <v>11</v>
@@ -3480,24 +4650,24 @@
         <v>19</v>
       </c>
       <c r="F30" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G30" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H30" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>166</v>
       </c>
       <c r="C31" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="D31" t="s">
         <v>11</v>
@@ -3506,24 +4676,24 @@
         <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="G31" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H31" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="B32" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="C32" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D32" t="s">
         <v>11</v>
@@ -3532,24 +4702,24 @@
         <v>19</v>
       </c>
       <c r="F32" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="G32" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="H32" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="D33" t="s">
         <v>11</v>
@@ -3558,24 +4728,24 @@
         <v>19</v>
       </c>
       <c r="F33" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G33" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="H33" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
       <c r="C34" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="D34" t="s">
         <v>11</v>
@@ -3584,24 +4754,24 @@
         <v>19</v>
       </c>
       <c r="F34" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="G34" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="H34" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="C35" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="D35" t="s">
         <v>11</v>
@@ -3610,24 +4780,24 @@
         <v>19</v>
       </c>
       <c r="F35" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="G35" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="H35" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>205</v>
       </c>
       <c r="C36" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="D36" t="s">
         <v>11</v>
@@ -3636,24 +4806,24 @@
         <v>19</v>
       </c>
       <c r="F36" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="G36" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="H36" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="D37" t="s">
         <v>11</v>
@@ -3662,50 +4832,50 @@
         <v>19</v>
       </c>
       <c r="F37" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="G37" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="H37" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C38" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D38" t="s">
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F38" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="G38" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="H38" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="C39" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="D39" t="s">
         <v>11</v>
@@ -3714,24 +4884,24 @@
         <v>19</v>
       </c>
       <c r="F39" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="G39" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="H39" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>223</v>
       </c>
       <c r="C40" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="D40" t="s">
         <v>11</v>
@@ -3740,24 +4910,24 @@
         <v>19</v>
       </c>
       <c r="F40" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="G40" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="H40" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
       <c r="C41" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="D41" t="s">
         <v>11</v>
@@ -3766,24 +4936,24 @@
         <v>19</v>
       </c>
       <c r="F41" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="G41" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="H41" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>238</v>
+      </c>
+      <c r="B42" t="s">
         <v>223</v>
       </c>
-      <c r="B42" t="s">
-        <v>53</v>
-      </c>
       <c r="C42" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="D42" t="s">
         <v>11</v>
@@ -3792,24 +4962,24 @@
         <v>19</v>
       </c>
       <c r="F42" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G42" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="H42" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="C43" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="D43" t="s">
         <v>11</v>
@@ -3818,24 +4988,24 @@
         <v>19</v>
       </c>
       <c r="F43" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="G43" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="H43" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="D44" t="s">
         <v>11</v>
@@ -3844,24 +5014,24 @@
         <v>19</v>
       </c>
       <c r="F44" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="G44" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="H44" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>254</v>
       </c>
       <c r="C45" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="D45" t="s">
         <v>11</v>
@@ -3870,24 +5040,24 @@
         <v>19</v>
       </c>
       <c r="F45" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="G45" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="H45" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="C46" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>11</v>
@@ -3896,24 +5066,24 @@
         <v>19</v>
       </c>
       <c r="F46" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="G46" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="H46" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="C47" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="D47" t="s">
         <v>11</v>
@@ -3922,24 +5092,24 @@
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="G47" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="H47" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="B48" t="s">
-        <v>41</v>
+        <v>223</v>
       </c>
       <c r="C48" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="D48" t="s">
         <v>11</v>
@@ -3948,24 +5118,24 @@
         <v>19</v>
       </c>
       <c r="F48" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="G48" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="H48" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="B49" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="C49" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="D49" t="s">
         <v>11</v>
@@ -3974,24 +5144,24 @@
         <v>19</v>
       </c>
       <c r="F49" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="G49" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="H49" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="C50" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="D50" t="s">
         <v>11</v>
@@ -4000,24 +5170,24 @@
         <v>19</v>
       </c>
       <c r="F50" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="G50" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="H50" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>254</v>
       </c>
       <c r="C51" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="D51" t="s">
         <v>11</v>
@@ -4026,24 +5196,24 @@
         <v>19</v>
       </c>
       <c r="F51" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="G51" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="H51" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>290</v>
       </c>
       <c r="C52" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="D52" t="s">
         <v>11</v>
@@ -4052,24 +5222,24 @@
         <v>19</v>
       </c>
       <c r="F52" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="G52" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="H52" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B53" t="s">
-        <v>280</v>
+        <v>166</v>
       </c>
       <c r="C53" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="D53" t="s">
         <v>11</v>
@@ -4078,24 +5248,24 @@
         <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="G53" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="H53" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B54" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="C54" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="D54" t="s">
         <v>11</v>
@@ -4104,24 +5274,24 @@
         <v>19</v>
       </c>
       <c r="F54" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="G54" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="H54" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>306</v>
       </c>
       <c r="C55" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D55" t="s">
         <v>11</v>
@@ -4130,24 +5300,24 @@
         <v>19</v>
       </c>
       <c r="F55" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="G55" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="H55" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>312</v>
       </c>
       <c r="C56" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="D56" t="s">
         <v>11</v>
@@ -4156,24 +5326,24 @@
         <v>19</v>
       </c>
       <c r="F56" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="G56" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="H56" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="C57" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="D57" t="s">
         <v>11</v>
@@ -4182,24 +5352,24 @@
         <v>19</v>
       </c>
       <c r="F57" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="G57" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="H57" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B58" t="s">
-        <v>286</v>
+        <v>323</v>
       </c>
       <c r="C58" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="D58" t="s">
         <v>11</v>
@@ -4208,362 +5378,362 @@
         <v>19</v>
       </c>
       <c r="F58" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="G58" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="H58" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B59" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="C59" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D59" t="s">
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F59" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="G59" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="H59" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B60" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C60" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="D60" t="s">
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F60" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="G60" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="H60" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="B61" t="s">
-        <v>323</v>
+        <v>216</v>
       </c>
       <c r="C61" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="D61" t="s">
         <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F61" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="G61" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="H61" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B62" t="s">
-        <v>311</v>
+        <v>346</v>
       </c>
       <c r="C62" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
       </c>
       <c r="E62" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F62" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="G62" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="H62" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>352</v>
       </c>
       <c r="C63" t="s">
-        <v>334</v>
+        <v>353</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
       </c>
       <c r="E63" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F63" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="G63" t="s">
-        <v>336</v>
+        <v>355</v>
       </c>
       <c r="H63" t="s">
-        <v>337</v>
+        <v>356</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="B64" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="C64" t="s">
-        <v>340</v>
+        <v>359</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
       </c>
       <c r="E64" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F64" t="s">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="G64" t="s">
-        <v>342</v>
+        <v>361</v>
       </c>
       <c r="H64" t="s">
-        <v>343</v>
+        <v>362</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>364</v>
       </c>
       <c r="C65" t="s">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="D65" t="s">
         <v>11</v>
       </c>
       <c r="E65" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F65" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="G65" t="s">
-        <v>347</v>
+        <v>367</v>
       </c>
       <c r="H65" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>349</v>
+        <v>369</v>
       </c>
       <c r="B66" t="s">
-        <v>53</v>
+        <v>358</v>
       </c>
       <c r="C66" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="D66" t="s">
         <v>11</v>
       </c>
       <c r="E66" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F66" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="G66" t="s">
-        <v>352</v>
+        <v>372</v>
       </c>
       <c r="H66" t="s">
-        <v>353</v>
+        <v>373</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>354</v>
+        <v>374</v>
       </c>
       <c r="B67" t="s">
-        <v>41</v>
+        <v>375</v>
       </c>
       <c r="C67" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="D67" t="s">
         <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F67" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="G67" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="H67" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="B68" t="s">
-        <v>24</v>
+        <v>375</v>
       </c>
       <c r="C68" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="D68" t="s">
         <v>11</v>
       </c>
       <c r="E68" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F68" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="G68" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="H68" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>386</v>
       </c>
       <c r="C69" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="D69" t="s">
         <v>11</v>
       </c>
       <c r="E69" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F69" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="G69" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="H69" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>216</v>
       </c>
       <c r="C70" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="D70" t="s">
         <v>11</v>
       </c>
       <c r="E70" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F70" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="G70" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="H70" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>335</v>
       </c>
       <c r="C71" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="D71" t="s">
         <v>11</v>
       </c>
       <c r="E71" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F71" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="G71" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="H71" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="B72" t="s">
-        <v>380</v>
+        <v>149</v>
       </c>
       <c r="C72" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="D72" t="s">
         <v>11</v>
@@ -4572,1963 +5742,3913 @@
         <v>19</v>
       </c>
       <c r="F72" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="G72" t="s">
-        <v>383</v>
+        <v>152</v>
       </c>
       <c r="H72" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>216</v>
       </c>
       <c r="C73" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="D73" t="s">
         <v>11</v>
       </c>
       <c r="E73" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F73" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="G73" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="H73" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="B74" t="s">
-        <v>380</v>
+        <v>335</v>
       </c>
       <c r="C74" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="D74" t="s">
         <v>11</v>
       </c>
       <c r="E74" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F74" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="G74" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="H74" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>335</v>
       </c>
       <c r="C75" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="D75" t="s">
         <v>11</v>
       </c>
       <c r="E75" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F75" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="G75" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="H75" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>375</v>
       </c>
       <c r="C76" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="D76" t="s">
         <v>11</v>
       </c>
       <c r="E76" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F76" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="G76" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="H76" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>329</v>
       </c>
       <c r="C77" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="D77" t="s">
         <v>11</v>
       </c>
       <c r="E77" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F77" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="G77" t="s">
-        <v>403</v>
+        <v>428</v>
       </c>
       <c r="H77" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="B78" t="s">
-        <v>311</v>
+        <v>431</v>
       </c>
       <c r="C78" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="D78" t="s">
         <v>11</v>
       </c>
       <c r="E78" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F78" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="G78" t="s">
-        <v>331</v>
+        <v>434</v>
       </c>
       <c r="H78" t="s">
-        <v>412</v>
+        <v>435</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="B79" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C79" t="s">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="D79" t="s">
         <v>11</v>
       </c>
       <c r="E79" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F79" t="s">
-        <v>415</v>
+        <v>438</v>
       </c>
       <c r="G79" t="s">
-        <v>416</v>
+        <v>439</v>
       </c>
       <c r="H79" t="s">
-        <v>417</v>
+        <v>440</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>418</v>
+        <v>441</v>
       </c>
       <c r="B80" t="s">
-        <v>24</v>
+        <v>375</v>
       </c>
       <c r="C80" t="s">
-        <v>419</v>
+        <v>442</v>
       </c>
       <c r="D80" t="s">
         <v>11</v>
       </c>
       <c r="E80" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F80" t="s">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="G80" t="s">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="H80" t="s">
-        <v>422</v>
+        <v>445</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>423</v>
+        <v>446</v>
       </c>
       <c r="B81" t="s">
-        <v>41</v>
+        <v>364</v>
       </c>
       <c r="C81" t="s">
-        <v>424</v>
+        <v>447</v>
       </c>
       <c r="D81" t="s">
         <v>11</v>
       </c>
       <c r="E81" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F81" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="G81" t="s">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="H81" t="s">
-        <v>427</v>
+        <v>450</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>428</v>
+        <v>451</v>
       </c>
       <c r="B82" t="s">
-        <v>30</v>
+        <v>335</v>
       </c>
       <c r="C82" t="s">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="D82" t="s">
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F82" t="s">
-        <v>430</v>
+        <v>453</v>
       </c>
       <c r="G82" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="H82" t="s">
-        <v>432</v>
+        <v>455</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>433</v>
+        <v>456</v>
       </c>
       <c r="B83" t="s">
-        <v>30</v>
+        <v>457</v>
       </c>
       <c r="C83" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="D83" t="s">
         <v>11</v>
       </c>
       <c r="E83" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F83" t="s">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="G83" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="H83" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="B84" t="s">
-        <v>17</v>
+        <v>346</v>
       </c>
       <c r="C84" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="D84" t="s">
         <v>11</v>
       </c>
       <c r="E84" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F84" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="G84" t="s">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="H84" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="B85" t="s">
-        <v>30</v>
+        <v>346</v>
       </c>
       <c r="C85" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="D85" t="s">
         <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F85" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="G85" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="H85" t="s">
-        <v>447</v>
+        <v>471</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="B86" t="s">
-        <v>30</v>
+        <v>329</v>
       </c>
       <c r="C86" t="s">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="D86" t="s">
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F86" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="G86" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="H86" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="B87" t="s">
-        <v>317</v>
+        <v>358</v>
       </c>
       <c r="C87" t="s">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="D87" t="s">
         <v>11</v>
       </c>
       <c r="E87" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F87" t="s">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="G87" t="s">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="H87" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C88" t="s">
-        <v>459</v>
+        <v>483</v>
       </c>
       <c r="D88" t="s">
         <v>11</v>
       </c>
       <c r="E88" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F88" t="s">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="G88" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="H88" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="B89" t="s">
-        <v>17</v>
+        <v>216</v>
       </c>
       <c r="C89" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="D89" t="s">
         <v>11</v>
       </c>
       <c r="E89" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F89" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="G89" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="H89" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="B90" t="s">
-        <v>469</v>
+        <v>335</v>
       </c>
       <c r="C90" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="D90" t="s">
         <v>11</v>
       </c>
       <c r="E90" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F90" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="G90" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="H90" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>216</v>
       </c>
       <c r="C91" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="D91" t="s">
         <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F91" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="G91" t="s">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="H91" t="s">
-        <v>478</v>
+        <v>501</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>479</v>
+        <v>502</v>
       </c>
       <c r="B92" t="s">
-        <v>41</v>
+        <v>216</v>
       </c>
       <c r="C92" t="s">
-        <v>480</v>
+        <v>503</v>
       </c>
       <c r="D92" t="s">
         <v>11</v>
       </c>
       <c r="E92" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F92" t="s">
-        <v>481</v>
+        <v>504</v>
       </c>
       <c r="G92" t="s">
-        <v>482</v>
+        <v>505</v>
       </c>
       <c r="H92" t="s">
-        <v>483</v>
+        <v>506</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>484</v>
+        <v>507</v>
       </c>
       <c r="B93" t="s">
-        <v>485</v>
+        <v>364</v>
       </c>
       <c r="C93" t="s">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="D93" t="s">
         <v>11</v>
       </c>
       <c r="E93" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F93" t="s">
-        <v>487</v>
+        <v>509</v>
       </c>
       <c r="G93" t="s">
-        <v>488</v>
+        <v>510</v>
       </c>
       <c r="H93" t="s">
-        <v>489</v>
+        <v>511</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>490</v>
+        <v>512</v>
       </c>
       <c r="B94" t="s">
-        <v>491</v>
+        <v>329</v>
       </c>
       <c r="C94" t="s">
-        <v>492</v>
+        <v>513</v>
       </c>
       <c r="D94" t="s">
         <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F94" t="s">
-        <v>493</v>
+        <v>514</v>
       </c>
       <c r="G94" t="s">
-        <v>494</v>
+        <v>515</v>
       </c>
       <c r="H94" t="s">
-        <v>495</v>
+        <v>516</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="B95" t="s">
-        <v>497</v>
+        <v>386</v>
       </c>
       <c r="C95" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="D95" t="s">
         <v>11</v>
       </c>
       <c r="E95" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F95" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="G95" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="H95" t="s">
-        <v>501</v>
+        <v>521</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>502</v>
+        <v>522</v>
       </c>
       <c r="B96" t="s">
-        <v>503</v>
+        <v>358</v>
       </c>
       <c r="C96" t="s">
-        <v>504</v>
+        <v>523</v>
       </c>
       <c r="D96" t="s">
         <v>11</v>
       </c>
       <c r="E96" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F96" t="s">
-        <v>505</v>
+        <v>524</v>
       </c>
       <c r="G96" t="s">
-        <v>506</v>
+        <v>525</v>
       </c>
       <c r="H96" t="s">
-        <v>507</v>
+        <v>526</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>508</v>
+        <v>527</v>
       </c>
       <c r="B97" t="s">
-        <v>509</v>
+        <v>358</v>
       </c>
       <c r="C97" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="D97" t="s">
         <v>11</v>
       </c>
       <c r="E97" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F97" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="G97" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="H97" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="B98" t="s">
-        <v>503</v>
+        <v>358</v>
       </c>
       <c r="C98" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="D98" t="s">
         <v>11</v>
       </c>
       <c r="E98" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F98" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="G98" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="H98" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="B99" t="s">
-        <v>497</v>
+        <v>335</v>
       </c>
       <c r="C99" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="D99" t="s">
         <v>11</v>
       </c>
       <c r="E99" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F99" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="G99" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="H99" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="B100" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="C100" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="D100" t="s">
         <v>11</v>
       </c>
       <c r="E100" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F100" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="G100" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="H100" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s">
-        <v>503</v>
+        <v>216</v>
       </c>
       <c r="C101" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="D101" t="s">
         <v>11</v>
       </c>
       <c r="E101" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F101" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="G101" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="H101" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="B102" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C102" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="D102" t="s">
         <v>11</v>
       </c>
       <c r="E102" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F102" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="G102" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="H102" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="B103" t="s">
-        <v>70</v>
+        <v>216</v>
       </c>
       <c r="C103" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="D103" t="s">
         <v>11</v>
       </c>
       <c r="E103" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F103" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="G103" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="H103" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
       <c r="B104" t="s">
-        <v>41</v>
+        <v>346</v>
       </c>
       <c r="C104" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="D104" t="s">
         <v>11</v>
       </c>
       <c r="E104" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F104" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="G104" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="H104" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="B105" t="s">
-        <v>41</v>
+        <v>346</v>
       </c>
       <c r="C105" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="D105" t="s">
         <v>11</v>
       </c>
       <c r="E105" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F105" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="G105" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="H105" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
       <c r="B106" t="s">
-        <v>47</v>
+        <v>335</v>
       </c>
       <c r="C106" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="D106" t="s">
         <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F106" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="G106" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
       <c r="H106" t="s">
-        <v>559</v>
+        <v>577</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="B107" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="C107" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
       <c r="D107" t="s">
         <v>11</v>
       </c>
       <c r="E107" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F107" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="G107" t="s">
-        <v>563</v>
+        <v>581</v>
       </c>
       <c r="H107" t="s">
-        <v>564</v>
+        <v>582</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>565</v>
+        <v>583</v>
       </c>
       <c r="B108" t="s">
-        <v>503</v>
+        <v>335</v>
       </c>
       <c r="C108" t="s">
-        <v>566</v>
+        <v>584</v>
       </c>
       <c r="D108" t="s">
         <v>11</v>
       </c>
       <c r="E108" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F108" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="G108" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="H108" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>570</v>
+        <v>588</v>
       </c>
       <c r="B109" t="s">
-        <v>491</v>
+        <v>589</v>
       </c>
       <c r="C109" t="s">
-        <v>571</v>
+        <v>590</v>
       </c>
       <c r="D109" t="s">
         <v>11</v>
       </c>
       <c r="E109" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F109" t="s">
-        <v>572</v>
+        <v>591</v>
       </c>
       <c r="G109" t="s">
-        <v>573</v>
+        <v>592</v>
       </c>
       <c r="H109" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>575</v>
+        <v>594</v>
       </c>
       <c r="B110" t="s">
-        <v>485</v>
+        <v>595</v>
       </c>
       <c r="C110" t="s">
-        <v>576</v>
+        <v>596</v>
       </c>
       <c r="D110" t="s">
         <v>11</v>
       </c>
       <c r="E110" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F110" t="s">
-        <v>577</v>
+        <v>597</v>
       </c>
       <c r="G110" t="s">
-        <v>578</v>
+        <v>598</v>
       </c>
       <c r="H110" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="B111" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="C111" t="s">
-        <v>581</v>
+        <v>601</v>
       </c>
       <c r="D111" t="s">
         <v>11</v>
       </c>
       <c r="E111" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F111" t="s">
-        <v>582</v>
+        <v>602</v>
       </c>
       <c r="G111" t="s">
-        <v>583</v>
+        <v>603</v>
       </c>
       <c r="H111" t="s">
-        <v>584</v>
+        <v>604</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="B112" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="C112" t="s">
-        <v>586</v>
+        <v>606</v>
       </c>
       <c r="D112" t="s">
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F112" t="s">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="G112" t="s">
-        <v>588</v>
+        <v>608</v>
       </c>
       <c r="H112" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>590</v>
+        <v>610</v>
       </c>
       <c r="B113" t="s">
-        <v>591</v>
+        <v>335</v>
       </c>
       <c r="C113" t="s">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="D113" t="s">
         <v>11</v>
       </c>
       <c r="E113" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F113" t="s">
-        <v>593</v>
+        <v>612</v>
       </c>
       <c r="G113" t="s">
-        <v>594</v>
+        <v>613</v>
       </c>
       <c r="H113" t="s">
-        <v>595</v>
+        <v>614</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="B114" t="s">
-        <v>485</v>
+        <v>595</v>
       </c>
       <c r="C114" t="s">
-        <v>597</v>
+        <v>616</v>
       </c>
       <c r="D114" t="s">
         <v>11</v>
       </c>
       <c r="E114" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F114" t="s">
+        <v>617</v>
+      </c>
+      <c r="G114" t="s">
         <v>598</v>
       </c>
-      <c r="G114" t="s">
-        <v>599</v>
-      </c>
       <c r="H114" t="s">
-        <v>600</v>
+        <v>618</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="B115" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="C115" t="s">
-        <v>602</v>
+        <v>621</v>
       </c>
       <c r="D115" t="s">
         <v>11</v>
       </c>
       <c r="E115" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F115" t="s">
-        <v>603</v>
+        <v>622</v>
       </c>
       <c r="G115" t="s">
-        <v>604</v>
+        <v>623</v>
       </c>
       <c r="H115" t="s">
-        <v>605</v>
+        <v>624</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>606</v>
+        <v>625</v>
       </c>
       <c r="B116" t="s">
-        <v>607</v>
+        <v>626</v>
       </c>
       <c r="C116" t="s">
-        <v>608</v>
+        <v>627</v>
       </c>
       <c r="D116" t="s">
         <v>11</v>
       </c>
       <c r="E116" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F116" t="s">
-        <v>609</v>
+        <v>628</v>
       </c>
       <c r="G116" t="s">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c r="H116" t="s">
-        <v>611</v>
+        <v>630</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>612</v>
+        <v>631</v>
       </c>
       <c r="B117" t="s">
-        <v>485</v>
+        <v>632</v>
       </c>
       <c r="C117" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="D117" t="s">
         <v>11</v>
       </c>
       <c r="E117" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F117" t="s">
-        <v>614</v>
+        <v>634</v>
       </c>
       <c r="G117" t="s">
-        <v>615</v>
+        <v>635</v>
       </c>
       <c r="H117" t="s">
-        <v>616</v>
+        <v>636</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>617</v>
+        <v>637</v>
       </c>
       <c r="B118" t="s">
-        <v>497</v>
+        <v>620</v>
       </c>
       <c r="C118" t="s">
-        <v>618</v>
+        <v>638</v>
       </c>
       <c r="D118" t="s">
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F118" t="s">
-        <v>619</v>
+        <v>639</v>
       </c>
       <c r="G118" t="s">
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="H118" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="B119" t="s">
-        <v>485</v>
+        <v>216</v>
       </c>
       <c r="C119" t="s">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="D119" t="s">
         <v>11</v>
       </c>
       <c r="E119" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F119" t="s">
-        <v>624</v>
+        <v>644</v>
       </c>
       <c r="G119" t="s">
-        <v>625</v>
+        <v>645</v>
       </c>
       <c r="H119" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>627</v>
+        <v>647</v>
       </c>
       <c r="B120" t="s">
-        <v>491</v>
+        <v>648</v>
       </c>
       <c r="C120" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="D120" t="s">
         <v>11</v>
       </c>
       <c r="E120" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F120" t="s">
-        <v>629</v>
+        <v>650</v>
       </c>
       <c r="G120" t="s">
-        <v>630</v>
+        <v>651</v>
       </c>
       <c r="H120" t="s">
-        <v>631</v>
+        <v>652</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>632</v>
+        <v>653</v>
       </c>
       <c r="B121" t="s">
-        <v>591</v>
+        <v>335</v>
       </c>
       <c r="C121" t="s">
-        <v>633</v>
+        <v>654</v>
       </c>
       <c r="D121" t="s">
         <v>11</v>
       </c>
       <c r="E121" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F121" t="s">
-        <v>634</v>
+        <v>655</v>
       </c>
       <c r="G121" t="s">
-        <v>635</v>
+        <v>656</v>
       </c>
       <c r="H121" t="s">
-        <v>636</v>
+        <v>657</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>637</v>
+        <v>658</v>
       </c>
       <c r="B122" t="s">
-        <v>485</v>
+        <v>358</v>
       </c>
       <c r="C122" t="s">
-        <v>638</v>
+        <v>659</v>
       </c>
       <c r="D122" t="s">
         <v>11</v>
       </c>
       <c r="E122" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F122" t="s">
-        <v>639</v>
+        <v>660</v>
       </c>
       <c r="G122" t="s">
-        <v>640</v>
+        <v>661</v>
       </c>
       <c r="H122" t="s">
-        <v>641</v>
+        <v>662</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>642</v>
+        <v>663</v>
       </c>
       <c r="B123" t="s">
-        <v>591</v>
+        <v>346</v>
       </c>
       <c r="C123" t="s">
-        <v>643</v>
+        <v>664</v>
       </c>
       <c r="D123" t="s">
         <v>11</v>
       </c>
       <c r="E123" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F123" t="s">
-        <v>644</v>
+        <v>665</v>
       </c>
       <c r="G123" t="s">
-        <v>645</v>
+        <v>666</v>
       </c>
       <c r="H123" t="s">
-        <v>646</v>
+        <v>667</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>647</v>
+        <v>668</v>
       </c>
       <c r="B124" t="s">
-        <v>648</v>
+        <v>329</v>
       </c>
       <c r="C124" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="D124" t="s">
         <v>11</v>
       </c>
       <c r="E124" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F124" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="G124" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="H124" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="B125" t="s">
-        <v>17</v>
+        <v>335</v>
       </c>
       <c r="C125" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="D125" t="s">
         <v>11</v>
       </c>
       <c r="E125" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F125" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="G125" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="H125" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>658</v>
+        <v>678</v>
       </c>
       <c r="B126" t="s">
-        <v>469</v>
+        <v>335</v>
       </c>
       <c r="C126" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="D126" t="s">
         <v>11</v>
       </c>
       <c r="E126" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F126" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="G126" t="s">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="H126" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="B127" t="s">
-        <v>503</v>
+        <v>335</v>
       </c>
       <c r="C127" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="D127" t="s">
         <v>11</v>
       </c>
       <c r="E127" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F127" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="G127" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="H127" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="B128" t="s">
-        <v>485</v>
+        <v>689</v>
       </c>
       <c r="C128" t="s">
-        <v>669</v>
+        <v>690</v>
       </c>
       <c r="D128" t="s">
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F128" t="s">
-        <v>670</v>
+        <v>691</v>
       </c>
       <c r="G128" t="s">
-        <v>671</v>
+        <v>692</v>
       </c>
       <c r="H128" t="s">
-        <v>672</v>
+        <v>693</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>673</v>
+        <v>694</v>
       </c>
       <c r="B129" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="C129" t="s">
-        <v>674</v>
+        <v>695</v>
       </c>
       <c r="D129" t="s">
         <v>11</v>
       </c>
       <c r="E129" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F129" t="s">
-        <v>675</v>
+        <v>696</v>
       </c>
       <c r="G129" t="s">
-        <v>676</v>
+        <v>697</v>
       </c>
       <c r="H129" t="s">
-        <v>677</v>
+        <v>698</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>678</v>
+        <v>699</v>
       </c>
       <c r="B130" t="s">
-        <v>485</v>
+        <v>689</v>
       </c>
       <c r="C130" t="s">
-        <v>679</v>
+        <v>700</v>
       </c>
       <c r="D130" t="s">
         <v>11</v>
       </c>
       <c r="E130" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F130" t="s">
-        <v>680</v>
+        <v>701</v>
       </c>
       <c r="G130" t="s">
-        <v>681</v>
+        <v>702</v>
       </c>
       <c r="H130" t="s">
-        <v>682</v>
+        <v>703</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>683</v>
+        <v>704</v>
       </c>
       <c r="B131" t="s">
-        <v>491</v>
+        <v>375</v>
       </c>
       <c r="C131" t="s">
-        <v>684</v>
+        <v>705</v>
       </c>
       <c r="D131" t="s">
         <v>11</v>
       </c>
       <c r="E131" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F131" t="s">
-        <v>685</v>
+        <v>706</v>
       </c>
       <c r="G131" t="s">
-        <v>686</v>
+        <v>707</v>
       </c>
       <c r="H131" t="s">
-        <v>687</v>
+        <v>708</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>688</v>
+        <v>709</v>
       </c>
       <c r="B132" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="C132" t="s">
-        <v>689</v>
+        <v>710</v>
       </c>
       <c r="D132" t="s">
         <v>11</v>
       </c>
       <c r="E132" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F132" t="s">
-        <v>690</v>
+        <v>711</v>
       </c>
       <c r="G132" t="s">
-        <v>691</v>
+        <v>712</v>
       </c>
       <c r="H132" t="s">
-        <v>692</v>
+        <v>713</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>693</v>
+        <v>714</v>
       </c>
       <c r="B133" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="C133" t="s">
-        <v>694</v>
+        <v>715</v>
       </c>
       <c r="D133" t="s">
         <v>11</v>
       </c>
       <c r="E133" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F133" t="s">
-        <v>695</v>
+        <v>716</v>
       </c>
       <c r="G133" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="H133" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="B134" t="s">
-        <v>497</v>
+        <v>620</v>
       </c>
       <c r="C134" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
       <c r="D134" t="s">
         <v>11</v>
       </c>
       <c r="E134" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F134" t="s">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="G134" t="s">
-        <v>500</v>
+        <v>640</v>
       </c>
       <c r="H134" t="s">
-        <v>701</v>
+        <v>721</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="B135" t="s">
-        <v>469</v>
+        <v>648</v>
       </c>
       <c r="C135" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
       <c r="D135" t="s">
         <v>11</v>
       </c>
       <c r="E135" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F135" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="G135" t="s">
-        <v>661</v>
+        <v>725</v>
       </c>
       <c r="H135" t="s">
-        <v>705</v>
+        <v>726</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>706</v>
+        <v>727</v>
       </c>
       <c r="B136" t="s">
-        <v>17</v>
+        <v>329</v>
       </c>
       <c r="C136" t="s">
-        <v>707</v>
+        <v>728</v>
       </c>
       <c r="D136" t="s">
         <v>11</v>
       </c>
       <c r="E136" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F136" t="s">
-        <v>708</v>
+        <v>729</v>
       </c>
       <c r="G136" t="s">
-        <v>709</v>
+        <v>730</v>
       </c>
       <c r="H136" t="s">
-        <v>710</v>
+        <v>731</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>711</v>
+        <v>732</v>
       </c>
       <c r="B137" t="s">
-        <v>712</v>
+        <v>346</v>
       </c>
       <c r="C137" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
       <c r="D137" t="s">
         <v>11</v>
       </c>
       <c r="E137" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F137" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="G137" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="H137" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="B138" t="s">
-        <v>503</v>
+        <v>335</v>
       </c>
       <c r="C138" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="D138" t="s">
         <v>11</v>
       </c>
       <c r="E138" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F138" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="G138" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="H138" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>722</v>
+        <v>742</v>
       </c>
       <c r="B139" t="s">
-        <v>503</v>
+        <v>335</v>
       </c>
       <c r="C139" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="D139" t="s">
         <v>11</v>
       </c>
       <c r="E139" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F139" t="s">
-        <v>724</v>
+        <v>744</v>
       </c>
       <c r="G139" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="H139" t="s">
-        <v>726</v>
+        <v>746</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>727</v>
+        <v>747</v>
       </c>
       <c r="B140" t="s">
-        <v>525</v>
+        <v>216</v>
       </c>
       <c r="C140" t="s">
-        <v>728</v>
+        <v>748</v>
       </c>
       <c r="D140" t="s">
         <v>11</v>
       </c>
       <c r="E140" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F140" t="s">
-        <v>729</v>
+        <v>749</v>
       </c>
       <c r="G140" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
       <c r="H140" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>732</v>
+        <v>752</v>
       </c>
       <c r="B141" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="C141" t="s">
-        <v>733</v>
+        <v>753</v>
       </c>
       <c r="D141" t="s">
         <v>11</v>
       </c>
       <c r="E141" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F141" t="s">
-        <v>734</v>
+        <v>754</v>
       </c>
       <c r="G141" t="s">
-        <v>735</v>
+        <v>755</v>
       </c>
       <c r="H141" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="B142" t="s">
-        <v>485</v>
+        <v>335</v>
       </c>
       <c r="C142" t="s">
-        <v>738</v>
+        <v>758</v>
       </c>
       <c r="D142" t="s">
         <v>11</v>
       </c>
       <c r="E142" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F142" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="G142" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="H142" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="B143" t="s">
-        <v>591</v>
+        <v>626</v>
       </c>
       <c r="C143" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="D143" t="s">
         <v>11</v>
       </c>
       <c r="E143" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F143" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="G143" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="H143" t="s">
-        <v>746</v>
+        <v>766</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="B144" t="s">
-        <v>591</v>
+        <v>329</v>
       </c>
       <c r="C144" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="D144" t="s">
         <v>11</v>
       </c>
       <c r="E144" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F144" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="G144" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="H144" t="s">
-        <v>751</v>
+        <v>771</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="B145" t="s">
-        <v>485</v>
+        <v>216</v>
       </c>
       <c r="C145" t="s">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="D145" t="s">
         <v>11</v>
       </c>
       <c r="E145" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F145" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="G145" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="H145" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>757</v>
+        <v>777</v>
       </c>
       <c r="B146" t="s">
-        <v>148</v>
+        <v>778</v>
       </c>
       <c r="C146" t="s">
-        <v>758</v>
+        <v>779</v>
       </c>
       <c r="D146" t="s">
         <v>11</v>
       </c>
       <c r="E146" t="s">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="F146" t="s">
-        <v>759</v>
+        <v>780</v>
       </c>
       <c r="G146" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
       <c r="H146" t="s">
-        <v>761</v>
+        <v>782</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>762</v>
+        <v>783</v>
       </c>
       <c r="B147" t="s">
-        <v>148</v>
+        <v>329</v>
       </c>
       <c r="C147" t="s">
-        <v>763</v>
+        <v>784</v>
       </c>
       <c r="D147" t="s">
         <v>11</v>
       </c>
       <c r="E147" t="s">
+        <v>218</v>
+      </c>
+      <c r="F147" t="s">
+        <v>785</v>
+      </c>
+      <c r="G147" t="s">
+        <v>786</v>
+      </c>
+      <c r="H147" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>788</v>
+      </c>
+      <c r="B148" t="s">
+        <v>346</v>
+      </c>
+      <c r="C148" t="s">
+        <v>789</v>
+      </c>
+      <c r="D148" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" t="s">
+        <v>218</v>
+      </c>
+      <c r="F148" t="s">
+        <v>790</v>
+      </c>
+      <c r="G148" t="s">
+        <v>791</v>
+      </c>
+      <c r="H148" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>793</v>
+      </c>
+      <c r="B149" t="s">
+        <v>794</v>
+      </c>
+      <c r="C149" t="s">
+        <v>795</v>
+      </c>
+      <c r="D149" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" t="s">
+        <v>218</v>
+      </c>
+      <c r="F149" t="s">
+        <v>796</v>
+      </c>
+      <c r="G149" t="s">
+        <v>797</v>
+      </c>
+      <c r="H149" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>799</v>
+      </c>
+      <c r="B150" t="s">
+        <v>800</v>
+      </c>
+      <c r="C150" t="s">
+        <v>801</v>
+      </c>
+      <c r="D150" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" t="s">
+        <v>218</v>
+      </c>
+      <c r="F150" t="s">
+        <v>802</v>
+      </c>
+      <c r="G150" t="s">
+        <v>803</v>
+      </c>
+      <c r="H150" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>805</v>
+      </c>
+      <c r="B151" t="s">
+        <v>806</v>
+      </c>
+      <c r="C151" t="s">
+        <v>807</v>
+      </c>
+      <c r="D151" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" t="s">
+        <v>218</v>
+      </c>
+      <c r="F151" t="s">
+        <v>808</v>
+      </c>
+      <c r="G151" t="s">
+        <v>809</v>
+      </c>
+      <c r="H151" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>811</v>
+      </c>
+      <c r="B152" t="s">
+        <v>812</v>
+      </c>
+      <c r="C152" t="s">
+        <v>813</v>
+      </c>
+      <c r="D152" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" t="s">
+        <v>218</v>
+      </c>
+      <c r="F152" t="s">
+        <v>814</v>
+      </c>
+      <c r="G152" t="s">
+        <v>815</v>
+      </c>
+      <c r="H152" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>817</v>
+      </c>
+      <c r="B153" t="s">
+        <v>818</v>
+      </c>
+      <c r="C153" t="s">
+        <v>819</v>
+      </c>
+      <c r="D153" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" t="s">
+        <v>218</v>
+      </c>
+      <c r="F153" t="s">
+        <v>820</v>
+      </c>
+      <c r="G153" t="s">
+        <v>821</v>
+      </c>
+      <c r="H153" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>823</v>
+      </c>
+      <c r="B154" t="s">
+        <v>137</v>
+      </c>
+      <c r="C154" t="s">
+        <v>824</v>
+      </c>
+      <c r="D154" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" t="s">
         <v>19</v>
       </c>
-      <c r="F147" t="s">
-        <v>764</v>
-      </c>
-      <c r="G147" t="s">
-        <v>765</v>
-      </c>
-      <c r="H147" t="s">
-        <v>766</v>
+      <c r="F154" t="s">
+        <v>825</v>
+      </c>
+      <c r="G154" t="s">
+        <v>262</v>
+      </c>
+      <c r="H154" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>827</v>
+      </c>
+      <c r="B155" t="s">
+        <v>137</v>
+      </c>
+      <c r="C155" t="s">
+        <v>828</v>
+      </c>
+      <c r="D155" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" t="s">
+        <v>19</v>
+      </c>
+      <c r="F155" t="s">
+        <v>829</v>
+      </c>
+      <c r="G155" t="s">
+        <v>262</v>
+      </c>
+      <c r="H155" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>831</v>
+      </c>
+      <c r="B156" t="s">
+        <v>812</v>
+      </c>
+      <c r="C156" t="s">
+        <v>832</v>
+      </c>
+      <c r="D156" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" t="s">
+        <v>218</v>
+      </c>
+      <c r="F156" t="s">
+        <v>833</v>
+      </c>
+      <c r="G156" t="s">
+        <v>834</v>
+      </c>
+      <c r="H156" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>836</v>
+      </c>
+      <c r="B157" t="s">
+        <v>137</v>
+      </c>
+      <c r="C157" t="s">
+        <v>837</v>
+      </c>
+      <c r="D157" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" t="s">
+        <v>19</v>
+      </c>
+      <c r="F157" t="s">
+        <v>838</v>
+      </c>
+      <c r="G157" t="s">
+        <v>262</v>
+      </c>
+      <c r="H157" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>840</v>
+      </c>
+      <c r="B158" t="s">
+        <v>806</v>
+      </c>
+      <c r="C158" t="s">
+        <v>841</v>
+      </c>
+      <c r="D158" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" t="s">
+        <v>218</v>
+      </c>
+      <c r="F158" t="s">
+        <v>842</v>
+      </c>
+      <c r="G158" t="s">
+        <v>843</v>
+      </c>
+      <c r="H158" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>845</v>
+      </c>
+      <c r="B159" t="s">
+        <v>137</v>
+      </c>
+      <c r="C159" t="s">
+        <v>846</v>
+      </c>
+      <c r="D159" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" t="s">
+        <v>19</v>
+      </c>
+      <c r="F159" t="s">
+        <v>847</v>
+      </c>
+      <c r="G159" t="s">
+        <v>262</v>
+      </c>
+      <c r="H159" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>849</v>
+      </c>
+      <c r="B160" t="s">
+        <v>137</v>
+      </c>
+      <c r="C160" t="s">
+        <v>850</v>
+      </c>
+      <c r="D160" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" t="s">
+        <v>19</v>
+      </c>
+      <c r="F160" t="s">
+        <v>851</v>
+      </c>
+      <c r="G160" t="s">
+        <v>262</v>
+      </c>
+      <c r="H160" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>853</v>
+      </c>
+      <c r="B161" t="s">
+        <v>137</v>
+      </c>
+      <c r="C161" t="s">
+        <v>854</v>
+      </c>
+      <c r="D161" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" t="s">
+        <v>19</v>
+      </c>
+      <c r="F161" t="s">
+        <v>855</v>
+      </c>
+      <c r="G161" t="s">
+        <v>262</v>
+      </c>
+      <c r="H161" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>857</v>
+      </c>
+      <c r="B162" t="s">
+        <v>858</v>
+      </c>
+      <c r="C162" t="s">
+        <v>859</v>
+      </c>
+      <c r="D162" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" t="s">
+        <v>218</v>
+      </c>
+      <c r="F162" t="s">
+        <v>860</v>
+      </c>
+      <c r="G162" t="s">
+        <v>861</v>
+      </c>
+      <c r="H162" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>863</v>
+      </c>
+      <c r="B163" t="s">
+        <v>812</v>
+      </c>
+      <c r="C163" t="s">
+        <v>864</v>
+      </c>
+      <c r="D163" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" t="s">
+        <v>218</v>
+      </c>
+      <c r="F163" t="s">
+        <v>865</v>
+      </c>
+      <c r="G163" t="s">
+        <v>866</v>
+      </c>
+      <c r="H163" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>868</v>
+      </c>
+      <c r="B164" t="s">
+        <v>137</v>
+      </c>
+      <c r="C164" t="s">
+        <v>869</v>
+      </c>
+      <c r="D164" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" t="s">
+        <v>19</v>
+      </c>
+      <c r="F164" t="s">
+        <v>870</v>
+      </c>
+      <c r="G164" t="s">
+        <v>262</v>
+      </c>
+      <c r="H164" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>872</v>
+      </c>
+      <c r="B165" t="s">
+        <v>648</v>
+      </c>
+      <c r="C165" t="s">
+        <v>873</v>
+      </c>
+      <c r="D165" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" t="s">
+        <v>218</v>
+      </c>
+      <c r="F165" t="s">
+        <v>874</v>
+      </c>
+      <c r="G165" t="s">
+        <v>875</v>
+      </c>
+      <c r="H165" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>877</v>
+      </c>
+      <c r="B166" t="s">
+        <v>375</v>
+      </c>
+      <c r="C166" t="s">
+        <v>878</v>
+      </c>
+      <c r="D166" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" t="s">
+        <v>218</v>
+      </c>
+      <c r="F166" t="s">
+        <v>879</v>
+      </c>
+      <c r="G166" t="s">
+        <v>880</v>
+      </c>
+      <c r="H166" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>882</v>
+      </c>
+      <c r="B167" t="s">
+        <v>346</v>
+      </c>
+      <c r="C167" t="s">
+        <v>883</v>
+      </c>
+      <c r="D167" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" t="s">
+        <v>218</v>
+      </c>
+      <c r="F167" t="s">
+        <v>884</v>
+      </c>
+      <c r="G167" t="s">
+        <v>885</v>
+      </c>
+      <c r="H167" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>887</v>
+      </c>
+      <c r="B168" t="s">
+        <v>346</v>
+      </c>
+      <c r="C168" t="s">
+        <v>888</v>
+      </c>
+      <c r="D168" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" t="s">
+        <v>218</v>
+      </c>
+      <c r="F168" t="s">
+        <v>889</v>
+      </c>
+      <c r="G168" t="s">
+        <v>890</v>
+      </c>
+      <c r="H168" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>892</v>
+      </c>
+      <c r="B169" t="s">
+        <v>352</v>
+      </c>
+      <c r="C169" t="s">
+        <v>893</v>
+      </c>
+      <c r="D169" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" t="s">
+        <v>218</v>
+      </c>
+      <c r="F169" t="s">
+        <v>894</v>
+      </c>
+      <c r="G169" t="s">
+        <v>895</v>
+      </c>
+      <c r="H169" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>897</v>
+      </c>
+      <c r="B170" t="s">
+        <v>648</v>
+      </c>
+      <c r="C170" t="s">
+        <v>898</v>
+      </c>
+      <c r="D170" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" t="s">
+        <v>218</v>
+      </c>
+      <c r="F170" t="s">
+        <v>899</v>
+      </c>
+      <c r="G170" t="s">
+        <v>900</v>
+      </c>
+      <c r="H170" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>902</v>
+      </c>
+      <c r="B171" t="s">
+        <v>812</v>
+      </c>
+      <c r="C171" t="s">
+        <v>903</v>
+      </c>
+      <c r="D171" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" t="s">
+        <v>218</v>
+      </c>
+      <c r="F171" t="s">
+        <v>904</v>
+      </c>
+      <c r="G171" t="s">
+        <v>905</v>
+      </c>
+      <c r="H171" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>907</v>
+      </c>
+      <c r="B172" t="s">
+        <v>800</v>
+      </c>
+      <c r="C172" t="s">
+        <v>908</v>
+      </c>
+      <c r="D172" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" t="s">
+        <v>218</v>
+      </c>
+      <c r="F172" t="s">
+        <v>909</v>
+      </c>
+      <c r="G172" t="s">
+        <v>910</v>
+      </c>
+      <c r="H172" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>912</v>
+      </c>
+      <c r="B173" t="s">
+        <v>223</v>
+      </c>
+      <c r="C173" t="s">
+        <v>913</v>
+      </c>
+      <c r="D173" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" t="s">
+        <v>19</v>
+      </c>
+      <c r="F173" t="s">
+        <v>914</v>
+      </c>
+      <c r="G173" t="s">
+        <v>272</v>
+      </c>
+      <c r="H173" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>916</v>
+      </c>
+      <c r="B174" t="s">
+        <v>794</v>
+      </c>
+      <c r="C174" t="s">
+        <v>917</v>
+      </c>
+      <c r="D174" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" t="s">
+        <v>218</v>
+      </c>
+      <c r="F174" t="s">
+        <v>918</v>
+      </c>
+      <c r="G174" t="s">
+        <v>919</v>
+      </c>
+      <c r="H174" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>921</v>
+      </c>
+      <c r="B175" t="s">
+        <v>794</v>
+      </c>
+      <c r="C175" t="s">
+        <v>922</v>
+      </c>
+      <c r="D175" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" t="s">
+        <v>218</v>
+      </c>
+      <c r="F175" t="s">
+        <v>923</v>
+      </c>
+      <c r="G175" t="s">
+        <v>924</v>
+      </c>
+      <c r="H175" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>926</v>
+      </c>
+      <c r="B176" t="s">
+        <v>794</v>
+      </c>
+      <c r="C176" t="s">
+        <v>927</v>
+      </c>
+      <c r="D176" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" t="s">
+        <v>218</v>
+      </c>
+      <c r="F176" t="s">
+        <v>928</v>
+      </c>
+      <c r="G176" t="s">
+        <v>929</v>
+      </c>
+      <c r="H176" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>931</v>
+      </c>
+      <c r="B177" t="s">
+        <v>223</v>
+      </c>
+      <c r="C177" t="s">
+        <v>932</v>
+      </c>
+      <c r="D177" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" t="s">
+        <v>19</v>
+      </c>
+      <c r="F177" t="s">
+        <v>933</v>
+      </c>
+      <c r="G177" t="s">
+        <v>272</v>
+      </c>
+      <c r="H177" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>935</v>
+      </c>
+      <c r="B178" t="s">
+        <v>936</v>
+      </c>
+      <c r="C178" t="s">
+        <v>937</v>
+      </c>
+      <c r="D178" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" t="s">
+        <v>218</v>
+      </c>
+      <c r="F178" t="s">
+        <v>938</v>
+      </c>
+      <c r="G178" t="s">
+        <v>939</v>
+      </c>
+      <c r="H178" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>941</v>
+      </c>
+      <c r="B179" t="s">
+        <v>794</v>
+      </c>
+      <c r="C179" t="s">
+        <v>942</v>
+      </c>
+      <c r="D179" t="s">
+        <v>11</v>
+      </c>
+      <c r="E179" t="s">
+        <v>218</v>
+      </c>
+      <c r="F179" t="s">
+        <v>943</v>
+      </c>
+      <c r="G179" t="s">
+        <v>944</v>
+      </c>
+      <c r="H179" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>946</v>
+      </c>
+      <c r="B180" t="s">
+        <v>936</v>
+      </c>
+      <c r="C180" t="s">
+        <v>947</v>
+      </c>
+      <c r="D180" t="s">
+        <v>11</v>
+      </c>
+      <c r="E180" t="s">
+        <v>218</v>
+      </c>
+      <c r="F180" t="s">
+        <v>948</v>
+      </c>
+      <c r="G180" t="s">
+        <v>949</v>
+      </c>
+      <c r="H180" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>951</v>
+      </c>
+      <c r="B181" t="s">
+        <v>952</v>
+      </c>
+      <c r="C181" t="s">
+        <v>953</v>
+      </c>
+      <c r="D181" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" t="s">
+        <v>218</v>
+      </c>
+      <c r="F181" t="s">
+        <v>954</v>
+      </c>
+      <c r="G181" t="s">
+        <v>955</v>
+      </c>
+      <c r="H181" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>957</v>
+      </c>
+      <c r="B182" t="s">
+        <v>794</v>
+      </c>
+      <c r="C182" t="s">
+        <v>958</v>
+      </c>
+      <c r="D182" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" t="s">
+        <v>218</v>
+      </c>
+      <c r="F182" t="s">
+        <v>959</v>
+      </c>
+      <c r="G182" t="s">
+        <v>960</v>
+      </c>
+      <c r="H182" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>962</v>
+      </c>
+      <c r="B183" t="s">
+        <v>806</v>
+      </c>
+      <c r="C183" t="s">
+        <v>963</v>
+      </c>
+      <c r="D183" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" t="s">
+        <v>218</v>
+      </c>
+      <c r="F183" t="s">
+        <v>964</v>
+      </c>
+      <c r="G183" t="s">
+        <v>965</v>
+      </c>
+      <c r="H183" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>967</v>
+      </c>
+      <c r="B184" t="s">
+        <v>794</v>
+      </c>
+      <c r="C184" t="s">
+        <v>968</v>
+      </c>
+      <c r="D184" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" t="s">
+        <v>218</v>
+      </c>
+      <c r="F184" t="s">
+        <v>969</v>
+      </c>
+      <c r="G184" t="s">
+        <v>970</v>
+      </c>
+      <c r="H184" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>972</v>
+      </c>
+      <c r="B185" t="s">
+        <v>800</v>
+      </c>
+      <c r="C185" t="s">
+        <v>973</v>
+      </c>
+      <c r="D185" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" t="s">
+        <v>218</v>
+      </c>
+      <c r="F185" t="s">
+        <v>974</v>
+      </c>
+      <c r="G185" t="s">
+        <v>975</v>
+      </c>
+      <c r="H185" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>977</v>
+      </c>
+      <c r="B186" t="s">
+        <v>936</v>
+      </c>
+      <c r="C186" t="s">
+        <v>978</v>
+      </c>
+      <c r="D186" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" t="s">
+        <v>218</v>
+      </c>
+      <c r="F186" t="s">
+        <v>979</v>
+      </c>
+      <c r="G186" t="s">
+        <v>980</v>
+      </c>
+      <c r="H186" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>982</v>
+      </c>
+      <c r="B187" t="s">
+        <v>794</v>
+      </c>
+      <c r="C187" t="s">
+        <v>983</v>
+      </c>
+      <c r="D187" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" t="s">
+        <v>218</v>
+      </c>
+      <c r="F187" t="s">
+        <v>984</v>
+      </c>
+      <c r="G187" t="s">
+        <v>985</v>
+      </c>
+      <c r="H187" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>987</v>
+      </c>
+      <c r="B188" t="s">
+        <v>936</v>
+      </c>
+      <c r="C188" t="s">
+        <v>988</v>
+      </c>
+      <c r="D188" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" t="s">
+        <v>218</v>
+      </c>
+      <c r="F188" t="s">
+        <v>989</v>
+      </c>
+      <c r="G188" t="s">
+        <v>990</v>
+      </c>
+      <c r="H188" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>992</v>
+      </c>
+      <c r="B189" t="s">
+        <v>993</v>
+      </c>
+      <c r="C189" t="s">
+        <v>994</v>
+      </c>
+      <c r="D189" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" t="s">
+        <v>218</v>
+      </c>
+      <c r="F189" t="s">
+        <v>995</v>
+      </c>
+      <c r="G189" t="s">
+        <v>996</v>
+      </c>
+      <c r="H189" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>998</v>
+      </c>
+      <c r="B190" t="s">
+        <v>223</v>
+      </c>
+      <c r="C190" t="s">
+        <v>999</v>
+      </c>
+      <c r="D190" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" t="s">
+        <v>19</v>
+      </c>
+      <c r="F190" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G190" t="s">
+        <v>272</v>
+      </c>
+      <c r="H190" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B191" t="s">
+        <v>216</v>
+      </c>
+      <c r="C191" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D191" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" t="s">
+        <v>218</v>
+      </c>
+      <c r="F191" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G191" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H191" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B192" t="s">
+        <v>778</v>
+      </c>
+      <c r="C192" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D192" t="s">
+        <v>11</v>
+      </c>
+      <c r="E192" t="s">
+        <v>218</v>
+      </c>
+      <c r="F192" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G192" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H192" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B193" t="s">
+        <v>812</v>
+      </c>
+      <c r="C193" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D193" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" t="s">
+        <v>218</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G193" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H193" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B194" t="s">
+        <v>794</v>
+      </c>
+      <c r="C194" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D194" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" t="s">
+        <v>218</v>
+      </c>
+      <c r="F194" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G194" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H194" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B195" t="s">
+        <v>794</v>
+      </c>
+      <c r="C195" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D195" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" t="s">
+        <v>218</v>
+      </c>
+      <c r="F195" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G195" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H195" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B196" t="s">
+        <v>794</v>
+      </c>
+      <c r="C196" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D196" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" t="s">
+        <v>218</v>
+      </c>
+      <c r="F196" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G196" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H196" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B197" t="s">
+        <v>166</v>
+      </c>
+      <c r="C197" t="s">
+        <v>1033</v>
+      </c>
+      <c r="D197" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" t="s">
+        <v>19</v>
+      </c>
+      <c r="F197" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G197" t="s">
+        <v>277</v>
+      </c>
+      <c r="H197" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B198" t="s">
+        <v>800</v>
+      </c>
+      <c r="C198" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D198" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" t="s">
+        <v>218</v>
+      </c>
+      <c r="F198" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G198" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H198" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B199" t="s">
+        <v>620</v>
+      </c>
+      <c r="C199" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D199" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" t="s">
+        <v>218</v>
+      </c>
+      <c r="F199" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G199" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H199" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B200" t="s">
+        <v>689</v>
+      </c>
+      <c r="C200" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D200" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" t="s">
+        <v>218</v>
+      </c>
+      <c r="F200" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G200" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H200" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B201" t="s">
+        <v>254</v>
+      </c>
+      <c r="C201" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D201" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" t="s">
+        <v>19</v>
+      </c>
+      <c r="F201" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G201" t="s">
+        <v>287</v>
+      </c>
+      <c r="H201" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B202" t="s">
+        <v>254</v>
+      </c>
+      <c r="C202" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D202" t="s">
+        <v>11</v>
+      </c>
+      <c r="E202" t="s">
+        <v>19</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G202" t="s">
+        <v>287</v>
+      </c>
+      <c r="H202" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B203" t="s">
+        <v>806</v>
+      </c>
+      <c r="C203" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D203" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" t="s">
+        <v>218</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G203" t="s">
+        <v>809</v>
+      </c>
+      <c r="H203" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B204" t="s">
+        <v>778</v>
+      </c>
+      <c r="C204" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D204" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" t="s">
+        <v>218</v>
+      </c>
+      <c r="F204" t="s">
+        <v>1065</v>
+      </c>
+      <c r="G204" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H204" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B205" t="s">
+        <v>216</v>
+      </c>
+      <c r="C205" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D205" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" t="s">
+        <v>218</v>
+      </c>
+      <c r="F205" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G205" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H205" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D206" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" t="s">
+        <v>218</v>
+      </c>
+      <c r="F206" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G206" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H206" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B207" t="s">
+        <v>223</v>
+      </c>
+      <c r="C207" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D207" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" t="s">
+        <v>19</v>
+      </c>
+      <c r="F207" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G207" t="s">
+        <v>303</v>
+      </c>
+      <c r="H207" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B208" t="s">
+        <v>36</v>
+      </c>
+      <c r="C208" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D208" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" t="s">
+        <v>19</v>
+      </c>
+      <c r="F208" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G208" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H208" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B209" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C209" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D209" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" t="s">
+        <v>19</v>
+      </c>
+      <c r="F209" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G209" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H209" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B210" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C210" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D210" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" t="s">
+        <v>19</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G210" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H210" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C211" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D211" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" t="s">
+        <v>19</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G211" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H211" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B212" t="s">
+        <v>812</v>
+      </c>
+      <c r="C212" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D212" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" t="s">
+        <v>218</v>
+      </c>
+      <c r="F212" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G212" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H212" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B213" t="s">
+        <v>812</v>
+      </c>
+      <c r="C213" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D213" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" t="s">
+        <v>218</v>
+      </c>
+      <c r="F213" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G213" t="s">
+        <v>1111</v>
+      </c>
+      <c r="H213" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B214" t="s">
+        <v>155</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D214" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" t="s">
+        <v>19</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1115</v>
+      </c>
+      <c r="G214" t="s">
+        <v>246</v>
+      </c>
+      <c r="H214" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B215" t="s">
+        <v>858</v>
+      </c>
+      <c r="C215" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D215" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" t="s">
+        <v>218</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G215" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H215" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B216" t="s">
+        <v>794</v>
+      </c>
+      <c r="C216" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D216" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" t="s">
+        <v>218</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G216" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H216" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B217" t="s">
+        <v>794</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D217" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" t="s">
+        <v>218</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G217" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H217" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B218" t="s">
+        <v>936</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D218" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" t="s">
+        <v>218</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G218" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H218" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B219" t="s">
+        <v>936</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D219" t="s">
+        <v>11</v>
+      </c>
+      <c r="E219" t="s">
+        <v>218</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G219" t="s">
+        <v>1140</v>
+      </c>
+      <c r="H219" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B220" t="s">
+        <v>794</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D220" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" t="s">
+        <v>218</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G220" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H220" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B221" t="s">
+        <v>457</v>
+      </c>
+      <c r="C221" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D221" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" t="s">
+        <v>218</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G221" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H221" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B222" t="s">
+        <v>457</v>
+      </c>
+      <c r="C222" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D222" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" t="s">
+        <v>218</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G222" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H222" t="s">
+        <v>1156</v>
       </c>
     </row>
   </sheetData>
